--- a/Utah_Index_of_Changes.xlsx
+++ b/Utah_Index_of_Changes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Shared drives\DAS_Rules_DAR\Index of Changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93178F6-E823-468E-A328-1F3F44BA8080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEB33FE-70E0-41B8-8F34-D211DCACCAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AB629357-4CE5-4584-B8BD-0FC25277305B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="501">
   <si>
     <t>Published Date</t>
   </si>
@@ -1282,6 +1282,267 @@
   </si>
   <si>
     <t>R746-409</t>
+  </si>
+  <si>
+    <t>Kratom Manufacturer Food Establishment Registration</t>
+  </si>
+  <si>
+    <t>R70-580</t>
+  </si>
+  <si>
+    <t>Internet Content Provider Ratings Methods Rule</t>
+  </si>
+  <si>
+    <t>R152-1a</t>
+  </si>
+  <si>
+    <t>Building Inspector and Factory Built Housing Licensing Act Rule</t>
+  </si>
+  <si>
+    <t>R156-56</t>
+  </si>
+  <si>
+    <t>Respiratory Care Practices Act Rule</t>
+  </si>
+  <si>
+    <t>R156-57</t>
+  </si>
+  <si>
+    <t>Direct-Entry Midwife Act Rule</t>
+  </si>
+  <si>
+    <t>R156-77</t>
+  </si>
+  <si>
+    <t>Crime Victim Reparations</t>
+  </si>
+  <si>
+    <t>Award and Reparation Standards</t>
+  </si>
+  <si>
+    <t>R270-1</t>
+  </si>
+  <si>
+    <t>Process for Reporting Violations of Statute and Board Rule</t>
+  </si>
+  <si>
+    <t>R277-123</t>
+  </si>
+  <si>
+    <t>Teacher Preparation Programs</t>
+  </si>
+  <si>
+    <t>R277-304</t>
+  </si>
+  <si>
+    <t>Standards for LEA Discipline Policy</t>
+  </si>
+  <si>
+    <t>R277-609</t>
+  </si>
+  <si>
+    <t>Education Programs Serving Youth in Care</t>
+  </si>
+  <si>
+    <t>R277-709</t>
+  </si>
+  <si>
+    <t>Statewide Online Education Program</t>
+  </si>
+  <si>
+    <t>R277-726</t>
+  </si>
+  <si>
+    <t>Drinking Water</t>
+  </si>
+  <si>
+    <t>Administration: General Responsibilities of Public Water Systems</t>
+  </si>
+  <si>
+    <t>R309-105</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Payment of Attorney's Fees in Death Penalty Cases</t>
+  </si>
+  <si>
+    <t>R25-14</t>
+  </si>
+  <si>
+    <t>Finance Adjudicative Proceedings</t>
+  </si>
+  <si>
+    <t>R25-2</t>
+  </si>
+  <si>
+    <t>Accounting and Protection of Federal Benefits for Minor Beneficiaries in Custody</t>
+  </si>
+  <si>
+    <t>R380-90</t>
+  </si>
+  <si>
+    <t>Communicable Disease Rule</t>
+  </si>
+  <si>
+    <t>R386-702</t>
+  </si>
+  <si>
+    <t>Food Service Sanitation in Child Care and Residential Care Facilities</t>
+  </si>
+  <si>
+    <t>R392-110</t>
+  </si>
+  <si>
+    <t>Medical Support Services</t>
+  </si>
+  <si>
+    <t>R527-201</t>
+  </si>
+  <si>
+    <t>Parental Support for Children in Care</t>
+  </si>
+  <si>
+    <t>R527-220</t>
+  </si>
+  <si>
+    <t>Children in Care Support Services</t>
+  </si>
+  <si>
+    <t>R527-221</t>
+  </si>
+  <si>
+    <t>Release of Information</t>
+  </si>
+  <si>
+    <t>R527-5</t>
+  </si>
+  <si>
+    <t>Government Records Access and Management</t>
+  </si>
+  <si>
+    <t>R765-124</t>
+  </si>
+  <si>
+    <t>Equal Opportunity Initiatives</t>
+  </si>
+  <si>
+    <t>R765-130</t>
+  </si>
+  <si>
+    <t>Student Religious Accommodations</t>
+  </si>
+  <si>
+    <t>R765-264</t>
+  </si>
+  <si>
+    <t>Utah System of Higher Education Disclosures</t>
+  </si>
+  <si>
+    <t>R765-266</t>
+  </si>
+  <si>
+    <t>State Authorization Reciprocity Agreement Rule</t>
+  </si>
+  <si>
+    <t>R765-431</t>
+  </si>
+  <si>
+    <t>Prohibitions on and Disclosures of Foreign Donations to Higher Education Institutions</t>
+  </si>
+  <si>
+    <t>R765-545</t>
+  </si>
+  <si>
+    <t>Public Safety Officer Career Advancement Grant Program</t>
+  </si>
+  <si>
+    <t>R765-614</t>
+  </si>
+  <si>
+    <t>International Internship Scholarship Pilot Program Fund</t>
+  </si>
+  <si>
+    <t>R765-625</t>
+  </si>
+  <si>
+    <t>Minimum Standards for Short-Term Limited Duration Health Insurance</t>
+  </si>
+  <si>
+    <t>R590-286</t>
+  </si>
+  <si>
+    <t>Predator Control Incentives</t>
+  </si>
+  <si>
+    <t>R657-64</t>
+  </si>
+  <si>
+    <t>Cooperative Agreements for Big Game or Turkey</t>
+  </si>
+  <si>
+    <t>R657-74</t>
+  </si>
+  <si>
+    <t>R671-101</t>
+  </si>
+  <si>
+    <t>Notification of Hearings</t>
+  </si>
+  <si>
+    <t>R671-202</t>
+  </si>
+  <si>
+    <t>News Media and Public Access to Hearings</t>
+  </si>
+  <si>
+    <t>R671-302</t>
+  </si>
+  <si>
+    <t>Motor Carrier</t>
+  </si>
+  <si>
+    <t>Utah Size and Weight Rule</t>
+  </si>
+  <si>
+    <t>R909-2</t>
+  </si>
+  <si>
+    <t>Operations, Construction</t>
+  </si>
+  <si>
+    <t>Advertising and Awarding Construction Contracts</t>
+  </si>
+  <si>
+    <t>R916-1</t>
+  </si>
+  <si>
+    <t>Prequalification of Contractors</t>
+  </si>
+  <si>
+    <t>R916-2</t>
+  </si>
+  <si>
+    <t>Design-Build Contracts</t>
+  </si>
+  <si>
+    <t>R916-3</t>
+  </si>
+  <si>
+    <t>Construction Manager/General Contractor and Progressive Construction Manager/General Contractor Contracts</t>
+  </si>
+  <si>
+    <t>R916-4</t>
+  </si>
+  <si>
+    <t>Transportation Commission</t>
+  </si>
+  <si>
+    <t>Establishment of Toll Rates</t>
+  </si>
+  <si>
+    <t>R940-1</t>
   </si>
 </sst>
 </file>
@@ -1981,8 +2242,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}" name="IndexofChanges2026" displayName="IndexofChanges2026" ref="A1:I181" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A1:I181" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}" name="IndexofChanges2026" displayName="IndexofChanges2026" ref="A1:I225" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A1:I225" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A5D7328E-E900-42CC-861B-C0B93E9FA323}" name="Agency Name" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{6813DE60-D8C9-46E4-9980-0485DD9243AF}" name="Title Name"/>
@@ -2329,7 +2590,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I181"/>
+  <dimension ref="A1:I225"/>
   <sheetFormatPr defaultColWidth="32.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.7109375" bestFit="1" customWidth="1"/>
@@ -2754,28 +3015,28 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>414</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>415</v>
       </c>
       <c r="E15">
-        <v>57488</v>
+        <v>57525</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G15" s="5">
-        <v>45912</v>
+        <v>46084</v>
       </c>
       <c r="H15" s="5">
-        <v>45931</v>
+        <v>46096</v>
       </c>
       <c r="I15" s="5">
-        <v>46029</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2795,13 +3056,13 @@
         <v>57488</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G16" s="5">
-        <v>45966</v>
+        <v>45912</v>
       </c>
       <c r="H16" s="5">
-        <v>45992</v>
+        <v>45931</v>
       </c>
       <c r="I16" s="5">
         <v>46029</v>
@@ -2815,22 +3076,22 @@
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E17">
-        <v>57403</v>
+        <v>57488</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G17" s="5">
-        <v>45887</v>
+        <v>45966</v>
       </c>
       <c r="H17" s="5">
-        <v>45915</v>
+        <v>45992</v>
       </c>
       <c r="I17" s="5">
         <v>46029</v>
@@ -2853,13 +3114,13 @@
         <v>57403</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G18" s="5">
-        <v>45966</v>
+        <v>45887</v>
       </c>
       <c r="H18" s="5">
-        <v>45992</v>
+        <v>45915</v>
       </c>
       <c r="I18" s="5">
         <v>46029</v>
@@ -2867,22 +3128,22 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="E19">
-        <v>57665</v>
+        <v>57403</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G19" s="5">
         <v>45966</v>
@@ -2891,36 +3152,36 @@
         <v>45992</v>
       </c>
       <c r="I19" s="5">
-        <v>46052</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E20">
-        <v>57528</v>
+        <v>57665</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G20" s="5">
-        <v>45930</v>
+        <v>45966</v>
       </c>
       <c r="H20" s="5">
-        <v>45945</v>
+        <v>45992</v>
       </c>
       <c r="I20" s="5">
-        <v>46023</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -2928,28 +3189,28 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>373</v>
+        <v>416</v>
       </c>
       <c r="D21" t="s">
-        <v>374</v>
+        <v>417</v>
       </c>
       <c r="E21">
-        <v>57754</v>
+        <v>54255</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G21" s="5">
-        <v>46027</v>
+        <v>46093</v>
       </c>
       <c r="H21" s="5">
-        <v>46037</v>
+        <v>46096</v>
       </c>
       <c r="I21" s="5">
-        <v>46077</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -2957,28 +3218,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>416</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>417</v>
       </c>
       <c r="E22">
-        <v>57661</v>
+        <v>57852</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G22" s="5">
-        <v>45965</v>
-      </c>
-      <c r="H22" s="5">
-        <v>45992</v>
+        <v>46093</v>
+      </c>
+      <c r="H22" t="s">
+        <v>65</v>
       </c>
       <c r="I22" s="5">
-        <v>46037</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -2986,28 +3247,28 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="E23">
-        <v>56871</v>
+        <v>57528</v>
       </c>
       <c r="F23" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G23" s="5">
-        <v>46029</v>
+        <v>45930</v>
       </c>
       <c r="H23" s="5">
-        <v>46047</v>
+        <v>45945</v>
       </c>
       <c r="I23" s="5">
-        <v>46029</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -3018,228 +3279,228 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>373</v>
       </c>
       <c r="D24" t="s">
-        <v>118</v>
+        <v>374</v>
       </c>
       <c r="E24">
-        <v>50314</v>
+        <v>57754</v>
       </c>
       <c r="F24" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G24" s="5">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="H24" s="5">
-        <v>46047</v>
+        <v>46037</v>
       </c>
       <c r="I24" s="5">
-        <v>46029</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>260</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>261</v>
+        <v>58</v>
       </c>
       <c r="E25">
-        <v>57687</v>
+        <v>57661</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G25" s="5">
-        <v>45980</v>
+        <v>45965</v>
       </c>
       <c r="H25" s="5">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="I25" s="5">
-        <v>46066</v>
+        <v>46037</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>262</v>
+        <v>418</v>
       </c>
       <c r="D26" t="s">
-        <v>263</v>
+        <v>419</v>
       </c>
       <c r="E26">
-        <v>57688</v>
+        <v>57633</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G26" s="5">
-        <v>45980</v>
+        <v>45965</v>
       </c>
       <c r="H26" s="5">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="I26" s="5">
-        <v>46066</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>264</v>
+        <v>420</v>
       </c>
       <c r="D27" t="s">
-        <v>265</v>
+        <v>421</v>
       </c>
       <c r="E27">
-        <v>57689</v>
+        <v>50288</v>
       </c>
       <c r="F27" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G27" s="5">
-        <v>45980</v>
+        <v>46083</v>
       </c>
       <c r="H27" s="5">
-        <v>46006</v>
+        <v>46096</v>
       </c>
       <c r="I27" s="5">
-        <v>46066</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>267</v>
+        <v>116</v>
       </c>
       <c r="E28">
-        <v>57690</v>
+        <v>56871</v>
       </c>
       <c r="F28" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G28" s="5">
-        <v>45980</v>
+        <v>46029</v>
       </c>
       <c r="H28" s="5">
-        <v>46006</v>
+        <v>46047</v>
       </c>
       <c r="I28" s="5">
-        <v>46066</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>268</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>260</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>269</v>
+        <v>118</v>
       </c>
       <c r="E29">
-        <v>57564</v>
+        <v>50314</v>
       </c>
       <c r="F29" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G29" s="5">
-        <v>45947</v>
+        <v>46029</v>
       </c>
       <c r="H29" s="5">
-        <v>45976</v>
+        <v>46047</v>
       </c>
       <c r="I29" s="5">
-        <v>46066</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>268</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>270</v>
+        <v>422</v>
       </c>
       <c r="D30" t="s">
-        <v>271</v>
+        <v>423</v>
       </c>
       <c r="E30">
-        <v>57565</v>
+        <v>56813</v>
       </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G30" s="5">
-        <v>45947</v>
+        <v>46083</v>
       </c>
       <c r="H30" s="5">
-        <v>45976</v>
+        <v>46096</v>
       </c>
       <c r="I30" s="5">
-        <v>46066</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>258</v>
+        <v>424</v>
       </c>
       <c r="B31" t="s">
-        <v>268</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>264</v>
+        <v>425</v>
       </c>
       <c r="D31" t="s">
-        <v>272</v>
+        <v>426</v>
       </c>
       <c r="E31">
-        <v>57566</v>
+        <v>55794</v>
       </c>
       <c r="F31" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G31" s="5">
-        <v>45947</v>
+        <v>46087</v>
       </c>
       <c r="H31" s="5">
-        <v>45976</v>
+        <v>46096</v>
       </c>
       <c r="I31" s="5">
-        <v>46066</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -3247,25 +3508,25 @@
         <v>258</v>
       </c>
       <c r="B32" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D32" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="E32">
-        <v>57567</v>
+        <v>57687</v>
       </c>
       <c r="F32" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="G32" s="5">
-        <v>45947</v>
+        <v>45980</v>
       </c>
       <c r="H32" s="5">
-        <v>45976</v>
+        <v>46006</v>
       </c>
       <c r="I32" s="5">
         <v>46066</v>
@@ -3273,205 +3534,205 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>263</v>
       </c>
       <c r="E33">
-        <v>57677</v>
+        <v>57688</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G33" s="5">
-        <v>45975</v>
+        <v>45980</v>
       </c>
       <c r="H33" s="5">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="I33" s="5">
-        <v>46029</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="C34" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="E34">
-        <v>57719</v>
+        <v>57689</v>
       </c>
       <c r="F34" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="G34" s="5">
+        <v>45980</v>
+      </c>
+      <c r="H34" s="5">
         <v>46006</v>
       </c>
-      <c r="H34" s="5">
-        <v>46023</v>
-      </c>
       <c r="I34" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D35" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E35">
-        <v>57720</v>
+        <v>57690</v>
       </c>
       <c r="F35" t="s">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="G35" s="5">
+        <v>45980</v>
+      </c>
+      <c r="H35" s="5">
         <v>46006</v>
       </c>
-      <c r="H35" s="5">
-        <v>46023</v>
-      </c>
       <c r="I35" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="C36" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="D36" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="E36">
-        <v>57721</v>
+        <v>57564</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G36" s="5">
-        <v>46006</v>
+        <v>45947</v>
       </c>
       <c r="H36" s="5">
-        <v>46023</v>
+        <v>45976</v>
       </c>
       <c r="I36" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="C37" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D37" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="E37">
-        <v>57722</v>
+        <v>57565</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G37" s="5">
-        <v>46006</v>
+        <v>45947</v>
       </c>
       <c r="H37" s="5">
-        <v>46023</v>
+        <v>45976</v>
       </c>
       <c r="I37" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="C38" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="D38" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="E38">
-        <v>57723</v>
+        <v>57566</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G38" s="5">
-        <v>46006</v>
+        <v>45947</v>
       </c>
       <c r="H38" s="5">
-        <v>46023</v>
+        <v>45976</v>
       </c>
       <c r="I38" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="C39" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="D39" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E39">
-        <v>57724</v>
+        <v>57567</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G39" s="5">
-        <v>46006</v>
+        <v>45947</v>
       </c>
       <c r="H39" s="5">
-        <v>46023</v>
+        <v>45976</v>
       </c>
       <c r="I39" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -3482,25 +3743,25 @@
         <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E40">
-        <v>57737</v>
+        <v>57677</v>
       </c>
       <c r="F40" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G40" s="5">
-        <v>46008</v>
-      </c>
-      <c r="H40" t="s">
-        <v>65</v>
+        <v>45975</v>
+      </c>
+      <c r="H40" s="5">
+        <v>45992</v>
       </c>
       <c r="I40" s="5">
-        <v>46027</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -3511,25 +3772,25 @@
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>62</v>
+        <v>274</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>275</v>
       </c>
       <c r="E41">
-        <v>57765</v>
+        <v>57719</v>
       </c>
       <c r="F41" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G41" s="5">
-        <v>46037</v>
-      </c>
-      <c r="H41" t="s">
-        <v>65</v>
+        <v>46006</v>
+      </c>
+      <c r="H41" s="5">
+        <v>46023</v>
       </c>
       <c r="I41" s="5">
-        <v>46047</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -3540,25 +3801,25 @@
         <v>35</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>276</v>
       </c>
       <c r="D42" t="s">
-        <v>67</v>
+        <v>277</v>
       </c>
       <c r="E42">
-        <v>57678</v>
+        <v>57720</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="G42" s="5">
-        <v>45975</v>
+        <v>46006</v>
       </c>
       <c r="H42" s="5">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I42" s="5">
-        <v>46029</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -3569,25 +3830,25 @@
         <v>35</v>
       </c>
       <c r="C43" t="s">
-        <v>68</v>
+        <v>427</v>
       </c>
       <c r="D43" t="s">
-        <v>69</v>
+        <v>428</v>
       </c>
       <c r="E43">
-        <v>57679</v>
+        <v>57849</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G43" s="5">
-        <v>45975</v>
-      </c>
-      <c r="H43" s="5">
-        <v>45992</v>
+        <v>46087</v>
+      </c>
+      <c r="H43" t="s">
+        <v>65</v>
       </c>
       <c r="I43" s="5">
-        <v>46029</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -3598,25 +3859,25 @@
         <v>35</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>278</v>
       </c>
       <c r="D44" t="s">
-        <v>71</v>
+        <v>279</v>
       </c>
       <c r="E44">
-        <v>57735</v>
+        <v>57721</v>
       </c>
       <c r="F44" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G44" s="5">
-        <v>46007</v>
-      </c>
-      <c r="H44" t="s">
-        <v>65</v>
+        <v>46006</v>
+      </c>
+      <c r="H44" s="5">
+        <v>46023</v>
       </c>
       <c r="I44" s="5">
-        <v>46027</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -3627,13 +3888,13 @@
         <v>35</v>
       </c>
       <c r="C45" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D45" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E45">
-        <v>57725</v>
+        <v>57722</v>
       </c>
       <c r="F45" t="s">
         <v>10</v>
@@ -3656,13 +3917,13 @@
         <v>35</v>
       </c>
       <c r="C46" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D46" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E46">
-        <v>57726</v>
+        <v>57723</v>
       </c>
       <c r="F46" t="s">
         <v>10</v>
@@ -3685,13 +3946,13 @@
         <v>35</v>
       </c>
       <c r="C47" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D47" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E47">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="F47" t="s">
         <v>10</v>
@@ -3714,25 +3975,25 @@
         <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>292</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>293</v>
+        <v>63</v>
       </c>
       <c r="E48">
-        <v>57728</v>
+        <v>57737</v>
       </c>
       <c r="F48" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G48" s="5">
-        <v>46006</v>
-      </c>
-      <c r="H48" s="5">
-        <v>46023</v>
+        <v>46008</v>
+      </c>
+      <c r="H48" t="s">
+        <v>65</v>
       </c>
       <c r="I48" s="5">
-        <v>46062</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -3743,25 +4004,25 @@
         <v>35</v>
       </c>
       <c r="C49" t="s">
-        <v>294</v>
+        <v>62</v>
       </c>
       <c r="D49" t="s">
-        <v>295</v>
+        <v>63</v>
       </c>
       <c r="E49">
-        <v>57729</v>
+        <v>57765</v>
       </c>
       <c r="F49" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G49" s="5">
-        <v>46006</v>
-      </c>
-      <c r="H49" s="5">
-        <v>46023</v>
+        <v>46037</v>
+      </c>
+      <c r="H49" t="s">
+        <v>65</v>
       </c>
       <c r="I49" s="5">
-        <v>46062</v>
+        <v>46047</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -3772,25 +4033,25 @@
         <v>35</v>
       </c>
       <c r="C50" t="s">
-        <v>296</v>
+        <v>429</v>
       </c>
       <c r="D50" t="s">
-        <v>297</v>
+        <v>430</v>
       </c>
       <c r="E50">
-        <v>57730</v>
+        <v>57761</v>
       </c>
       <c r="F50" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="5">
-        <v>46006</v>
+        <v>46037</v>
       </c>
       <c r="H50" s="5">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="I50" s="5">
-        <v>46062</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -3801,25 +4062,25 @@
         <v>35</v>
       </c>
       <c r="C51" t="s">
-        <v>296</v>
+        <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>297</v>
+        <v>67</v>
       </c>
       <c r="E51">
-        <v>57807</v>
+        <v>57678</v>
       </c>
       <c r="F51" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G51" s="5">
-        <v>46073</v>
-      </c>
-      <c r="H51" t="s">
-        <v>65</v>
+        <v>45975</v>
+      </c>
+      <c r="H51" s="5">
+        <v>45992</v>
       </c>
       <c r="I51" s="5">
-        <v>46082</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -3830,25 +4091,25 @@
         <v>35</v>
       </c>
       <c r="C52" t="s">
-        <v>298</v>
+        <v>68</v>
       </c>
       <c r="D52" t="s">
-        <v>299</v>
+        <v>69</v>
       </c>
       <c r="E52">
-        <v>57731</v>
+        <v>57679</v>
       </c>
       <c r="F52" t="s">
         <v>10</v>
       </c>
       <c r="G52" s="5">
-        <v>46006</v>
+        <v>45975</v>
       </c>
       <c r="H52" s="5">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="I52" s="5">
-        <v>46062</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -3859,109 +4120,109 @@
         <v>35</v>
       </c>
       <c r="C53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E53">
-        <v>57680</v>
+        <v>57735</v>
       </c>
       <c r="F53" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="G53" s="5">
-        <v>45975</v>
-      </c>
-      <c r="H53" s="5">
-        <v>45992</v>
+        <v>46007</v>
+      </c>
+      <c r="H53" t="s">
+        <v>65</v>
       </c>
       <c r="I53" s="5">
-        <v>46029</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>300</v>
+        <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="D54" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="E54">
-        <v>57666</v>
+        <v>57725</v>
       </c>
       <c r="F54" t="s">
         <v>10</v>
       </c>
       <c r="G54" s="5">
-        <v>45966</v>
+        <v>46006</v>
       </c>
       <c r="H54" s="5">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I54" s="5">
-        <v>46057</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>300</v>
+        <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="D55" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="E55">
-        <v>53313</v>
+        <v>57726</v>
       </c>
       <c r="F55" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G55" s="5">
-        <v>46057</v>
+        <v>46006</v>
       </c>
       <c r="H55" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I55" s="5">
         <v>46062</v>
-      </c>
-      <c r="I55" s="5">
-        <v>46057</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="C56" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="D56" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="E56">
-        <v>50710</v>
+        <v>57727</v>
       </c>
       <c r="F56" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G56" s="5">
-        <v>46062</v>
+        <v>46006</v>
       </c>
       <c r="H56" s="5">
-        <v>46066</v>
+        <v>46023</v>
       </c>
       <c r="I56" s="5">
         <v>46062</v>
@@ -3969,814 +4230,814 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
+        <v>292</v>
       </c>
       <c r="D57" t="s">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="E57">
-        <v>57545</v>
+        <v>57728</v>
       </c>
       <c r="F57" t="s">
         <v>10</v>
       </c>
       <c r="G57" s="5">
-        <v>45939</v>
+        <v>46006</v>
       </c>
       <c r="H57" s="5">
-        <v>45962</v>
+        <v>46023</v>
       </c>
       <c r="I57" s="5">
-        <v>46034</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B58" t="s">
         <v>35</v>
       </c>
       <c r="C58" t="s">
-        <v>376</v>
+        <v>431</v>
       </c>
       <c r="D58" t="s">
-        <v>377</v>
+        <v>432</v>
       </c>
       <c r="E58">
-        <v>50789</v>
+        <v>57762</v>
       </c>
       <c r="F58" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="G58" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H58" t="s">
-        <v>358</v>
+        <v>46037</v>
+      </c>
+      <c r="H58" s="5">
+        <v>46054</v>
       </c>
       <c r="I58" s="5">
-        <v>46078</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B59" t="s">
         <v>35</v>
       </c>
       <c r="C59" t="s">
-        <v>378</v>
+        <v>294</v>
       </c>
       <c r="D59" t="s">
-        <v>379</v>
+        <v>295</v>
       </c>
       <c r="E59">
-        <v>50793</v>
+        <v>57729</v>
       </c>
       <c r="F59" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="G59" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H59" t="s">
-        <v>358</v>
+        <v>46006</v>
+      </c>
+      <c r="H59" s="5">
+        <v>46023</v>
       </c>
       <c r="I59" s="5">
-        <v>46078</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B60" t="s">
         <v>35</v>
       </c>
       <c r="C60" t="s">
-        <v>380</v>
+        <v>296</v>
       </c>
       <c r="D60" t="s">
-        <v>381</v>
+        <v>297</v>
       </c>
       <c r="E60">
-        <v>50790</v>
+        <v>57730</v>
       </c>
       <c r="F60" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="G60" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H60" t="s">
-        <v>358</v>
+        <v>46006</v>
+      </c>
+      <c r="H60" s="5">
+        <v>46023</v>
       </c>
       <c r="I60" s="5">
-        <v>46078</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
         <v>35</v>
       </c>
       <c r="C61" t="s">
-        <v>382</v>
+        <v>296</v>
       </c>
       <c r="D61" t="s">
-        <v>383</v>
+        <v>297</v>
       </c>
       <c r="E61">
-        <v>50799</v>
+        <v>57807</v>
       </c>
       <c r="F61" t="s">
-        <v>357</v>
+        <v>64</v>
       </c>
       <c r="G61" s="5">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="H61" t="s">
-        <v>358</v>
+        <v>65</v>
       </c>
       <c r="I61" s="5">
-        <v>46078</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B62" t="s">
         <v>35</v>
       </c>
       <c r="C62" t="s">
-        <v>384</v>
+        <v>433</v>
       </c>
       <c r="D62" t="s">
-        <v>385</v>
+        <v>434</v>
       </c>
       <c r="E62">
-        <v>50803</v>
+        <v>57763</v>
       </c>
       <c r="F62" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="G62" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H62" t="s">
-        <v>358</v>
+        <v>46037</v>
+      </c>
+      <c r="H62" s="5">
+        <v>46054</v>
       </c>
       <c r="I62" s="5">
-        <v>46078</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="B63" t="s">
         <v>35</v>
       </c>
       <c r="C63" t="s">
-        <v>120</v>
+        <v>298</v>
       </c>
       <c r="D63" t="s">
-        <v>121</v>
+        <v>299</v>
       </c>
       <c r="E63">
-        <v>50812</v>
+        <v>57731</v>
       </c>
       <c r="F63" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G63" s="5">
-        <v>46028</v>
+        <v>46006</v>
       </c>
       <c r="H63" s="5">
-        <v>46047</v>
+        <v>46023</v>
       </c>
       <c r="I63" s="5">
-        <v>46028</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>435</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>436</v>
       </c>
       <c r="E64">
-        <v>57692</v>
+        <v>57764</v>
       </c>
       <c r="F64" t="s">
         <v>10</v>
       </c>
       <c r="G64" s="5">
-        <v>45987</v>
+        <v>46037</v>
       </c>
       <c r="H64" s="5">
-        <v>46006</v>
+        <v>46054</v>
       </c>
       <c r="I64" s="5">
-        <v>46043</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="B65" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="C65" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="D65" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="E65">
-        <v>57693</v>
+        <v>57680</v>
       </c>
       <c r="F65" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G65" s="5">
-        <v>45987</v>
+        <v>45975</v>
       </c>
       <c r="H65" s="5">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="I65" s="5">
-        <v>46043</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="B66" t="s">
-        <v>122</v>
+        <v>300</v>
       </c>
       <c r="C66" t="s">
-        <v>127</v>
+        <v>301</v>
       </c>
       <c r="D66" t="s">
-        <v>128</v>
+        <v>302</v>
       </c>
       <c r="E66">
-        <v>57694</v>
+        <v>57666</v>
       </c>
       <c r="F66" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="5">
-        <v>45987</v>
+        <v>45966</v>
       </c>
       <c r="H66" s="5">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="I66" s="5">
-        <v>46043</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="C67" t="s">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="D67" t="s">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="E67">
-        <v>57684</v>
+        <v>53313</v>
       </c>
       <c r="F67" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G67" s="5">
-        <v>45975</v>
+        <v>46057</v>
       </c>
       <c r="H67" s="5">
-        <v>45992</v>
+        <v>46062</v>
       </c>
       <c r="I67" s="5">
-        <v>46035</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>437</v>
       </c>
       <c r="C68" t="s">
-        <v>129</v>
+        <v>438</v>
       </c>
       <c r="D68" t="s">
-        <v>130</v>
+        <v>439</v>
       </c>
       <c r="E68">
-        <v>57696</v>
+        <v>57815</v>
       </c>
       <c r="F68" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G68" s="5">
-        <v>45989</v>
-      </c>
-      <c r="H68" s="5">
-        <v>46006</v>
+        <v>46078</v>
+      </c>
+      <c r="H68" t="s">
+        <v>65</v>
       </c>
       <c r="I68" s="5">
-        <v>46050</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="C69" t="s">
-        <v>129</v>
+        <v>306</v>
       </c>
       <c r="D69" t="s">
-        <v>130</v>
+        <v>307</v>
       </c>
       <c r="E69">
-        <v>57696</v>
+        <v>50710</v>
       </c>
       <c r="F69" t="s">
         <v>107</v>
       </c>
       <c r="G69" s="5">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H69" s="5">
+        <v>46066</v>
+      </c>
+      <c r="I69" s="5">
         <v>46062</v>
-      </c>
-      <c r="I69" s="5">
-        <v>46059</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="D70" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E70">
-        <v>57616</v>
+        <v>57545</v>
       </c>
       <c r="F70" t="s">
         <v>10</v>
       </c>
       <c r="G70" s="5">
-        <v>45954</v>
+        <v>45939</v>
       </c>
       <c r="H70" s="5">
-        <v>45976</v>
+        <v>45962</v>
       </c>
       <c r="I70" s="5">
-        <v>46048</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="B71" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C71" t="s">
-        <v>133</v>
+        <v>376</v>
       </c>
       <c r="D71" t="s">
-        <v>134</v>
+        <v>377</v>
       </c>
       <c r="E71">
-        <v>57588</v>
+        <v>50789</v>
       </c>
       <c r="F71" t="s">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="G71" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H71" s="5">
-        <v>45976</v>
+        <v>46077</v>
+      </c>
+      <c r="H71" t="s">
+        <v>358</v>
       </c>
       <c r="I71" s="5">
-        <v>46048</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="B72" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C72" t="s">
-        <v>135</v>
+        <v>378</v>
       </c>
       <c r="D72" t="s">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="E72">
-        <v>57589</v>
+        <v>50793</v>
       </c>
       <c r="F72" t="s">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="G72" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H72" s="5">
-        <v>45976</v>
+        <v>46077</v>
+      </c>
+      <c r="H72" t="s">
+        <v>358</v>
       </c>
       <c r="I72" s="5">
-        <v>46048</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="B73" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C73" t="s">
-        <v>137</v>
+        <v>380</v>
       </c>
       <c r="D73" t="s">
-        <v>138</v>
+        <v>381</v>
       </c>
       <c r="E73">
-        <v>57640</v>
+        <v>50790</v>
       </c>
       <c r="F73" t="s">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="G73" s="5">
-        <v>45963</v>
-      </c>
-      <c r="H73" s="5">
-        <v>45992</v>
+        <v>46077</v>
+      </c>
+      <c r="H73" t="s">
+        <v>358</v>
       </c>
       <c r="I73" s="5">
-        <v>46048</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="B74" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C74" t="s">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="D74" t="s">
-        <v>140</v>
+        <v>383</v>
       </c>
       <c r="E74">
-        <v>57584</v>
+        <v>50799</v>
       </c>
       <c r="F74" t="s">
-        <v>141</v>
+        <v>357</v>
       </c>
       <c r="G74" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H74" s="5">
-        <v>45976</v>
+        <v>46077</v>
+      </c>
+      <c r="H74" t="s">
+        <v>358</v>
       </c>
       <c r="I74" s="5">
-        <v>46048</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="B75" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C75" t="s">
-        <v>142</v>
+        <v>384</v>
       </c>
       <c r="D75" t="s">
-        <v>143</v>
+        <v>385</v>
       </c>
       <c r="E75">
-        <v>57585</v>
+        <v>50803</v>
       </c>
       <c r="F75" t="s">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="G75" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H75" s="5">
-        <v>45976</v>
+        <v>46077</v>
+      </c>
+      <c r="H75" t="s">
+        <v>358</v>
       </c>
       <c r="I75" s="5">
-        <v>46048</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="B76" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C76" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="D76" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="E76">
-        <v>57586</v>
+        <v>50812</v>
       </c>
       <c r="F76" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G76" s="5">
-        <v>45951</v>
+        <v>46028</v>
       </c>
       <c r="H76" s="5">
-        <v>45976</v>
+        <v>46047</v>
       </c>
       <c r="I76" s="5">
-        <v>46048</v>
+        <v>46028</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B77" t="s">
-        <v>131</v>
+        <v>440</v>
       </c>
       <c r="C77" t="s">
-        <v>146</v>
+        <v>441</v>
       </c>
       <c r="D77" t="s">
-        <v>147</v>
+        <v>442</v>
       </c>
       <c r="E77">
-        <v>57587</v>
+        <v>53490</v>
       </c>
       <c r="F77" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G77" s="5">
-        <v>45951</v>
+        <v>46091</v>
       </c>
       <c r="H77" s="5">
-        <v>45976</v>
+        <v>46096</v>
       </c>
       <c r="I77" s="5">
-        <v>46048</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B78" t="s">
-        <v>308</v>
+        <v>440</v>
       </c>
       <c r="C78" t="s">
-        <v>309</v>
+        <v>443</v>
       </c>
       <c r="D78" t="s">
-        <v>310</v>
+        <v>444</v>
       </c>
       <c r="E78">
-        <v>57777</v>
+        <v>54546</v>
       </c>
       <c r="F78" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G78" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H78" t="s">
-        <v>65</v>
+        <v>46091</v>
+      </c>
+      <c r="H78" s="5">
+        <v>46096</v>
       </c>
       <c r="I78" s="5">
-        <v>46055</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B79" t="s">
-        <v>308</v>
+        <v>122</v>
       </c>
       <c r="C79" t="s">
-        <v>311</v>
+        <v>123</v>
       </c>
       <c r="D79" t="s">
-        <v>312</v>
+        <v>124</v>
       </c>
       <c r="E79">
-        <v>57778</v>
+        <v>57692</v>
       </c>
       <c r="F79" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G79" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H79" t="s">
-        <v>65</v>
+        <v>45987</v>
+      </c>
+      <c r="H79" s="5">
+        <v>46006</v>
       </c>
       <c r="I79" s="5">
-        <v>46055</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>308</v>
+        <v>122</v>
       </c>
       <c r="C80" t="s">
-        <v>313</v>
+        <v>125</v>
       </c>
       <c r="D80" t="s">
-        <v>314</v>
+        <v>126</v>
       </c>
       <c r="E80">
-        <v>57775</v>
+        <v>57693</v>
       </c>
       <c r="F80" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G80" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H80" t="s">
-        <v>65</v>
+        <v>45987</v>
+      </c>
+      <c r="H80" s="5">
+        <v>46006</v>
       </c>
       <c r="I80" s="5">
-        <v>46055</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>308</v>
+        <v>122</v>
       </c>
       <c r="C81" t="s">
-        <v>315</v>
+        <v>127</v>
       </c>
       <c r="D81" t="s">
-        <v>316</v>
+        <v>128</v>
       </c>
       <c r="E81">
-        <v>57776</v>
+        <v>57694</v>
       </c>
       <c r="F81" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G81" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H81" t="s">
-        <v>65</v>
+        <v>45987</v>
+      </c>
+      <c r="H81" s="5">
+        <v>46006</v>
       </c>
       <c r="I81" s="5">
-        <v>46055</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B82" t="s">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="C82" t="s">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="D82" t="s">
-        <v>319</v>
+        <v>81</v>
       </c>
       <c r="E82">
-        <v>57782</v>
+        <v>57684</v>
       </c>
       <c r="F82" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G82" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H82" t="s">
-        <v>65</v>
+        <v>45975</v>
+      </c>
+      <c r="H82" s="5">
+        <v>45992</v>
       </c>
       <c r="I82" s="5">
-        <v>46055</v>
+        <v>46035</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B83" t="s">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="C83" t="s">
-        <v>320</v>
+        <v>129</v>
       </c>
       <c r="D83" t="s">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="E83">
-        <v>57780</v>
+        <v>57696</v>
       </c>
       <c r="F83" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G83" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H83" t="s">
-        <v>65</v>
+        <v>45989</v>
+      </c>
+      <c r="H83" s="5">
+        <v>46006</v>
       </c>
       <c r="I83" s="5">
-        <v>46055</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B84" t="s">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="C84" t="s">
-        <v>386</v>
+        <v>129</v>
       </c>
       <c r="D84" t="s">
-        <v>387</v>
+        <v>130</v>
       </c>
       <c r="E84">
-        <v>57703</v>
+        <v>57696</v>
       </c>
       <c r="F84" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G84" s="5">
-        <v>45993</v>
+        <v>46059</v>
       </c>
       <c r="H84" s="5">
-        <v>46023</v>
+        <v>46062</v>
       </c>
       <c r="I84" s="5">
-        <v>46070</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -4784,28 +5045,28 @@
         <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>148</v>
+        <v>35</v>
       </c>
       <c r="C85" t="s">
-        <v>149</v>
+        <v>445</v>
       </c>
       <c r="D85" t="s">
-        <v>150</v>
+        <v>446</v>
       </c>
       <c r="E85">
-        <v>57781</v>
+        <v>57746</v>
       </c>
       <c r="F85" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="G85" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H85" t="s">
-        <v>65</v>
+        <v>46020</v>
+      </c>
+      <c r="H85" s="5">
+        <v>46037</v>
       </c>
       <c r="I85" s="5">
-        <v>46052</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -4813,16 +5074,16 @@
         <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C86" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="D86" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="E86">
-        <v>57618</v>
+        <v>57616</v>
       </c>
       <c r="F86" t="s">
         <v>10</v>
@@ -4834,7 +5095,7 @@
         <v>45976</v>
       </c>
       <c r="I86" s="5">
-        <v>46070</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -4842,28 +5103,28 @@
         <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="C87" t="s">
-        <v>322</v>
+        <v>133</v>
       </c>
       <c r="D87" t="s">
-        <v>323</v>
+        <v>134</v>
       </c>
       <c r="E87">
-        <v>55992</v>
+        <v>57588</v>
       </c>
       <c r="F87" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="G87" s="5">
-        <v>46057</v>
+        <v>45951</v>
       </c>
       <c r="H87" s="5">
-        <v>46062</v>
+        <v>45976</v>
       </c>
       <c r="I87" s="5">
-        <v>46057</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -4871,28 +5132,28 @@
         <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="C88" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="D88" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="E88">
-        <v>57641</v>
+        <v>57589</v>
       </c>
       <c r="F88" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G88" s="5">
-        <v>45963</v>
+        <v>45951</v>
       </c>
       <c r="H88" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I88" s="5">
-        <v>46042</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -4900,28 +5161,28 @@
         <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="C89" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D89" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="E89">
-        <v>57645</v>
+        <v>57640</v>
       </c>
       <c r="F89" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="5">
-        <v>45964</v>
+        <v>45963</v>
       </c>
       <c r="H89" s="5">
         <v>45992</v>
       </c>
       <c r="I89" s="5">
-        <v>46042</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -4929,25 +5190,25 @@
         <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C90" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="D90" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="E90">
-        <v>57646</v>
+        <v>57584</v>
       </c>
       <c r="F90" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="G90" s="5">
-        <v>45964</v>
+        <v>45951</v>
       </c>
       <c r="H90" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I90" s="5">
         <v>46048</v>
@@ -4958,25 +5219,25 @@
         <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C91" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D91" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="E91">
-        <v>57647</v>
+        <v>57585</v>
       </c>
       <c r="F91" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G91" s="5">
-        <v>45964</v>
+        <v>45951</v>
       </c>
       <c r="H91" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I91" s="5">
         <v>46048</v>
@@ -4987,25 +5248,25 @@
         <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C92" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D92" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="E92">
-        <v>57648</v>
+        <v>57586</v>
       </c>
       <c r="F92" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G92" s="5">
-        <v>45964</v>
+        <v>45951</v>
       </c>
       <c r="H92" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I92" s="5">
         <v>46048</v>
@@ -5016,28 +5277,28 @@
         <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="C93" t="s">
-        <v>324</v>
+        <v>146</v>
       </c>
       <c r="D93" t="s">
-        <v>325</v>
+        <v>147</v>
       </c>
       <c r="E93">
-        <v>56446</v>
+        <v>57587</v>
       </c>
       <c r="F93" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="G93" s="5">
-        <v>46038</v>
+        <v>45951</v>
       </c>
       <c r="H93" s="5">
-        <v>46055</v>
+        <v>45976</v>
       </c>
       <c r="I93" s="5">
-        <v>46038</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -5045,28 +5306,28 @@
         <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>167</v>
+        <v>308</v>
       </c>
       <c r="C94" t="s">
-        <v>168</v>
+        <v>309</v>
       </c>
       <c r="D94" t="s">
-        <v>169</v>
+        <v>310</v>
       </c>
       <c r="E94">
-        <v>57652</v>
+        <v>57777</v>
       </c>
       <c r="F94" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G94" s="5">
-        <v>45964</v>
-      </c>
-      <c r="H94" s="5">
-        <v>45992</v>
+        <v>46049</v>
+      </c>
+      <c r="H94" t="s">
+        <v>65</v>
       </c>
       <c r="I94" s="5">
-        <v>46042</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -5074,28 +5335,28 @@
         <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>167</v>
+        <v>308</v>
       </c>
       <c r="C95" t="s">
-        <v>170</v>
+        <v>311</v>
       </c>
       <c r="D95" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
       <c r="E95">
-        <v>57653</v>
+        <v>57778</v>
       </c>
       <c r="F95" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="G95" s="5">
-        <v>45964</v>
-      </c>
-      <c r="H95" s="5">
-        <v>45992</v>
+        <v>46049</v>
+      </c>
+      <c r="H95" t="s">
+        <v>65</v>
       </c>
       <c r="I95" s="5">
-        <v>46042</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -5103,28 +5364,28 @@
         <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>167</v>
+        <v>308</v>
       </c>
       <c r="C96" t="s">
-        <v>172</v>
+        <v>313</v>
       </c>
       <c r="D96" t="s">
-        <v>173</v>
+        <v>314</v>
       </c>
       <c r="E96">
-        <v>57579</v>
+        <v>57775</v>
       </c>
       <c r="F96" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G96" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H96" s="5">
-        <v>45976</v>
+        <v>46049</v>
+      </c>
+      <c r="H96" t="s">
+        <v>65</v>
       </c>
       <c r="I96" s="5">
-        <v>46042</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -5132,28 +5393,28 @@
         <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>388</v>
+        <v>308</v>
       </c>
       <c r="C97" t="s">
-        <v>389</v>
+        <v>315</v>
       </c>
       <c r="D97" t="s">
-        <v>390</v>
+        <v>316</v>
       </c>
       <c r="E97">
-        <v>57659</v>
+        <v>57776</v>
       </c>
       <c r="F97" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G97" s="5">
-        <v>45964</v>
-      </c>
-      <c r="H97" s="5">
-        <v>45992</v>
+        <v>46049</v>
+      </c>
+      <c r="H97" t="s">
+        <v>65</v>
       </c>
       <c r="I97" s="5">
-        <v>46078</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -5161,28 +5422,28 @@
         <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>174</v>
+        <v>317</v>
       </c>
       <c r="C98" t="s">
-        <v>175</v>
+        <v>318</v>
       </c>
       <c r="D98" t="s">
-        <v>176</v>
+        <v>319</v>
       </c>
       <c r="E98">
-        <v>57238</v>
+        <v>57782</v>
       </c>
       <c r="F98" t="s">
-        <v>141</v>
+        <v>64</v>
       </c>
       <c r="G98" s="5">
-        <v>45817</v>
-      </c>
-      <c r="H98" s="5">
-        <v>45839</v>
+        <v>46049</v>
+      </c>
+      <c r="H98" t="s">
+        <v>65</v>
       </c>
       <c r="I98" s="5">
-        <v>46048</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -5190,28 +5451,28 @@
         <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="C99" t="s">
-        <v>175</v>
+        <v>320</v>
       </c>
       <c r="D99" t="s">
-        <v>176</v>
+        <v>321</v>
       </c>
       <c r="E99">
-        <v>57238</v>
+        <v>57780</v>
       </c>
       <c r="F99" t="s">
-        <v>177</v>
+        <v>64</v>
       </c>
       <c r="G99" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H99" s="5">
-        <v>45976</v>
+        <v>46049</v>
+      </c>
+      <c r="H99" t="s">
+        <v>65</v>
       </c>
       <c r="I99" s="5">
-        <v>46048</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -5219,25 +5480,25 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="C100" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D100" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E100">
-        <v>57700</v>
+        <v>57703</v>
       </c>
       <c r="F100" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="G100" s="5">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="H100" s="5">
-        <v>46006</v>
+        <v>46023</v>
       </c>
       <c r="I100" s="5">
         <v>46070</v>
@@ -5248,28 +5509,28 @@
         <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="C101" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D101" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E101">
-        <v>57583</v>
+        <v>57781</v>
       </c>
       <c r="F101" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G101" s="5">
-        <v>45951</v>
+        <v>46083</v>
       </c>
       <c r="H101" s="5">
-        <v>45976</v>
+        <v>46096</v>
       </c>
       <c r="I101" s="5">
-        <v>46042</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -5277,28 +5538,28 @@
         <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="C102" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="D102" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="E102">
-        <v>57581</v>
+        <v>57781</v>
       </c>
       <c r="F102" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G102" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H102" s="5">
-        <v>45976</v>
+        <v>46049</v>
+      </c>
+      <c r="H102" t="s">
+        <v>65</v>
       </c>
       <c r="I102" s="5">
-        <v>46042</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -5306,28 +5567,28 @@
         <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="C103" t="s">
-        <v>389</v>
+        <v>152</v>
       </c>
       <c r="D103" t="s">
-        <v>393</v>
+        <v>153</v>
       </c>
       <c r="E103">
-        <v>57658</v>
+        <v>57618</v>
       </c>
       <c r="F103" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G103" s="5">
-        <v>45964</v>
+        <v>45954</v>
       </c>
       <c r="H103" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I103" s="5">
-        <v>46078</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -5335,28 +5596,28 @@
         <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="C104" t="s">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="D104" t="s">
-        <v>85</v>
+        <v>323</v>
       </c>
       <c r="E104">
-        <v>57736</v>
+        <v>55992</v>
       </c>
       <c r="F104" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G104" s="5">
-        <v>46007</v>
-      </c>
-      <c r="H104" t="s">
-        <v>65</v>
+        <v>46057</v>
+      </c>
+      <c r="H104" s="5">
+        <v>46062</v>
       </c>
       <c r="I104" s="5">
-        <v>46027</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -5364,19 +5625,19 @@
         <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="C105" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="D105" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="E105">
-        <v>57642</v>
+        <v>57641</v>
       </c>
       <c r="F105" t="s">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="G105" s="5">
         <v>45963</v>
@@ -5385,7 +5646,7 @@
         <v>45992</v>
       </c>
       <c r="I105" s="5">
-        <v>46048</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -5393,16 +5654,16 @@
         <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="C106" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="D106" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="E106">
-        <v>57655</v>
+        <v>57645</v>
       </c>
       <c r="F106" t="s">
         <v>10</v>
@@ -5414,7 +5675,7 @@
         <v>45992</v>
       </c>
       <c r="I106" s="5">
-        <v>46048</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -5422,28 +5683,28 @@
         <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="C107" t="s">
-        <v>394</v>
+        <v>161</v>
       </c>
       <c r="D107" t="s">
-        <v>395</v>
+        <v>162</v>
       </c>
       <c r="E107">
-        <v>57698</v>
+        <v>57646</v>
       </c>
       <c r="F107" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="5">
+        <v>45964</v>
+      </c>
+      <c r="H107" s="5">
         <v>45992</v>
       </c>
-      <c r="H107" s="5">
-        <v>46006</v>
-      </c>
       <c r="I107" s="5">
-        <v>46070</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
@@ -5451,25 +5712,25 @@
         <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="C108" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="D108" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="E108">
-        <v>57582</v>
+        <v>57647</v>
       </c>
       <c r="F108" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="G108" s="5">
-        <v>45951</v>
+        <v>45964</v>
       </c>
       <c r="H108" s="5">
-        <v>45976</v>
+        <v>45992</v>
       </c>
       <c r="I108" s="5">
         <v>46048</v>
@@ -5480,16 +5741,16 @@
         <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="C109" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="D109" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="E109">
-        <v>57654</v>
+        <v>57648</v>
       </c>
       <c r="F109" t="s">
         <v>10</v>
@@ -5509,28 +5770,28 @@
         <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C110" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D110" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E110">
-        <v>57779</v>
+        <v>56446</v>
       </c>
       <c r="F110" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G110" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H110" t="s">
-        <v>65</v>
+        <v>46038</v>
+      </c>
+      <c r="H110" s="5">
+        <v>46055</v>
       </c>
       <c r="I110" s="5">
-        <v>46055</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -5538,1733 +5799,1733 @@
         <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>396</v>
+        <v>167</v>
       </c>
       <c r="C111" t="s">
-        <v>397</v>
+        <v>168</v>
       </c>
       <c r="D111" t="s">
-        <v>398</v>
+        <v>169</v>
       </c>
       <c r="E111">
-        <v>56119</v>
+        <v>57652</v>
       </c>
       <c r="F111" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G111" s="5">
-        <v>46070</v>
+        <v>45964</v>
       </c>
       <c r="H111" s="5">
-        <v>46072</v>
+        <v>45992</v>
       </c>
       <c r="I111" s="5">
-        <v>46070</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="C112" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="D112" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="E112">
-        <v>57407</v>
+        <v>57653</v>
       </c>
       <c r="F112" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G112" s="5">
-        <v>46029</v>
+        <v>45964</v>
       </c>
       <c r="H112" s="5">
-        <v>46047</v>
+        <v>45992</v>
       </c>
       <c r="I112" s="5">
-        <v>46029</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="C113" t="s">
-        <v>87</v>
+        <v>172</v>
       </c>
       <c r="D113" t="s">
-        <v>88</v>
+        <v>173</v>
       </c>
       <c r="E113">
-        <v>57682</v>
+        <v>57579</v>
       </c>
       <c r="F113" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G113" s="5">
-        <v>45975</v>
+        <v>45951</v>
       </c>
       <c r="H113" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I113" s="5">
-        <v>46036</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>35</v>
+        <v>388</v>
       </c>
       <c r="C114" t="s">
-        <v>194</v>
+        <v>447</v>
       </c>
       <c r="D114" t="s">
-        <v>195</v>
+        <v>448</v>
       </c>
       <c r="E114">
-        <v>57406</v>
+        <v>56879</v>
       </c>
       <c r="F114" t="s">
         <v>107</v>
       </c>
       <c r="G114" s="5">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="H114" s="5">
-        <v>46047</v>
+        <v>46096</v>
       </c>
       <c r="I114" s="5">
-        <v>46029</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>35</v>
+        <v>388</v>
       </c>
       <c r="C115" t="s">
-        <v>194</v>
+        <v>389</v>
       </c>
       <c r="D115" t="s">
-        <v>195</v>
+        <v>390</v>
       </c>
       <c r="E115">
-        <v>57784</v>
+        <v>57659</v>
       </c>
       <c r="F115" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G115" s="5">
-        <v>46050</v>
-      </c>
-      <c r="H115" t="s">
-        <v>65</v>
+        <v>45964</v>
+      </c>
+      <c r="H115" s="5">
+        <v>45992</v>
       </c>
       <c r="I115" s="5">
-        <v>46055</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
       <c r="C116" t="s">
-        <v>89</v>
+        <v>449</v>
       </c>
       <c r="D116" t="s">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="E116">
-        <v>57683</v>
+        <v>55922</v>
       </c>
       <c r="F116" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G116" s="5">
-        <v>45975</v>
+        <v>46083</v>
       </c>
       <c r="H116" s="5">
-        <v>45992</v>
+        <v>46096</v>
       </c>
       <c r="I116" s="5">
-        <v>46036</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
       <c r="C117" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="D117" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="E117">
-        <v>57681</v>
+        <v>57238</v>
       </c>
       <c r="F117" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="G117" s="5">
-        <v>45975</v>
+        <v>45817</v>
       </c>
       <c r="H117" s="5">
-        <v>45992</v>
+        <v>45839</v>
       </c>
       <c r="I117" s="5">
-        <v>46036</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>328</v>
+        <v>174</v>
       </c>
       <c r="C118" t="s">
-        <v>329</v>
+        <v>175</v>
       </c>
       <c r="D118" t="s">
-        <v>330</v>
+        <v>176</v>
       </c>
       <c r="E118">
-        <v>57772</v>
+        <v>57238</v>
       </c>
       <c r="F118" t="s">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="G118" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H118" t="s">
-        <v>65</v>
+        <v>45951</v>
+      </c>
+      <c r="H118" s="5">
+        <v>45976</v>
       </c>
       <c r="I118" s="5">
-        <v>46055</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>328</v>
+        <v>178</v>
       </c>
       <c r="C119" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="D119" t="s">
-        <v>332</v>
+        <v>392</v>
       </c>
       <c r="E119">
-        <v>57773</v>
+        <v>57700</v>
       </c>
       <c r="F119" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="G119" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H119" t="s">
-        <v>65</v>
+        <v>45992</v>
+      </c>
+      <c r="H119" s="5">
+        <v>46006</v>
       </c>
       <c r="I119" s="5">
-        <v>46055</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>328</v>
+        <v>178</v>
       </c>
       <c r="C120" t="s">
-        <v>333</v>
+        <v>179</v>
       </c>
       <c r="D120" t="s">
-        <v>334</v>
+        <v>180</v>
       </c>
       <c r="E120">
-        <v>57774</v>
+        <v>57583</v>
       </c>
       <c r="F120" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G120" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H120" t="s">
-        <v>65</v>
+        <v>45951</v>
+      </c>
+      <c r="H120" s="5">
+        <v>45976</v>
       </c>
       <c r="I120" s="5">
-        <v>46055</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B121" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="C121" t="s">
-        <v>335</v>
+        <v>181</v>
       </c>
       <c r="D121" t="s">
-        <v>336</v>
+        <v>182</v>
       </c>
       <c r="E121">
-        <v>53987</v>
+        <v>57581</v>
       </c>
       <c r="F121" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G121" s="5">
-        <v>46059</v>
+        <v>45951</v>
       </c>
       <c r="H121" s="5">
-        <v>46062</v>
+        <v>45976</v>
       </c>
       <c r="I121" s="5">
-        <v>46059</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="C122" t="s">
-        <v>337</v>
+        <v>389</v>
       </c>
       <c r="D122" t="s">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="E122">
-        <v>55109</v>
+        <v>57658</v>
       </c>
       <c r="F122" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G122" s="5">
-        <v>46059</v>
+        <v>45964</v>
       </c>
       <c r="H122" s="5">
-        <v>46062</v>
+        <v>45992</v>
       </c>
       <c r="I122" s="5">
-        <v>46059</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C123" t="s">
-        <v>339</v>
+        <v>84</v>
       </c>
       <c r="D123" t="s">
-        <v>340</v>
+        <v>85</v>
       </c>
       <c r="E123">
-        <v>56415</v>
+        <v>57736</v>
       </c>
       <c r="F123" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G123" s="5">
-        <v>46059</v>
-      </c>
-      <c r="H123" s="5">
-        <v>46062</v>
+        <v>46007</v>
+      </c>
+      <c r="H123" t="s">
+        <v>65</v>
       </c>
       <c r="I123" s="5">
-        <v>46059</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B124" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C124" t="s">
-        <v>341</v>
+        <v>451</v>
       </c>
       <c r="D124" t="s">
-        <v>342</v>
+        <v>452</v>
       </c>
       <c r="E124">
-        <v>57704</v>
+        <v>57440</v>
       </c>
       <c r="F124" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G124" s="5">
-        <v>45995</v>
+        <v>46083</v>
       </c>
       <c r="H124" s="5">
-        <v>46023</v>
+        <v>46096</v>
       </c>
       <c r="I124" s="5">
-        <v>46062</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C125" t="s">
-        <v>196</v>
+        <v>453</v>
       </c>
       <c r="D125" t="s">
-        <v>197</v>
+        <v>454</v>
       </c>
       <c r="E125">
-        <v>55810</v>
+        <v>57829</v>
       </c>
       <c r="F125" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G125" s="5">
-        <v>46029</v>
-      </c>
-      <c r="H125" s="5">
-        <v>46047</v>
+        <v>46083</v>
+      </c>
+      <c r="H125" t="s">
+        <v>65</v>
       </c>
       <c r="I125" s="5">
-        <v>46029</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C126" t="s">
-        <v>36</v>
+        <v>455</v>
       </c>
       <c r="D126" t="s">
-        <v>37</v>
+        <v>456</v>
       </c>
       <c r="E126">
-        <v>57626</v>
+        <v>57830</v>
       </c>
       <c r="F126" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G126" s="5">
-        <v>45958</v>
-      </c>
-      <c r="H126" s="5">
-        <v>45976</v>
+        <v>46083</v>
+      </c>
+      <c r="H126" t="s">
+        <v>65</v>
       </c>
       <c r="I126" s="5">
-        <v>46023</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C127" t="s">
-        <v>343</v>
+        <v>457</v>
       </c>
       <c r="D127" t="s">
-        <v>344</v>
+        <v>458</v>
       </c>
       <c r="E127">
-        <v>56750</v>
+        <v>55583</v>
       </c>
       <c r="F127" t="s">
         <v>107</v>
       </c>
       <c r="G127" s="5">
-        <v>46059</v>
+        <v>46083</v>
       </c>
       <c r="H127" s="5">
-        <v>46062</v>
+        <v>46096</v>
       </c>
       <c r="I127" s="5">
-        <v>46059</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="C128" t="s">
-        <v>399</v>
+        <v>184</v>
       </c>
       <c r="D128" t="s">
-        <v>400</v>
+        <v>185</v>
       </c>
       <c r="E128">
-        <v>57607</v>
+        <v>57642</v>
       </c>
       <c r="F128" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="G128" s="5">
-        <v>45952</v>
+        <v>45963</v>
       </c>
       <c r="H128" s="5">
-        <v>45976</v>
+        <v>45992</v>
       </c>
       <c r="I128" s="5">
-        <v>46071</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="C129" t="s">
-        <v>399</v>
+        <v>186</v>
       </c>
       <c r="D129" t="s">
-        <v>400</v>
+        <v>187</v>
       </c>
       <c r="E129">
-        <v>57607</v>
+        <v>57655</v>
       </c>
       <c r="F129" t="s">
-        <v>401</v>
+        <v>10</v>
       </c>
       <c r="G129" s="5">
-        <v>46009</v>
+        <v>45964</v>
       </c>
       <c r="H129" s="5">
-        <v>46037</v>
+        <v>45992</v>
       </c>
       <c r="I129" s="5">
-        <v>46071</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="C130" t="s">
-        <v>345</v>
+        <v>394</v>
       </c>
       <c r="D130" t="s">
-        <v>346</v>
+        <v>395</v>
       </c>
       <c r="E130">
-        <v>54040</v>
+        <v>57698</v>
       </c>
       <c r="F130" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G130" s="5">
-        <v>46062</v>
+        <v>45992</v>
       </c>
       <c r="H130" s="5">
-        <v>46066</v>
+        <v>46006</v>
       </c>
       <c r="I130" s="5">
-        <v>46062</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="C131" t="s">
-        <v>94</v>
+        <v>188</v>
       </c>
       <c r="D131" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E131">
-        <v>57685</v>
+        <v>57582</v>
       </c>
       <c r="F131" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="G131" s="5">
-        <v>45975</v>
+        <v>45951</v>
       </c>
       <c r="H131" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I131" s="5">
-        <v>46029</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="C132" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D132" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E132">
-        <v>51497</v>
+        <v>57654</v>
       </c>
       <c r="F132" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G132" s="5">
-        <v>46030</v>
+        <v>45964</v>
       </c>
       <c r="H132" s="5">
-        <v>46047</v>
+        <v>45992</v>
       </c>
       <c r="I132" s="5">
-        <v>46030</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B133" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="C133" t="s">
-        <v>202</v>
+        <v>326</v>
       </c>
       <c r="D133" t="s">
-        <v>203</v>
+        <v>327</v>
       </c>
       <c r="E133">
-        <v>51493</v>
+        <v>57779</v>
       </c>
       <c r="F133" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G133" s="5">
-        <v>46030</v>
-      </c>
-      <c r="H133" s="5">
-        <v>46047</v>
+        <v>46049</v>
+      </c>
+      <c r="H133" t="s">
+        <v>65</v>
       </c>
       <c r="I133" s="5">
-        <v>46030</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>201</v>
+        <v>396</v>
       </c>
       <c r="C134" t="s">
-        <v>204</v>
+        <v>397</v>
       </c>
       <c r="D134" t="s">
-        <v>205</v>
+        <v>398</v>
       </c>
       <c r="E134">
-        <v>51495</v>
+        <v>56119</v>
       </c>
       <c r="F134" t="s">
         <v>107</v>
       </c>
       <c r="G134" s="5">
-        <v>46030</v>
+        <v>46070</v>
       </c>
       <c r="H134" s="5">
-        <v>46047</v>
+        <v>46072</v>
       </c>
       <c r="I134" s="5">
-        <v>46030</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B135" t="s">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="C135" t="s">
-        <v>206</v>
+        <v>459</v>
       </c>
       <c r="D135" t="s">
-        <v>207</v>
+        <v>460</v>
       </c>
       <c r="E135">
-        <v>51496</v>
+        <v>57840</v>
       </c>
       <c r="F135" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G135" s="5">
-        <v>46030</v>
-      </c>
-      <c r="H135" s="5">
-        <v>46047</v>
+        <v>46086</v>
+      </c>
+      <c r="H135" t="s">
+        <v>65</v>
       </c>
       <c r="I135" s="5">
-        <v>46030</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B136" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C136" t="s">
-        <v>40</v>
+        <v>461</v>
       </c>
       <c r="D136" t="s">
-        <v>41</v>
+        <v>462</v>
       </c>
       <c r="E136">
-        <v>57619</v>
+        <v>57841</v>
       </c>
       <c r="F136" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G136" s="5">
-        <v>45957</v>
-      </c>
-      <c r="H136" s="5">
-        <v>45976</v>
+        <v>46086</v>
+      </c>
+      <c r="H136" t="s">
+        <v>65</v>
       </c>
       <c r="I136" s="5">
-        <v>46023</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B137" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C137" t="s">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="D137" t="s">
-        <v>41</v>
+        <v>193</v>
       </c>
       <c r="E137">
-        <v>57620</v>
+        <v>57407</v>
       </c>
       <c r="F137" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G137" s="5">
-        <v>45957</v>
+        <v>46029</v>
       </c>
       <c r="H137" s="5">
-        <v>45976</v>
+        <v>46047</v>
       </c>
       <c r="I137" s="5">
-        <v>46023</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B138" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C138" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D138" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="E138">
-        <v>57625</v>
+        <v>57682</v>
       </c>
       <c r="F138" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G138" s="5">
-        <v>45958</v>
+        <v>45975</v>
       </c>
       <c r="H138" s="5">
-        <v>45976</v>
+        <v>45992</v>
       </c>
       <c r="I138" s="5">
-        <v>46023</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B139" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C139" t="s">
-        <v>40</v>
+        <v>463</v>
       </c>
       <c r="D139" t="s">
-        <v>41</v>
+        <v>464</v>
       </c>
       <c r="E139">
-        <v>57637</v>
+        <v>57842</v>
       </c>
       <c r="F139" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G139" s="5">
-        <v>45961</v>
-      </c>
-      <c r="H139" s="5">
-        <v>45976</v>
+        <v>46087</v>
+      </c>
+      <c r="H139" t="s">
+        <v>65</v>
       </c>
       <c r="I139" s="5">
-        <v>46023</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B140" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C140" t="s">
-        <v>42</v>
+        <v>465</v>
       </c>
       <c r="D140" t="s">
-        <v>43</v>
+        <v>466</v>
       </c>
       <c r="E140">
-        <v>57621</v>
+        <v>57845</v>
       </c>
       <c r="F140" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G140" s="5">
-        <v>45957</v>
-      </c>
-      <c r="H140" s="5">
-        <v>45976</v>
+        <v>46087</v>
+      </c>
+      <c r="H140" t="s">
+        <v>65</v>
       </c>
       <c r="I140" s="5">
-        <v>46023</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>208</v>
+        <v>86</v>
       </c>
       <c r="B141" t="s">
-        <v>209</v>
+        <v>35</v>
       </c>
       <c r="C141" t="s">
-        <v>210</v>
+        <v>467</v>
       </c>
       <c r="D141" t="s">
-        <v>211</v>
+        <v>468</v>
       </c>
       <c r="E141">
-        <v>57701</v>
+        <v>57524</v>
       </c>
       <c r="F141" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G141" s="5">
-        <v>45992</v>
+        <v>46086</v>
       </c>
       <c r="H141" s="5">
-        <v>46006</v>
+        <v>46096</v>
       </c>
       <c r="I141" s="5">
-        <v>46043</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>347</v>
+        <v>86</v>
       </c>
       <c r="B142" t="s">
         <v>35</v>
       </c>
       <c r="C142" t="s">
-        <v>348</v>
+        <v>467</v>
       </c>
       <c r="D142" t="s">
-        <v>349</v>
+        <v>468</v>
       </c>
       <c r="E142">
-        <v>57490</v>
+        <v>57847</v>
       </c>
       <c r="F142" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G142" s="5">
-        <v>46048</v>
-      </c>
-      <c r="H142" s="5">
-        <v>46055</v>
+        <v>46087</v>
+      </c>
+      <c r="H142" t="s">
+        <v>65</v>
       </c>
       <c r="I142" s="5">
-        <v>46048</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>347</v>
+        <v>86</v>
       </c>
       <c r="B143" t="s">
         <v>35</v>
       </c>
       <c r="C143" t="s">
-        <v>350</v>
+        <v>469</v>
       </c>
       <c r="D143" t="s">
-        <v>351</v>
+        <v>470</v>
       </c>
       <c r="E143">
-        <v>51528</v>
+        <v>57843</v>
       </c>
       <c r="F143" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G143" s="5">
-        <v>46048</v>
-      </c>
-      <c r="H143" s="5">
-        <v>46055</v>
+        <v>46087</v>
+      </c>
+      <c r="H143" t="s">
+        <v>65</v>
       </c>
       <c r="I143" s="5">
-        <v>46048</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>347</v>
+        <v>86</v>
       </c>
       <c r="B144" t="s">
         <v>35</v>
       </c>
       <c r="C144" t="s">
-        <v>352</v>
+        <v>194</v>
       </c>
       <c r="D144" t="s">
-        <v>353</v>
+        <v>195</v>
       </c>
       <c r="E144">
-        <v>51522</v>
+        <v>57406</v>
       </c>
       <c r="F144" t="s">
         <v>107</v>
       </c>
       <c r="G144" s="5">
-        <v>46048</v>
+        <v>46029</v>
       </c>
       <c r="H144" s="5">
-        <v>46055</v>
+        <v>46047</v>
       </c>
       <c r="I144" s="5">
-        <v>46048</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B145" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C145" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D145" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="E145">
-        <v>56438</v>
+        <v>57784</v>
       </c>
       <c r="F145" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G145" s="5">
-        <v>46030</v>
-      </c>
-      <c r="H145" s="5">
-        <v>46047</v>
+        <v>46050</v>
+      </c>
+      <c r="H145" t="s">
+        <v>65</v>
       </c>
       <c r="I145" s="5">
-        <v>46030</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B146" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C146" t="s">
-        <v>402</v>
+        <v>471</v>
       </c>
       <c r="D146" t="s">
-        <v>403</v>
+        <v>472</v>
       </c>
       <c r="E146">
-        <v>57743</v>
+        <v>57844</v>
       </c>
       <c r="F146" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="G146" s="5">
-        <v>46013</v>
-      </c>
-      <c r="H146" s="5">
-        <v>46037</v>
+        <v>46087</v>
+      </c>
+      <c r="H146" t="s">
+        <v>65</v>
       </c>
       <c r="I146" s="5">
-        <v>46077</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B147" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C147" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D147" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E147">
-        <v>57671</v>
+        <v>57683</v>
       </c>
       <c r="F147" t="s">
         <v>10</v>
       </c>
       <c r="G147" s="5">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="H147" s="5">
         <v>45992</v>
       </c>
       <c r="I147" s="5">
-        <v>46029</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B148" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C148" t="s">
-        <v>214</v>
+        <v>473</v>
       </c>
       <c r="D148" t="s">
-        <v>215</v>
+        <v>474</v>
       </c>
       <c r="E148">
-        <v>51696</v>
+        <v>57846</v>
       </c>
       <c r="F148" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G148" s="5">
-        <v>46029</v>
-      </c>
-      <c r="H148" s="5">
-        <v>46047</v>
+        <v>46087</v>
+      </c>
+      <c r="H148" t="s">
+        <v>65</v>
       </c>
       <c r="I148" s="5">
-        <v>46029</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B149" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C149" t="s">
-        <v>216</v>
+        <v>91</v>
       </c>
       <c r="D149" t="s">
-        <v>217</v>
+        <v>92</v>
       </c>
       <c r="E149">
-        <v>51693</v>
+        <v>57681</v>
       </c>
       <c r="F149" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G149" s="5">
-        <v>46029</v>
+        <v>45975</v>
       </c>
       <c r="H149" s="5">
-        <v>46047</v>
+        <v>45992</v>
       </c>
       <c r="I149" s="5">
-        <v>46029</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B150" t="s">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="C150" t="s">
-        <v>218</v>
+        <v>329</v>
       </c>
       <c r="D150" t="s">
-        <v>219</v>
+        <v>330</v>
       </c>
       <c r="E150">
-        <v>51697</v>
+        <v>57772</v>
       </c>
       <c r="F150" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G150" s="5">
-        <v>46029</v>
-      </c>
-      <c r="H150" s="5">
-        <v>46047</v>
+        <v>46049</v>
+      </c>
+      <c r="H150" t="s">
+        <v>65</v>
       </c>
       <c r="I150" s="5">
-        <v>46029</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B151" t="s">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="C151" t="s">
-        <v>220</v>
+        <v>331</v>
       </c>
       <c r="D151" t="s">
-        <v>221</v>
+        <v>332</v>
       </c>
       <c r="E151">
-        <v>51687</v>
+        <v>57773</v>
       </c>
       <c r="F151" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G151" s="5">
-        <v>46030</v>
-      </c>
-      <c r="H151" s="5">
-        <v>46047</v>
+        <v>46049</v>
+      </c>
+      <c r="H151" t="s">
+        <v>65</v>
       </c>
       <c r="I151" s="5">
-        <v>46030</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B152" t="s">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="C152" t="s">
-        <v>220</v>
+        <v>333</v>
       </c>
       <c r="D152" t="s">
-        <v>221</v>
+        <v>334</v>
       </c>
       <c r="E152">
-        <v>57756</v>
+        <v>57774</v>
       </c>
       <c r="F152" t="s">
         <v>64</v>
       </c>
       <c r="G152" s="5">
-        <v>46029</v>
+        <v>46049</v>
       </c>
       <c r="H152" t="s">
         <v>65</v>
       </c>
       <c r="I152" s="5">
-        <v>46047</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B153" t="s">
-        <v>354</v>
+        <v>35</v>
       </c>
       <c r="C153" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="D153" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="E153">
-        <v>53634</v>
+        <v>53987</v>
       </c>
       <c r="F153" t="s">
-        <v>357</v>
+        <v>107</v>
       </c>
       <c r="G153" s="5">
-        <v>46063</v>
-      </c>
-      <c r="H153" t="s">
-        <v>358</v>
+        <v>46059</v>
+      </c>
+      <c r="H153" s="5">
+        <v>46062</v>
       </c>
       <c r="I153" s="5">
-        <v>46063</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B154" t="s">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="C154" t="s">
-        <v>223</v>
+        <v>337</v>
       </c>
       <c r="D154" t="s">
-        <v>224</v>
+        <v>338</v>
       </c>
       <c r="E154">
-        <v>53224</v>
+        <v>55109</v>
       </c>
       <c r="F154" t="s">
         <v>107</v>
       </c>
       <c r="G154" s="5">
-        <v>46031</v>
+        <v>46059</v>
       </c>
       <c r="H154" s="5">
-        <v>46047</v>
+        <v>46062</v>
       </c>
       <c r="I154" s="5">
-        <v>46031</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B155" t="s">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c r="C155" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="D155" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="E155">
-        <v>57708</v>
+        <v>56415</v>
       </c>
       <c r="F155" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G155" s="5">
-        <v>46001</v>
+        <v>46059</v>
       </c>
       <c r="H155" s="5">
-        <v>46023</v>
+        <v>46062</v>
       </c>
       <c r="I155" s="5">
-        <v>46063</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B156" t="s">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c r="C156" t="s">
-        <v>226</v>
+        <v>341</v>
       </c>
       <c r="D156" t="s">
-        <v>227</v>
+        <v>342</v>
       </c>
       <c r="E156">
-        <v>55787</v>
+        <v>57704</v>
       </c>
       <c r="F156" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G156" s="5">
-        <v>46027</v>
+        <v>45995</v>
       </c>
       <c r="H156" s="5">
-        <v>46047</v>
+        <v>46023</v>
       </c>
       <c r="I156" s="5">
-        <v>46027</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>361</v>
+        <v>34</v>
       </c>
       <c r="B157" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C157" t="s">
-        <v>363</v>
+        <v>196</v>
       </c>
       <c r="D157" t="s">
-        <v>364</v>
+        <v>197</v>
       </c>
       <c r="E157">
-        <v>52702</v>
+        <v>55810</v>
       </c>
       <c r="F157" t="s">
         <v>107</v>
       </c>
       <c r="G157" s="5">
-        <v>46057</v>
+        <v>46029</v>
       </c>
       <c r="H157" s="5">
-        <v>46062</v>
+        <v>46047</v>
       </c>
       <c r="I157" s="5">
-        <v>46057</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>361</v>
+        <v>34</v>
       </c>
       <c r="B158" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C158" t="s">
-        <v>365</v>
+        <v>36</v>
       </c>
       <c r="D158" t="s">
-        <v>366</v>
+        <v>37</v>
       </c>
       <c r="E158">
-        <v>51793</v>
+        <v>57626</v>
       </c>
       <c r="F158" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G158" s="5">
-        <v>46057</v>
+        <v>45958</v>
       </c>
       <c r="H158" s="5">
-        <v>46062</v>
+        <v>45976</v>
       </c>
       <c r="I158" s="5">
-        <v>46057</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>361</v>
+        <v>34</v>
       </c>
       <c r="B159" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C159" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="D159" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="E159">
-        <v>51802</v>
+        <v>56750</v>
       </c>
       <c r="F159" t="s">
         <v>107</v>
       </c>
       <c r="G159" s="5">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="H159" s="5">
         <v>46062</v>
       </c>
       <c r="I159" s="5">
-        <v>46057</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>361</v>
+        <v>34</v>
       </c>
       <c r="B160" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C160" t="s">
-        <v>369</v>
+        <v>475</v>
       </c>
       <c r="D160" t="s">
-        <v>370</v>
+        <v>476</v>
       </c>
       <c r="E160">
-        <v>51798</v>
+        <v>57006</v>
       </c>
       <c r="F160" t="s">
         <v>107</v>
       </c>
       <c r="G160" s="5">
-        <v>46057</v>
+        <v>46090</v>
       </c>
       <c r="H160" s="5">
-        <v>46062</v>
+        <v>46096</v>
       </c>
       <c r="I160" s="5">
-        <v>46057</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>361</v>
+        <v>34</v>
       </c>
       <c r="B161" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C161" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="E161">
-        <v>51799</v>
+        <v>57607</v>
       </c>
       <c r="F161" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G161" s="5">
-        <v>46076</v>
+        <v>45952</v>
       </c>
       <c r="H161" s="5">
-        <v>46082</v>
+        <v>45976</v>
       </c>
       <c r="I161" s="5">
-        <v>46076</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>361</v>
+        <v>34</v>
       </c>
       <c r="B162" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C162" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D162" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="E162">
-        <v>51800</v>
+        <v>57607</v>
       </c>
       <c r="F162" t="s">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="G162" s="5">
-        <v>46076</v>
+        <v>46009</v>
       </c>
       <c r="H162" s="5">
-        <v>46082</v>
+        <v>46037</v>
       </c>
       <c r="I162" s="5">
-        <v>46076</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>361</v>
+        <v>34</v>
       </c>
       <c r="B163" t="s">
-        <v>362</v>
+        <v>93</v>
       </c>
       <c r="C163" t="s">
-        <v>408</v>
+        <v>345</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>346</v>
       </c>
       <c r="E163">
-        <v>51803</v>
+        <v>54040</v>
       </c>
       <c r="F163" t="s">
         <v>107</v>
       </c>
       <c r="G163" s="5">
-        <v>46076</v>
+        <v>46062</v>
       </c>
       <c r="H163" s="5">
-        <v>46082</v>
+        <v>46066</v>
       </c>
       <c r="I163" s="5">
-        <v>46076</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>361</v>
+        <v>34</v>
       </c>
       <c r="B164" t="s">
-        <v>362</v>
+        <v>93</v>
       </c>
       <c r="C164" t="s">
-        <v>410</v>
+        <v>94</v>
       </c>
       <c r="D164" t="s">
-        <v>411</v>
+        <v>95</v>
       </c>
       <c r="E164">
-        <v>51807</v>
+        <v>57685</v>
       </c>
       <c r="F164" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G164" s="5">
-        <v>46076</v>
+        <v>45975</v>
       </c>
       <c r="H164" s="5">
-        <v>46082</v>
+        <v>45992</v>
       </c>
       <c r="I164" s="5">
-        <v>46076</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>361</v>
+        <v>38</v>
       </c>
       <c r="B165" t="s">
-        <v>362</v>
+        <v>198</v>
       </c>
       <c r="C165" t="s">
-        <v>371</v>
+        <v>199</v>
       </c>
       <c r="D165" t="s">
-        <v>372</v>
+        <v>200</v>
       </c>
       <c r="E165">
-        <v>52701</v>
+        <v>51497</v>
       </c>
       <c r="F165" t="s">
         <v>107</v>
       </c>
       <c r="G165" s="5">
-        <v>46057</v>
+        <v>46030</v>
       </c>
       <c r="H165" s="5">
-        <v>46062</v>
+        <v>46047</v>
       </c>
       <c r="I165" s="5">
-        <v>46057</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="B166" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="C166" t="s">
-        <v>100</v>
+        <v>202</v>
       </c>
       <c r="D166" t="s">
-        <v>101</v>
+        <v>203</v>
       </c>
       <c r="E166">
-        <v>57604</v>
+        <v>51493</v>
       </c>
       <c r="F166" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G166" s="5">
-        <v>45952</v>
+        <v>46030</v>
       </c>
       <c r="H166" s="5">
-        <v>45976</v>
+        <v>46047</v>
       </c>
       <c r="I166" s="5">
-        <v>46038</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="B167" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="C167" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="D167" t="s">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="E167">
-        <v>57606</v>
+        <v>51495</v>
       </c>
       <c r="F167" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G167" s="5">
-        <v>45952</v>
+        <v>46030</v>
       </c>
       <c r="H167" s="5">
-        <v>45976</v>
+        <v>46047</v>
       </c>
       <c r="I167" s="5">
-        <v>46038</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="B168" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="C168" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="D168" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="E168">
-        <v>57088</v>
+        <v>51496</v>
       </c>
       <c r="F168" t="s">
         <v>107</v>
       </c>
       <c r="G168" s="5">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H168" s="5">
         <v>46047</v>
       </c>
       <c r="I168" s="5">
-        <v>46029</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="B169" t="s">
-        <v>231</v>
+        <v>39</v>
       </c>
       <c r="C169" t="s">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="D169" t="s">
-        <v>233</v>
+        <v>41</v>
       </c>
       <c r="E169">
-        <v>56876</v>
+        <v>57619</v>
       </c>
       <c r="F169" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G169" s="5">
-        <v>46029</v>
+        <v>45957</v>
       </c>
       <c r="H169" s="5">
-        <v>46047</v>
+        <v>45976</v>
       </c>
       <c r="I169" s="5">
-        <v>46029</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B170" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C170" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D170" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E170">
-        <v>57639</v>
+        <v>57620</v>
       </c>
       <c r="F170" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G170" s="5">
-        <v>45961</v>
+        <v>45957</v>
       </c>
       <c r="H170" s="5">
         <v>45976</v>
@@ -7275,57 +7536,57 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B171" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C171" t="s">
-        <v>412</v>
+        <v>40</v>
       </c>
       <c r="D171" t="s">
-        <v>413</v>
+        <v>41</v>
       </c>
       <c r="E171">
-        <v>56505</v>
+        <v>57625</v>
       </c>
       <c r="F171" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G171" s="5">
-        <v>46071</v>
+        <v>45958</v>
       </c>
       <c r="H171" s="5">
-        <v>46082</v>
+        <v>45976</v>
       </c>
       <c r="I171" s="5">
-        <v>46071</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B172" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C172" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D172" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E172">
-        <v>57419</v>
+        <v>57637</v>
       </c>
       <c r="F172" t="s">
         <v>10</v>
       </c>
       <c r="G172" s="5">
-        <v>45895</v>
+        <v>45961</v>
       </c>
       <c r="H172" s="5">
-        <v>45915</v>
+        <v>45976</v>
       </c>
       <c r="I172" s="5">
         <v>46023</v>
@@ -7333,28 +7594,28 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B173" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C173" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D173" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E173">
-        <v>57420</v>
+        <v>57621</v>
       </c>
       <c r="F173" t="s">
         <v>10</v>
       </c>
       <c r="G173" s="5">
-        <v>45895</v>
+        <v>45957</v>
       </c>
       <c r="H173" s="5">
-        <v>45915</v>
+        <v>45976</v>
       </c>
       <c r="I173" s="5">
         <v>46023</v>
@@ -7362,234 +7623,1510 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>12</v>
+        <v>208</v>
       </c>
       <c r="B174" t="s">
-        <v>27</v>
+        <v>209</v>
       </c>
       <c r="C174" t="s">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="D174" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="E174">
-        <v>57418</v>
+        <v>57701</v>
       </c>
       <c r="F174" t="s">
         <v>10</v>
       </c>
       <c r="G174" s="5">
-        <v>45895</v>
+        <v>45992</v>
       </c>
       <c r="H174" s="5">
-        <v>45915</v>
+        <v>46006</v>
       </c>
       <c r="I174" s="5">
-        <v>46023</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>12</v>
+        <v>347</v>
       </c>
       <c r="B175" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C175" t="s">
-        <v>32</v>
+        <v>348</v>
       </c>
       <c r="D175" t="s">
-        <v>33</v>
+        <v>349</v>
       </c>
       <c r="E175">
-        <v>57417</v>
+        <v>57490</v>
       </c>
       <c r="F175" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G175" s="5">
-        <v>45895</v>
+        <v>46048</v>
       </c>
       <c r="H175" s="5">
-        <v>45915</v>
+        <v>46055</v>
       </c>
       <c r="I175" s="5">
-        <v>46023</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>12</v>
+        <v>347</v>
       </c>
       <c r="B176" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C176" t="s">
-        <v>32</v>
+        <v>350</v>
       </c>
       <c r="D176" t="s">
-        <v>33</v>
+        <v>351</v>
       </c>
       <c r="E176">
-        <v>57421</v>
+        <v>51528</v>
       </c>
       <c r="F176" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G176" s="5">
-        <v>45895</v>
+        <v>46048</v>
       </c>
       <c r="H176" s="5">
-        <v>45915</v>
+        <v>46055</v>
       </c>
       <c r="I176" s="5">
-        <v>46023</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>12</v>
+        <v>347</v>
       </c>
       <c r="B177" t="s">
-        <v>234</v>
+        <v>35</v>
       </c>
       <c r="C177" t="s">
-        <v>234</v>
+        <v>352</v>
       </c>
       <c r="D177" t="s">
-        <v>235</v>
+        <v>353</v>
       </c>
       <c r="E177">
-        <v>57760</v>
+        <v>51522</v>
       </c>
       <c r="F177" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G177" s="5">
-        <v>46035</v>
-      </c>
-      <c r="H177" t="s">
-        <v>65</v>
+        <v>46048</v>
+      </c>
+      <c r="H177" s="5">
+        <v>46055</v>
       </c>
       <c r="I177" s="5">
-        <v>46047</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B178" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="C178" t="s">
-        <v>14</v>
+        <v>212</v>
       </c>
       <c r="D178" t="s">
-        <v>15</v>
+        <v>213</v>
       </c>
       <c r="E178">
-        <v>57459</v>
+        <v>56438</v>
       </c>
       <c r="F178" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G178" s="5">
-        <v>45902</v>
+        <v>46030</v>
       </c>
       <c r="H178" s="5">
-        <v>45915</v>
+        <v>46047</v>
       </c>
       <c r="I178" s="5">
-        <v>46023</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B179" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="C179" t="s">
-        <v>14</v>
+        <v>402</v>
       </c>
       <c r="D179" t="s">
-        <v>15</v>
+        <v>403</v>
       </c>
       <c r="E179">
-        <v>57485</v>
+        <v>57743</v>
       </c>
       <c r="F179" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G179" s="5">
-        <v>45911</v>
+        <v>46013</v>
       </c>
       <c r="H179" s="5">
-        <v>45931</v>
+        <v>46037</v>
       </c>
       <c r="I179" s="5">
-        <v>46023</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B180" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="C180" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="D180" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="E180">
-        <v>57486</v>
+        <v>57671</v>
       </c>
       <c r="F180" t="s">
         <v>10</v>
       </c>
       <c r="G180" s="5">
-        <v>45911</v>
+        <v>45974</v>
       </c>
       <c r="H180" s="5">
-        <v>45931</v>
+        <v>45992</v>
       </c>
       <c r="I180" s="5">
-        <v>46023</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="B181" t="s">
-        <v>237</v>
+        <v>96</v>
       </c>
       <c r="C181" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="D181" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="E181">
-        <v>57324</v>
+        <v>51696</v>
       </c>
       <c r="F181" t="s">
         <v>107</v>
       </c>
       <c r="G181" s="5">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="H181" s="5">
         <v>46047</v>
       </c>
       <c r="I181" s="5">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>20</v>
+      </c>
+      <c r="B182" t="s">
+        <v>96</v>
+      </c>
+      <c r="C182" t="s">
+        <v>216</v>
+      </c>
+      <c r="D182" t="s">
+        <v>217</v>
+      </c>
+      <c r="E182">
+        <v>51693</v>
+      </c>
+      <c r="F182" t="s">
+        <v>107</v>
+      </c>
+      <c r="G182" s="5">
+        <v>46029</v>
+      </c>
+      <c r="H182" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I182" s="5">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>20</v>
+      </c>
+      <c r="B183" t="s">
+        <v>96</v>
+      </c>
+      <c r="C183" t="s">
+        <v>218</v>
+      </c>
+      <c r="D183" t="s">
+        <v>219</v>
+      </c>
+      <c r="E183">
+        <v>51697</v>
+      </c>
+      <c r="F183" t="s">
+        <v>107</v>
+      </c>
+      <c r="G183" s="5">
+        <v>46029</v>
+      </c>
+      <c r="H183" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I183" s="5">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>20</v>
+      </c>
+      <c r="B184" t="s">
+        <v>96</v>
+      </c>
+      <c r="C184" t="s">
+        <v>220</v>
+      </c>
+      <c r="D184" t="s">
+        <v>221</v>
+      </c>
+      <c r="E184">
+        <v>51687</v>
+      </c>
+      <c r="F184" t="s">
+        <v>107</v>
+      </c>
+      <c r="G184" s="5">
         <v>46030</v>
+      </c>
+      <c r="H184" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I184" s="5">
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>20</v>
+      </c>
+      <c r="B185" t="s">
+        <v>96</v>
+      </c>
+      <c r="C185" t="s">
+        <v>220</v>
+      </c>
+      <c r="D185" t="s">
+        <v>221</v>
+      </c>
+      <c r="E185">
+        <v>57756</v>
+      </c>
+      <c r="F185" t="s">
+        <v>64</v>
+      </c>
+      <c r="G185" s="5">
+        <v>46029</v>
+      </c>
+      <c r="H185" t="s">
+        <v>65</v>
+      </c>
+      <c r="I185" s="5">
+        <v>46047</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>20</v>
+      </c>
+      <c r="B186" t="s">
+        <v>354</v>
+      </c>
+      <c r="C186" t="s">
+        <v>355</v>
+      </c>
+      <c r="D186" t="s">
+        <v>356</v>
+      </c>
+      <c r="E186">
+        <v>53634</v>
+      </c>
+      <c r="F186" t="s">
+        <v>357</v>
+      </c>
+      <c r="G186" s="5">
+        <v>46063</v>
+      </c>
+      <c r="H186" t="s">
+        <v>358</v>
+      </c>
+      <c r="I186" s="5">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>20</v>
+      </c>
+      <c r="B187" t="s">
+        <v>222</v>
+      </c>
+      <c r="C187" t="s">
+        <v>223</v>
+      </c>
+      <c r="D187" t="s">
+        <v>224</v>
+      </c>
+      <c r="E187">
+        <v>53224</v>
+      </c>
+      <c r="F187" t="s">
+        <v>107</v>
+      </c>
+      <c r="G187" s="5">
+        <v>46031</v>
+      </c>
+      <c r="H187" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I187" s="5">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>20</v>
+      </c>
+      <c r="B188" t="s">
+        <v>225</v>
+      </c>
+      <c r="C188" t="s">
+        <v>359</v>
+      </c>
+      <c r="D188" t="s">
+        <v>360</v>
+      </c>
+      <c r="E188">
+        <v>57708</v>
+      </c>
+      <c r="F188" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" s="5">
+        <v>46001</v>
+      </c>
+      <c r="H188" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I188" s="5">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>20</v>
+      </c>
+      <c r="B189" t="s">
+        <v>225</v>
+      </c>
+      <c r="C189" t="s">
+        <v>226</v>
+      </c>
+      <c r="D189" t="s">
+        <v>227</v>
+      </c>
+      <c r="E189">
+        <v>55787</v>
+      </c>
+      <c r="F189" t="s">
+        <v>107</v>
+      </c>
+      <c r="G189" s="5">
+        <v>46027</v>
+      </c>
+      <c r="H189" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I189" s="5">
+        <v>46027</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>20</v>
+      </c>
+      <c r="B190" t="s">
+        <v>225</v>
+      </c>
+      <c r="C190" t="s">
+        <v>477</v>
+      </c>
+      <c r="D190" t="s">
+        <v>478</v>
+      </c>
+      <c r="E190">
+        <v>57766</v>
+      </c>
+      <c r="F190" t="s">
+        <v>10</v>
+      </c>
+      <c r="G190" s="5">
+        <v>46037</v>
+      </c>
+      <c r="H190" s="5">
+        <v>46054</v>
+      </c>
+      <c r="I190" s="5">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>20</v>
+      </c>
+      <c r="B191" t="s">
+        <v>225</v>
+      </c>
+      <c r="C191" t="s">
+        <v>479</v>
+      </c>
+      <c r="D191" t="s">
+        <v>480</v>
+      </c>
+      <c r="E191">
+        <v>57767</v>
+      </c>
+      <c r="F191" t="s">
+        <v>19</v>
+      </c>
+      <c r="G191" s="5">
+        <v>46037</v>
+      </c>
+      <c r="H191" s="5">
+        <v>46054</v>
+      </c>
+      <c r="I191" s="5">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>361</v>
+      </c>
+      <c r="B192" t="s">
+        <v>362</v>
+      </c>
+      <c r="C192" t="s">
+        <v>363</v>
+      </c>
+      <c r="D192" t="s">
+        <v>364</v>
+      </c>
+      <c r="E192">
+        <v>52702</v>
+      </c>
+      <c r="F192" t="s">
+        <v>107</v>
+      </c>
+      <c r="G192" s="5">
+        <v>46057</v>
+      </c>
+      <c r="H192" s="5">
+        <v>46062</v>
+      </c>
+      <c r="I192" s="5">
+        <v>46057</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>361</v>
+      </c>
+      <c r="B193" t="s">
+        <v>362</v>
+      </c>
+      <c r="C193" t="s">
+        <v>365</v>
+      </c>
+      <c r="D193" t="s">
+        <v>366</v>
+      </c>
+      <c r="E193">
+        <v>51793</v>
+      </c>
+      <c r="F193" t="s">
+        <v>107</v>
+      </c>
+      <c r="G193" s="5">
+        <v>46057</v>
+      </c>
+      <c r="H193" s="5">
+        <v>46062</v>
+      </c>
+      <c r="I193" s="5">
+        <v>46057</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>361</v>
+      </c>
+      <c r="B194" t="s">
+        <v>362</v>
+      </c>
+      <c r="C194" t="s">
+        <v>367</v>
+      </c>
+      <c r="D194" t="s">
+        <v>368</v>
+      </c>
+      <c r="E194">
+        <v>51802</v>
+      </c>
+      <c r="F194" t="s">
+        <v>107</v>
+      </c>
+      <c r="G194" s="5">
+        <v>46057</v>
+      </c>
+      <c r="H194" s="5">
+        <v>46062</v>
+      </c>
+      <c r="I194" s="5">
+        <v>46057</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>361</v>
+      </c>
+      <c r="B195" t="s">
+        <v>362</v>
+      </c>
+      <c r="C195" t="s">
+        <v>369</v>
+      </c>
+      <c r="D195" t="s">
+        <v>370</v>
+      </c>
+      <c r="E195">
+        <v>51798</v>
+      </c>
+      <c r="F195" t="s">
+        <v>107</v>
+      </c>
+      <c r="G195" s="5">
+        <v>46057</v>
+      </c>
+      <c r="H195" s="5">
+        <v>46062</v>
+      </c>
+      <c r="I195" s="5">
+        <v>46057</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>361</v>
+      </c>
+      <c r="B196" t="s">
+        <v>362</v>
+      </c>
+      <c r="C196" t="s">
+        <v>404</v>
+      </c>
+      <c r="D196" t="s">
+        <v>405</v>
+      </c>
+      <c r="E196">
+        <v>51799</v>
+      </c>
+      <c r="F196" t="s">
+        <v>107</v>
+      </c>
+      <c r="G196" s="5">
+        <v>46076</v>
+      </c>
+      <c r="H196" s="5">
+        <v>46082</v>
+      </c>
+      <c r="I196" s="5">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>361</v>
+      </c>
+      <c r="B197" t="s">
+        <v>362</v>
+      </c>
+      <c r="C197" t="s">
+        <v>406</v>
+      </c>
+      <c r="D197" t="s">
+        <v>407</v>
+      </c>
+      <c r="E197">
+        <v>51800</v>
+      </c>
+      <c r="F197" t="s">
+        <v>107</v>
+      </c>
+      <c r="G197" s="5">
+        <v>46076</v>
+      </c>
+      <c r="H197" s="5">
+        <v>46082</v>
+      </c>
+      <c r="I197" s="5">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>361</v>
+      </c>
+      <c r="B198" t="s">
+        <v>362</v>
+      </c>
+      <c r="C198" t="s">
+        <v>408</v>
+      </c>
+      <c r="D198" t="s">
+        <v>409</v>
+      </c>
+      <c r="E198">
+        <v>51803</v>
+      </c>
+      <c r="F198" t="s">
+        <v>107</v>
+      </c>
+      <c r="G198" s="5">
+        <v>46076</v>
+      </c>
+      <c r="H198" s="5">
+        <v>46082</v>
+      </c>
+      <c r="I198" s="5">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>361</v>
+      </c>
+      <c r="B199" t="s">
+        <v>362</v>
+      </c>
+      <c r="C199" t="s">
+        <v>410</v>
+      </c>
+      <c r="D199" t="s">
+        <v>411</v>
+      </c>
+      <c r="E199">
+        <v>51807</v>
+      </c>
+      <c r="F199" t="s">
+        <v>107</v>
+      </c>
+      <c r="G199" s="5">
+        <v>46076</v>
+      </c>
+      <c r="H199" s="5">
+        <v>46082</v>
+      </c>
+      <c r="I199" s="5">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>361</v>
+      </c>
+      <c r="B200" t="s">
+        <v>362</v>
+      </c>
+      <c r="C200" t="s">
+        <v>371</v>
+      </c>
+      <c r="D200" t="s">
+        <v>372</v>
+      </c>
+      <c r="E200">
+        <v>52701</v>
+      </c>
+      <c r="F200" t="s">
+        <v>107</v>
+      </c>
+      <c r="G200" s="5">
+        <v>46057</v>
+      </c>
+      <c r="H200" s="5">
+        <v>46062</v>
+      </c>
+      <c r="I200" s="5">
+        <v>46057</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>99</v>
+      </c>
+      <c r="B201" t="s">
+        <v>35</v>
+      </c>
+      <c r="C201" t="s">
+        <v>123</v>
+      </c>
+      <c r="D201" t="s">
+        <v>481</v>
+      </c>
+      <c r="E201">
+        <v>57591</v>
+      </c>
+      <c r="F201" t="s">
+        <v>107</v>
+      </c>
+      <c r="G201" s="5">
+        <v>46087</v>
+      </c>
+      <c r="H201" s="5">
+        <v>46096</v>
+      </c>
+      <c r="I201" s="5">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>99</v>
+      </c>
+      <c r="B202" t="s">
+        <v>35</v>
+      </c>
+      <c r="C202" t="s">
+        <v>482</v>
+      </c>
+      <c r="D202" t="s">
+        <v>483</v>
+      </c>
+      <c r="E202">
+        <v>57097</v>
+      </c>
+      <c r="F202" t="s">
+        <v>107</v>
+      </c>
+      <c r="G202" s="5">
+        <v>46087</v>
+      </c>
+      <c r="H202" s="5">
+        <v>46096</v>
+      </c>
+      <c r="I202" s="5">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>99</v>
+      </c>
+      <c r="B203" t="s">
+        <v>35</v>
+      </c>
+      <c r="C203" t="s">
+        <v>484</v>
+      </c>
+      <c r="D203" t="s">
+        <v>485</v>
+      </c>
+      <c r="E203">
+        <v>57272</v>
+      </c>
+      <c r="F203" t="s">
+        <v>107</v>
+      </c>
+      <c r="G203" s="5">
+        <v>46087</v>
+      </c>
+      <c r="H203" s="5">
+        <v>46096</v>
+      </c>
+      <c r="I203" s="5">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>99</v>
+      </c>
+      <c r="B204" t="s">
+        <v>35</v>
+      </c>
+      <c r="C204" t="s">
+        <v>100</v>
+      </c>
+      <c r="D204" t="s">
+        <v>101</v>
+      </c>
+      <c r="E204">
+        <v>57604</v>
+      </c>
+      <c r="F204" t="s">
+        <v>10</v>
+      </c>
+      <c r="G204" s="5">
+        <v>45952</v>
+      </c>
+      <c r="H204" s="5">
+        <v>45976</v>
+      </c>
+      <c r="I204" s="5">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>99</v>
+      </c>
+      <c r="B205" t="s">
+        <v>35</v>
+      </c>
+      <c r="C205" t="s">
+        <v>102</v>
+      </c>
+      <c r="D205" t="s">
+        <v>103</v>
+      </c>
+      <c r="E205">
+        <v>57606</v>
+      </c>
+      <c r="F205" t="s">
+        <v>10</v>
+      </c>
+      <c r="G205" s="5">
+        <v>45952</v>
+      </c>
+      <c r="H205" s="5">
+        <v>45976</v>
+      </c>
+      <c r="I205" s="5">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>228</v>
+      </c>
+      <c r="B206" t="s">
+        <v>35</v>
+      </c>
+      <c r="C206" t="s">
+        <v>229</v>
+      </c>
+      <c r="D206" t="s">
+        <v>230</v>
+      </c>
+      <c r="E206">
+        <v>57088</v>
+      </c>
+      <c r="F206" t="s">
+        <v>107</v>
+      </c>
+      <c r="G206" s="5">
+        <v>46029</v>
+      </c>
+      <c r="H206" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I206" s="5">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>228</v>
+      </c>
+      <c r="B207" t="s">
+        <v>231</v>
+      </c>
+      <c r="C207" t="s">
+        <v>232</v>
+      </c>
+      <c r="D207" t="s">
+        <v>233</v>
+      </c>
+      <c r="E207">
+        <v>56876</v>
+      </c>
+      <c r="F207" t="s">
+        <v>107</v>
+      </c>
+      <c r="G207" s="5">
+        <v>46029</v>
+      </c>
+      <c r="H207" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I207" s="5">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>44</v>
+      </c>
+      <c r="B208" t="s">
+        <v>35</v>
+      </c>
+      <c r="C208" t="s">
+        <v>45</v>
+      </c>
+      <c r="D208" t="s">
+        <v>46</v>
+      </c>
+      <c r="E208">
+        <v>57639</v>
+      </c>
+      <c r="F208" t="s">
+        <v>19</v>
+      </c>
+      <c r="G208" s="5">
+        <v>45961</v>
+      </c>
+      <c r="H208" s="5">
+        <v>45976</v>
+      </c>
+      <c r="I208" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>44</v>
+      </c>
+      <c r="B209" t="s">
+        <v>35</v>
+      </c>
+      <c r="C209" t="s">
+        <v>412</v>
+      </c>
+      <c r="D209" t="s">
+        <v>413</v>
+      </c>
+      <c r="E209">
+        <v>56505</v>
+      </c>
+      <c r="F209" t="s">
+        <v>107</v>
+      </c>
+      <c r="G209" s="5">
+        <v>46071</v>
+      </c>
+      <c r="H209" s="5">
+        <v>46082</v>
+      </c>
+      <c r="I209" s="5">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>12</v>
+      </c>
+      <c r="B210" t="s">
+        <v>27</v>
+      </c>
+      <c r="C210" t="s">
+        <v>28</v>
+      </c>
+      <c r="D210" t="s">
+        <v>29</v>
+      </c>
+      <c r="E210">
+        <v>57419</v>
+      </c>
+      <c r="F210" t="s">
+        <v>10</v>
+      </c>
+      <c r="G210" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H210" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I210" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>12</v>
+      </c>
+      <c r="B211" t="s">
+        <v>27</v>
+      </c>
+      <c r="C211" t="s">
+        <v>28</v>
+      </c>
+      <c r="D211" t="s">
+        <v>29</v>
+      </c>
+      <c r="E211">
+        <v>57420</v>
+      </c>
+      <c r="F211" t="s">
+        <v>10</v>
+      </c>
+      <c r="G211" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H211" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I211" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>12</v>
+      </c>
+      <c r="B212" t="s">
+        <v>27</v>
+      </c>
+      <c r="C212" t="s">
+        <v>30</v>
+      </c>
+      <c r="D212" t="s">
+        <v>31</v>
+      </c>
+      <c r="E212">
+        <v>57418</v>
+      </c>
+      <c r="F212" t="s">
+        <v>10</v>
+      </c>
+      <c r="G212" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H212" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I212" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>12</v>
+      </c>
+      <c r="B213" t="s">
+        <v>27</v>
+      </c>
+      <c r="C213" t="s">
+        <v>32</v>
+      </c>
+      <c r="D213" t="s">
+        <v>33</v>
+      </c>
+      <c r="E213">
+        <v>57417</v>
+      </c>
+      <c r="F213" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H213" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I213" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>12</v>
+      </c>
+      <c r="B214" t="s">
+        <v>27</v>
+      </c>
+      <c r="C214" t="s">
+        <v>32</v>
+      </c>
+      <c r="D214" t="s">
+        <v>33</v>
+      </c>
+      <c r="E214">
+        <v>57421</v>
+      </c>
+      <c r="F214" t="s">
+        <v>10</v>
+      </c>
+      <c r="G214" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H214" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I214" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>12</v>
+      </c>
+      <c r="B215" t="s">
+        <v>234</v>
+      </c>
+      <c r="C215" t="s">
+        <v>234</v>
+      </c>
+      <c r="D215" t="s">
+        <v>235</v>
+      </c>
+      <c r="E215">
+        <v>57760</v>
+      </c>
+      <c r="F215" t="s">
+        <v>64</v>
+      </c>
+      <c r="G215" s="5">
+        <v>46035</v>
+      </c>
+      <c r="H215" t="s">
+        <v>65</v>
+      </c>
+      <c r="I215" s="5">
+        <v>46047</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>12</v>
+      </c>
+      <c r="B216" t="s">
+        <v>14</v>
+      </c>
+      <c r="C216" t="s">
+        <v>14</v>
+      </c>
+      <c r="D216" t="s">
+        <v>15</v>
+      </c>
+      <c r="E216">
+        <v>57459</v>
+      </c>
+      <c r="F216" t="s">
+        <v>10</v>
+      </c>
+      <c r="G216" s="5">
+        <v>45902</v>
+      </c>
+      <c r="H216" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I216" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>12</v>
+      </c>
+      <c r="B217" t="s">
+        <v>14</v>
+      </c>
+      <c r="C217" t="s">
+        <v>14</v>
+      </c>
+      <c r="D217" t="s">
+        <v>15</v>
+      </c>
+      <c r="E217">
+        <v>57485</v>
+      </c>
+      <c r="F217" t="s">
+        <v>10</v>
+      </c>
+      <c r="G217" s="5">
+        <v>45911</v>
+      </c>
+      <c r="H217" s="5">
+        <v>45931</v>
+      </c>
+      <c r="I217" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>12</v>
+      </c>
+      <c r="B218" t="s">
+        <v>14</v>
+      </c>
+      <c r="C218" t="s">
+        <v>14</v>
+      </c>
+      <c r="D218" t="s">
+        <v>15</v>
+      </c>
+      <c r="E218">
+        <v>57486</v>
+      </c>
+      <c r="F218" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" s="5">
+        <v>45911</v>
+      </c>
+      <c r="H218" s="5">
+        <v>45931</v>
+      </c>
+      <c r="I218" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>236</v>
+      </c>
+      <c r="B219" t="s">
+        <v>486</v>
+      </c>
+      <c r="C219" t="s">
+        <v>487</v>
+      </c>
+      <c r="D219" t="s">
+        <v>488</v>
+      </c>
+      <c r="E219">
+        <v>57758</v>
+      </c>
+      <c r="F219" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" s="5">
+        <v>46030</v>
+      </c>
+      <c r="H219" s="5">
+        <v>46054</v>
+      </c>
+      <c r="I219" s="5">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>236</v>
+      </c>
+      <c r="B220" t="s">
+        <v>489</v>
+      </c>
+      <c r="C220" t="s">
+        <v>490</v>
+      </c>
+      <c r="D220" t="s">
+        <v>491</v>
+      </c>
+      <c r="E220">
+        <v>57738</v>
+      </c>
+      <c r="F220" t="s">
+        <v>141</v>
+      </c>
+      <c r="G220" s="5">
+        <v>46010</v>
+      </c>
+      <c r="H220" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I220" s="5">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>236</v>
+      </c>
+      <c r="B221" t="s">
+        <v>489</v>
+      </c>
+      <c r="C221" t="s">
+        <v>492</v>
+      </c>
+      <c r="D221" t="s">
+        <v>493</v>
+      </c>
+      <c r="E221">
+        <v>57739</v>
+      </c>
+      <c r="F221" t="s">
+        <v>141</v>
+      </c>
+      <c r="G221" s="5">
+        <v>46010</v>
+      </c>
+      <c r="H221" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I221" s="5">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>236</v>
+      </c>
+      <c r="B222" t="s">
+        <v>489</v>
+      </c>
+      <c r="C222" t="s">
+        <v>494</v>
+      </c>
+      <c r="D222" t="s">
+        <v>495</v>
+      </c>
+      <c r="E222">
+        <v>57744</v>
+      </c>
+      <c r="F222" t="s">
+        <v>82</v>
+      </c>
+      <c r="G222" s="5">
+        <v>46014</v>
+      </c>
+      <c r="H222" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I222" s="5">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>236</v>
+      </c>
+      <c r="B223" t="s">
+        <v>489</v>
+      </c>
+      <c r="C223" t="s">
+        <v>496</v>
+      </c>
+      <c r="D223" t="s">
+        <v>497</v>
+      </c>
+      <c r="E223">
+        <v>57742</v>
+      </c>
+      <c r="F223" t="s">
+        <v>82</v>
+      </c>
+      <c r="G223" s="5">
+        <v>46010</v>
+      </c>
+      <c r="H223" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I223" s="5">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>236</v>
+      </c>
+      <c r="B224" t="s">
+        <v>237</v>
+      </c>
+      <c r="C224" t="s">
+        <v>238</v>
+      </c>
+      <c r="D224" t="s">
+        <v>239</v>
+      </c>
+      <c r="E224">
+        <v>57324</v>
+      </c>
+      <c r="F224" t="s">
+        <v>107</v>
+      </c>
+      <c r="G224" s="5">
+        <v>46030</v>
+      </c>
+      <c r="H224" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I224" s="5">
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>498</v>
+      </c>
+      <c r="B225" t="s">
+        <v>35</v>
+      </c>
+      <c r="C225" t="s">
+        <v>499</v>
+      </c>
+      <c r="D225" t="s">
+        <v>500</v>
+      </c>
+      <c r="E225">
+        <v>57686</v>
+      </c>
+      <c r="F225" t="s">
+        <v>10</v>
+      </c>
+      <c r="G225" s="5">
+        <v>45976</v>
+      </c>
+      <c r="H225" s="5">
+        <v>46006</v>
+      </c>
+      <c r="I225" s="5">
+        <v>46043</v>
       </c>
     </row>
   </sheetData>

--- a/Utah_Index_of_Changes.xlsx
+++ b/Utah_Index_of_Changes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Shared drives\DAS_Rules_DAR\Index of Changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEB33FE-70E0-41B8-8F34-D211DCACCAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DB68CF-7E16-456E-B633-3D711C8EC43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AB629357-4CE5-4584-B8BD-0FC25277305B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AB629357-4CE5-4584-B8BD-0FC25277305B}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="548">
   <si>
     <t>Published Date</t>
   </si>
@@ -1543,6 +1543,147 @@
   </si>
   <si>
     <t>R940-1</t>
+  </si>
+  <si>
+    <t>Quarantine Pertaining to the Emerald Ash Borer</t>
+  </si>
+  <si>
+    <t>R68-11</t>
+  </si>
+  <si>
+    <t>Recreational Therapy Practice Act Rule</t>
+  </si>
+  <si>
+    <t>R156-40</t>
+  </si>
+  <si>
+    <t>Division Utah Administrative Procedures Act Rule</t>
+  </si>
+  <si>
+    <t>R156-46b</t>
+  </si>
+  <si>
+    <t>Utah Construction Trades Licensing Act Rule</t>
+  </si>
+  <si>
+    <t>R156-55a</t>
+  </si>
+  <si>
+    <t>Psychologist Licensing Act Rule</t>
+  </si>
+  <si>
+    <t>R156-61</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Utah Residential Mortgage Practices and Licensing Rules</t>
+  </si>
+  <si>
+    <t>R162-2c</t>
+  </si>
+  <si>
+    <t>Communications Authority Board (Utah)</t>
+  </si>
+  <si>
+    <t>Utah Communications Authority Board</t>
+  </si>
+  <si>
+    <t>R174-1</t>
+  </si>
+  <si>
+    <t>Corrections</t>
+  </si>
+  <si>
+    <t>Undercover Roles of Offenders</t>
+  </si>
+  <si>
+    <t>R251-701</t>
+  </si>
+  <si>
+    <t>Inmate Communication: Telephones</t>
+  </si>
+  <si>
+    <t>R251-702</t>
+  </si>
+  <si>
+    <t>Crime Victim Reparations Adjudicative Proceedings</t>
+  </si>
+  <si>
+    <t>R270-2</t>
+  </si>
+  <si>
+    <t>Private School, Home School, Scholarship, and Bureau of Indian Education (BIE) Student Participation in Public School Achievement Tests</t>
+  </si>
+  <si>
+    <t>R277-604</t>
+  </si>
+  <si>
+    <t>Education Programs for Students with Disabilities</t>
+  </si>
+  <si>
+    <t>R277-750</t>
+  </si>
+  <si>
+    <t>School Improvement and Leadership Development</t>
+  </si>
+  <si>
+    <t>R277-920</t>
+  </si>
+  <si>
+    <t>Partnerships for Student Success Grant Program</t>
+  </si>
+  <si>
+    <t>R277-924</t>
+  </si>
+  <si>
+    <t>Affordable Housing Infrastructure Grant Rule</t>
+  </si>
+  <si>
+    <t>R357-48</t>
+  </si>
+  <si>
+    <t>Telehealth</t>
+  </si>
+  <si>
+    <t>R414-42</t>
+  </si>
+  <si>
+    <t>Veterans Tuition Gap Program</t>
+  </si>
+  <si>
+    <t>R765-611</t>
+  </si>
+  <si>
+    <t>Opportunity Scholarship</t>
+  </si>
+  <si>
+    <t>R765-612</t>
+  </si>
+  <si>
+    <t>Student Educational Enrichment Program</t>
+  </si>
+  <si>
+    <t>R661-19</t>
+  </si>
+  <si>
+    <t>Photovoltaic (Solar) Systems Program</t>
+  </si>
+  <si>
+    <t>R661-20</t>
+  </si>
+  <si>
+    <t>Utah Navajo Trust Fund Higher Education Financial Assistance and Scholarship Program</t>
+  </si>
+  <si>
+    <t>R661-24</t>
+  </si>
+  <si>
+    <t>Utah Navajo Trust Fund Housing Projects Policy</t>
+  </si>
+  <si>
+    <t>R661-25</t>
   </si>
 </sst>
 </file>
@@ -2242,8 +2383,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}" name="IndexofChanges2026" displayName="IndexofChanges2026" ref="A1:I225" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A1:I225" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}" name="IndexofChanges2026" displayName="IndexofChanges2026" ref="A1:I250" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A1:I250" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A5D7328E-E900-42CC-861B-C0B93E9FA323}" name="Agency Name" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{6813DE60-D8C9-46E4-9980-0485DD9243AF}" name="Title Name"/>
@@ -2590,10 +2731,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I225"/>
+  <dimension ref="A1:I250"/>
   <sheetFormatPr defaultColWidth="32.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="180" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
@@ -2928,28 +3069,28 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>501</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>502</v>
       </c>
       <c r="E12">
-        <v>55403</v>
+        <v>54512</v>
       </c>
       <c r="F12" t="s">
         <v>107</v>
       </c>
       <c r="G12" s="5">
-        <v>46030</v>
+        <v>46097</v>
       </c>
       <c r="H12" s="5">
-        <v>46047</v>
+        <v>46104</v>
       </c>
       <c r="I12" s="5">
-        <v>46030</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2960,13 +3101,13 @@
         <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E13">
-        <v>55041</v>
+        <v>55403</v>
       </c>
       <c r="F13" t="s">
         <v>107</v>
@@ -2989,13 +3130,13 @@
         <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E14">
-        <v>55034</v>
+        <v>55041</v>
       </c>
       <c r="F14" t="s">
         <v>107</v>
@@ -3018,25 +3159,25 @@
         <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>414</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>415</v>
+        <v>111</v>
       </c>
       <c r="E15">
-        <v>57525</v>
+        <v>55034</v>
       </c>
       <c r="F15" t="s">
         <v>107</v>
       </c>
       <c r="G15" s="5">
-        <v>46084</v>
+        <v>46030</v>
       </c>
       <c r="H15" s="5">
-        <v>46096</v>
+        <v>46047</v>
       </c>
       <c r="I15" s="5">
-        <v>46084</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -3044,28 +3185,28 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>414</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>415</v>
       </c>
       <c r="E16">
-        <v>57488</v>
+        <v>57525</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G16" s="5">
-        <v>45912</v>
+        <v>46084</v>
       </c>
       <c r="H16" s="5">
-        <v>45931</v>
+        <v>46096</v>
       </c>
       <c r="I16" s="5">
-        <v>46029</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -3085,13 +3226,13 @@
         <v>57488</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G17" s="5">
-        <v>45966</v>
+        <v>45912</v>
       </c>
       <c r="H17" s="5">
-        <v>45992</v>
+        <v>45931</v>
       </c>
       <c r="I17" s="5">
         <v>46029</v>
@@ -3105,22 +3246,22 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E18">
-        <v>57403</v>
+        <v>57488</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G18" s="5">
-        <v>45887</v>
+        <v>45966</v>
       </c>
       <c r="H18" s="5">
-        <v>45915</v>
+        <v>45992</v>
       </c>
       <c r="I18" s="5">
         <v>46029</v>
@@ -3143,13 +3284,13 @@
         <v>57403</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G19" s="5">
-        <v>45966</v>
+        <v>45887</v>
       </c>
       <c r="H19" s="5">
-        <v>45992</v>
+        <v>45915</v>
       </c>
       <c r="I19" s="5">
         <v>46029</v>
@@ -3157,22 +3298,22 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="E20">
-        <v>57665</v>
+        <v>57403</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G20" s="5">
         <v>45966</v>
@@ -3181,36 +3322,36 @@
         <v>45992</v>
       </c>
       <c r="I20" s="5">
-        <v>46052</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>416</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>417</v>
+        <v>114</v>
       </c>
       <c r="E21">
-        <v>54255</v>
+        <v>57665</v>
       </c>
       <c r="F21" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G21" s="5">
-        <v>46093</v>
+        <v>45966</v>
       </c>
       <c r="H21" s="5">
-        <v>46096</v>
+        <v>45992</v>
       </c>
       <c r="I21" s="5">
-        <v>46093</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -3227,19 +3368,19 @@
         <v>417</v>
       </c>
       <c r="E22">
-        <v>57852</v>
+        <v>54255</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G22" s="5">
         <v>46093</v>
       </c>
-      <c r="H22" t="s">
-        <v>65</v>
+      <c r="H22" s="5">
+        <v>46096</v>
       </c>
       <c r="I22" s="5">
-        <v>46096</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -3250,25 +3391,25 @@
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>416</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>417</v>
       </c>
       <c r="E23">
-        <v>57528</v>
+        <v>57852</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="G23" s="5">
-        <v>45930</v>
-      </c>
-      <c r="H23" s="5">
-        <v>45945</v>
+        <v>46093</v>
+      </c>
+      <c r="H23" t="s">
+        <v>65</v>
       </c>
       <c r="I23" s="5">
-        <v>46023</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -3276,28 +3417,28 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>373</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>374</v>
+        <v>26</v>
       </c>
       <c r="E24">
-        <v>57754</v>
+        <v>57528</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G24" s="5">
-        <v>46027</v>
+        <v>45930</v>
       </c>
       <c r="H24" s="5">
-        <v>46037</v>
+        <v>45945</v>
       </c>
       <c r="I24" s="5">
-        <v>46077</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -3308,25 +3449,25 @@
         <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>503</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>504</v>
       </c>
       <c r="E25">
-        <v>57661</v>
+        <v>57192</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G25" s="5">
-        <v>45965</v>
+        <v>46083</v>
       </c>
       <c r="H25" s="5">
-        <v>45992</v>
+        <v>46104</v>
       </c>
       <c r="I25" s="5">
-        <v>46037</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -3337,25 +3478,25 @@
         <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>418</v>
+        <v>505</v>
       </c>
       <c r="D26" t="s">
-        <v>419</v>
+        <v>506</v>
       </c>
       <c r="E26">
-        <v>57633</v>
+        <v>57787</v>
       </c>
       <c r="F26" t="s">
         <v>10</v>
       </c>
       <c r="G26" s="5">
-        <v>45965</v>
+        <v>46051</v>
       </c>
       <c r="H26" s="5">
-        <v>45992</v>
+        <v>46068</v>
       </c>
       <c r="I26" s="5">
-        <v>46111</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -3366,25 +3507,25 @@
         <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="D27" t="s">
-        <v>421</v>
+        <v>374</v>
       </c>
       <c r="E27">
-        <v>50288</v>
+        <v>57754</v>
       </c>
       <c r="F27" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G27" s="5">
-        <v>46083</v>
+        <v>46027</v>
       </c>
       <c r="H27" s="5">
-        <v>46096</v>
+        <v>46037</v>
       </c>
       <c r="I27" s="5">
-        <v>46083</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -3395,25 +3536,25 @@
         <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>507</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>508</v>
       </c>
       <c r="E28">
-        <v>56871</v>
+        <v>57745</v>
       </c>
       <c r="F28" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G28" s="5">
-        <v>46029</v>
+        <v>46014</v>
       </c>
       <c r="H28" s="5">
-        <v>46047</v>
+        <v>46068</v>
       </c>
       <c r="I28" s="5">
-        <v>46029</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -3424,25 +3565,25 @@
         <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="E29">
-        <v>50314</v>
+        <v>57661</v>
       </c>
       <c r="F29" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G29" s="5">
-        <v>46029</v>
+        <v>45965</v>
       </c>
       <c r="H29" s="5">
-        <v>46047</v>
+        <v>45992</v>
       </c>
       <c r="I29" s="5">
-        <v>46029</v>
+        <v>46037</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -3453,605 +3594,605 @@
         <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D30" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E30">
-        <v>56813</v>
+        <v>57633</v>
       </c>
       <c r="F30" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G30" s="5">
-        <v>46083</v>
+        <v>45965</v>
       </c>
       <c r="H30" s="5">
-        <v>46096</v>
+        <v>45992</v>
       </c>
       <c r="I30" s="5">
-        <v>46083</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>424</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D31" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E31">
-        <v>55794</v>
+        <v>50288</v>
       </c>
       <c r="F31" t="s">
         <v>107</v>
       </c>
       <c r="G31" s="5">
-        <v>46087</v>
+        <v>46083</v>
       </c>
       <c r="H31" s="5">
         <v>46096</v>
       </c>
       <c r="I31" s="5">
-        <v>46087</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>260</v>
+        <v>509</v>
       </c>
       <c r="D32" t="s">
-        <v>261</v>
+        <v>510</v>
       </c>
       <c r="E32">
-        <v>57687</v>
+        <v>57657</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G32" s="5">
-        <v>45980</v>
+        <v>45964</v>
       </c>
       <c r="H32" s="5">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="I32" s="5">
-        <v>46066</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>262</v>
+        <v>509</v>
       </c>
       <c r="D33" t="s">
-        <v>263</v>
+        <v>510</v>
       </c>
       <c r="E33">
-        <v>57688</v>
+        <v>57657</v>
       </c>
       <c r="F33" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G33" s="5">
-        <v>45980</v>
+        <v>46045</v>
       </c>
       <c r="H33" s="5">
-        <v>46006</v>
+        <v>46068</v>
       </c>
       <c r="I33" s="5">
-        <v>46066</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>264</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="E34">
-        <v>57689</v>
+        <v>56871</v>
       </c>
       <c r="F34" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G34" s="5">
-        <v>45980</v>
+        <v>46029</v>
       </c>
       <c r="H34" s="5">
-        <v>46006</v>
+        <v>46047</v>
       </c>
       <c r="I34" s="5">
-        <v>46066</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>266</v>
+        <v>117</v>
       </c>
       <c r="D35" t="s">
-        <v>267</v>
+        <v>118</v>
       </c>
       <c r="E35">
-        <v>57690</v>
+        <v>50314</v>
       </c>
       <c r="F35" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G35" s="5">
-        <v>45980</v>
+        <v>46029</v>
       </c>
       <c r="H35" s="5">
-        <v>46006</v>
+        <v>46047</v>
       </c>
       <c r="I35" s="5">
-        <v>46066</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>268</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>260</v>
+        <v>422</v>
       </c>
       <c r="D36" t="s">
-        <v>269</v>
+        <v>423</v>
       </c>
       <c r="E36">
-        <v>57564</v>
+        <v>56813</v>
       </c>
       <c r="F36" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G36" s="5">
-        <v>45947</v>
+        <v>46083</v>
       </c>
       <c r="H36" s="5">
-        <v>45976</v>
+        <v>46096</v>
       </c>
       <c r="I36" s="5">
-        <v>46066</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>268</v>
+        <v>511</v>
       </c>
       <c r="C37" t="s">
-        <v>270</v>
+        <v>512</v>
       </c>
       <c r="D37" t="s">
-        <v>271</v>
+        <v>513</v>
       </c>
       <c r="E37">
-        <v>57565</v>
+        <v>57786</v>
       </c>
       <c r="F37" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="G37" s="5">
-        <v>45947</v>
+        <v>46051</v>
       </c>
       <c r="H37" s="5">
-        <v>45976</v>
+        <v>46068</v>
       </c>
       <c r="I37" s="5">
-        <v>46066</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>258</v>
+        <v>514</v>
       </c>
       <c r="B38" t="s">
-        <v>268</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>264</v>
+        <v>515</v>
       </c>
       <c r="D38" t="s">
-        <v>272</v>
+        <v>516</v>
       </c>
       <c r="E38">
-        <v>57566</v>
+        <v>54815</v>
       </c>
       <c r="F38" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G38" s="5">
-        <v>45947</v>
+        <v>46097</v>
       </c>
       <c r="H38" s="5">
-        <v>45976</v>
+        <v>46104</v>
       </c>
       <c r="I38" s="5">
-        <v>46066</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>258</v>
+        <v>517</v>
       </c>
       <c r="B39" t="s">
-        <v>268</v>
+        <v>35</v>
       </c>
       <c r="C39" t="s">
-        <v>266</v>
+        <v>518</v>
       </c>
       <c r="D39" t="s">
-        <v>273</v>
+        <v>519</v>
       </c>
       <c r="E39">
-        <v>57567</v>
+        <v>57674</v>
       </c>
       <c r="F39" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="G39" s="5">
-        <v>45947</v>
+        <v>45974</v>
       </c>
       <c r="H39" s="5">
-        <v>45976</v>
+        <v>45992</v>
       </c>
       <c r="I39" s="5">
-        <v>46066</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>517</v>
       </c>
       <c r="B40" t="s">
         <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>520</v>
       </c>
       <c r="D40" t="s">
-        <v>61</v>
+        <v>521</v>
       </c>
       <c r="E40">
-        <v>57677</v>
+        <v>57672</v>
       </c>
       <c r="F40" t="s">
         <v>10</v>
       </c>
       <c r="G40" s="5">
-        <v>45975</v>
+        <v>45974</v>
       </c>
       <c r="H40" s="5">
         <v>45992</v>
       </c>
       <c r="I40" s="5">
-        <v>46029</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>424</v>
       </c>
       <c r="B41" t="s">
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>274</v>
+        <v>425</v>
       </c>
       <c r="D41" t="s">
-        <v>275</v>
+        <v>426</v>
       </c>
       <c r="E41">
-        <v>57719</v>
+        <v>55794</v>
       </c>
       <c r="F41" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G41" s="5">
-        <v>46006</v>
+        <v>46087</v>
       </c>
       <c r="H41" s="5">
-        <v>46023</v>
+        <v>46096</v>
       </c>
       <c r="I41" s="5">
-        <v>46062</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>424</v>
       </c>
       <c r="B42" t="s">
         <v>35</v>
       </c>
       <c r="C42" t="s">
-        <v>276</v>
+        <v>522</v>
       </c>
       <c r="D42" t="s">
-        <v>277</v>
+        <v>523</v>
       </c>
       <c r="E42">
-        <v>57720</v>
+        <v>50375</v>
       </c>
       <c r="F42" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G42" s="5">
-        <v>46006</v>
+        <v>46087</v>
       </c>
       <c r="H42" s="5">
-        <v>46023</v>
+        <v>46098</v>
       </c>
       <c r="I42" s="5">
-        <v>46062</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="C43" t="s">
-        <v>427</v>
+        <v>260</v>
       </c>
       <c r="D43" t="s">
-        <v>428</v>
+        <v>261</v>
       </c>
       <c r="E43">
-        <v>57849</v>
+        <v>57687</v>
       </c>
       <c r="F43" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="G43" s="5">
-        <v>46087</v>
-      </c>
-      <c r="H43" t="s">
-        <v>65</v>
+        <v>45980</v>
+      </c>
+      <c r="H43" s="5">
+        <v>46006</v>
       </c>
       <c r="I43" s="5">
-        <v>46096</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B44" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="C44" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="E44">
-        <v>57721</v>
+        <v>57688</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G44" s="5">
+        <v>45980</v>
+      </c>
+      <c r="H44" s="5">
         <v>46006</v>
       </c>
-      <c r="H44" s="5">
-        <v>46023</v>
-      </c>
       <c r="I44" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B45" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="C45" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="D45" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="E45">
-        <v>57722</v>
+        <v>57689</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G45" s="5">
+        <v>45980</v>
+      </c>
+      <c r="H45" s="5">
         <v>46006</v>
       </c>
-      <c r="H45" s="5">
-        <v>46023</v>
-      </c>
       <c r="I45" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E46">
-        <v>57723</v>
+        <v>57690</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G46" s="5">
+        <v>45980</v>
+      </c>
+      <c r="H46" s="5">
         <v>46006</v>
       </c>
-      <c r="H46" s="5">
-        <v>46023</v>
-      </c>
       <c r="I46" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="C47" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="D47" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="E47">
-        <v>57724</v>
+        <v>57564</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G47" s="5">
-        <v>46006</v>
+        <v>45947</v>
       </c>
       <c r="H47" s="5">
-        <v>46023</v>
+        <v>45976</v>
       </c>
       <c r="I47" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>270</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>271</v>
       </c>
       <c r="E48">
-        <v>57737</v>
+        <v>57565</v>
       </c>
       <c r="F48" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G48" s="5">
-        <v>46008</v>
-      </c>
-      <c r="H48" t="s">
-        <v>65</v>
+        <v>45947</v>
+      </c>
+      <c r="H48" s="5">
+        <v>45976</v>
       </c>
       <c r="I48" s="5">
-        <v>46027</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>264</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>272</v>
       </c>
       <c r="E49">
-        <v>57765</v>
+        <v>57566</v>
       </c>
       <c r="F49" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G49" s="5">
-        <v>46037</v>
-      </c>
-      <c r="H49" t="s">
-        <v>65</v>
+        <v>45947</v>
+      </c>
+      <c r="H49" s="5">
+        <v>45976</v>
       </c>
       <c r="I49" s="5">
-        <v>46047</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B50" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="C50" t="s">
-        <v>429</v>
+        <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>430</v>
+        <v>273</v>
       </c>
       <c r="E50">
-        <v>57761</v>
+        <v>57567</v>
       </c>
       <c r="F50" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G50" s="5">
-        <v>46037</v>
+        <v>45947</v>
       </c>
       <c r="H50" s="5">
-        <v>46054</v>
+        <v>45976</v>
       </c>
       <c r="I50" s="5">
-        <v>46091</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -4062,13 +4203,13 @@
         <v>35</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E51">
-        <v>57678</v>
+        <v>57677</v>
       </c>
       <c r="F51" t="s">
         <v>10</v>
@@ -4091,25 +4232,25 @@
         <v>35</v>
       </c>
       <c r="C52" t="s">
-        <v>68</v>
+        <v>274</v>
       </c>
       <c r="D52" t="s">
-        <v>69</v>
+        <v>275</v>
       </c>
       <c r="E52">
-        <v>57679</v>
+        <v>57719</v>
       </c>
       <c r="F52" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G52" s="5">
-        <v>45975</v>
+        <v>46006</v>
       </c>
       <c r="H52" s="5">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I52" s="5">
-        <v>46029</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -4120,25 +4261,25 @@
         <v>35</v>
       </c>
       <c r="C53" t="s">
-        <v>70</v>
+        <v>276</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>277</v>
       </c>
       <c r="E53">
-        <v>57735</v>
+        <v>57720</v>
       </c>
       <c r="F53" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="G53" s="5">
-        <v>46007</v>
-      </c>
-      <c r="H53" t="s">
-        <v>65</v>
+        <v>46006</v>
+      </c>
+      <c r="H53" s="5">
+        <v>46023</v>
       </c>
       <c r="I53" s="5">
-        <v>46027</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -4149,25 +4290,25 @@
         <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>286</v>
+        <v>427</v>
       </c>
       <c r="D54" t="s">
-        <v>287</v>
+        <v>428</v>
       </c>
       <c r="E54">
-        <v>57725</v>
+        <v>57849</v>
       </c>
       <c r="F54" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G54" s="5">
-        <v>46006</v>
-      </c>
-      <c r="H54" s="5">
-        <v>46023</v>
+        <v>46087</v>
+      </c>
+      <c r="H54" t="s">
+        <v>65</v>
       </c>
       <c r="I54" s="5">
-        <v>46062</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -4178,13 +4319,13 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D55" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="E55">
-        <v>57726</v>
+        <v>57721</v>
       </c>
       <c r="F55" t="s">
         <v>10</v>
@@ -4207,13 +4348,13 @@
         <v>35</v>
       </c>
       <c r="C56" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="D56" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="E56">
-        <v>57727</v>
+        <v>57722</v>
       </c>
       <c r="F56" t="s">
         <v>10</v>
@@ -4236,13 +4377,13 @@
         <v>35</v>
       </c>
       <c r="C57" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D57" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="E57">
-        <v>57728</v>
+        <v>57723</v>
       </c>
       <c r="F57" t="s">
         <v>10</v>
@@ -4265,25 +4406,25 @@
         <v>35</v>
       </c>
       <c r="C58" t="s">
-        <v>431</v>
+        <v>284</v>
       </c>
       <c r="D58" t="s">
-        <v>432</v>
+        <v>285</v>
       </c>
       <c r="E58">
-        <v>57762</v>
+        <v>57724</v>
       </c>
       <c r="F58" t="s">
         <v>10</v>
       </c>
       <c r="G58" s="5">
-        <v>46037</v>
+        <v>46006</v>
       </c>
       <c r="H58" s="5">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="I58" s="5">
-        <v>46091</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -4294,25 +4435,25 @@
         <v>35</v>
       </c>
       <c r="C59" t="s">
-        <v>294</v>
+        <v>62</v>
       </c>
       <c r="D59" t="s">
-        <v>295</v>
+        <v>63</v>
       </c>
       <c r="E59">
-        <v>57729</v>
+        <v>57737</v>
       </c>
       <c r="F59" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G59" s="5">
-        <v>46006</v>
-      </c>
-      <c r="H59" s="5">
-        <v>46023</v>
+        <v>46008</v>
+      </c>
+      <c r="H59" t="s">
+        <v>65</v>
       </c>
       <c r="I59" s="5">
-        <v>46062</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -4323,25 +4464,25 @@
         <v>35</v>
       </c>
       <c r="C60" t="s">
-        <v>296</v>
+        <v>62</v>
       </c>
       <c r="D60" t="s">
-        <v>297</v>
+        <v>63</v>
       </c>
       <c r="E60">
-        <v>57730</v>
+        <v>57765</v>
       </c>
       <c r="F60" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G60" s="5">
-        <v>46006</v>
-      </c>
-      <c r="H60" s="5">
-        <v>46023</v>
+        <v>46037</v>
+      </c>
+      <c r="H60" t="s">
+        <v>65</v>
       </c>
       <c r="I60" s="5">
-        <v>46062</v>
+        <v>46047</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -4352,25 +4493,25 @@
         <v>35</v>
       </c>
       <c r="C61" t="s">
-        <v>296</v>
+        <v>429</v>
       </c>
       <c r="D61" t="s">
-        <v>297</v>
+        <v>430</v>
       </c>
       <c r="E61">
-        <v>57807</v>
+        <v>57761</v>
       </c>
       <c r="F61" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G61" s="5">
-        <v>46073</v>
-      </c>
-      <c r="H61" t="s">
-        <v>65</v>
+        <v>46037</v>
+      </c>
+      <c r="H61" s="5">
+        <v>46054</v>
       </c>
       <c r="I61" s="5">
-        <v>46082</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -4381,25 +4522,25 @@
         <v>35</v>
       </c>
       <c r="C62" t="s">
-        <v>433</v>
+        <v>66</v>
       </c>
       <c r="D62" t="s">
-        <v>434</v>
+        <v>67</v>
       </c>
       <c r="E62">
-        <v>57763</v>
+        <v>57678</v>
       </c>
       <c r="F62" t="s">
         <v>10</v>
       </c>
       <c r="G62" s="5">
-        <v>46037</v>
+        <v>45975</v>
       </c>
       <c r="H62" s="5">
-        <v>46054</v>
+        <v>45992</v>
       </c>
       <c r="I62" s="5">
-        <v>46091</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -4410,25 +4551,25 @@
         <v>35</v>
       </c>
       <c r="C63" t="s">
-        <v>298</v>
+        <v>68</v>
       </c>
       <c r="D63" t="s">
-        <v>299</v>
+        <v>69</v>
       </c>
       <c r="E63">
-        <v>57731</v>
+        <v>57679</v>
       </c>
       <c r="F63" t="s">
         <v>10</v>
       </c>
       <c r="G63" s="5">
-        <v>46006</v>
+        <v>45975</v>
       </c>
       <c r="H63" s="5">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="I63" s="5">
-        <v>46062</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -4439,25 +4580,25 @@
         <v>35</v>
       </c>
       <c r="C64" t="s">
-        <v>435</v>
+        <v>70</v>
       </c>
       <c r="D64" t="s">
-        <v>436</v>
+        <v>71</v>
       </c>
       <c r="E64">
-        <v>57764</v>
+        <v>57735</v>
       </c>
       <c r="F64" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G64" s="5">
-        <v>46037</v>
-      </c>
-      <c r="H64" s="5">
-        <v>46054</v>
+        <v>46007</v>
+      </c>
+      <c r="H64" t="s">
+        <v>65</v>
       </c>
       <c r="I64" s="5">
-        <v>46091</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -4468,399 +4609,399 @@
         <v>35</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>286</v>
       </c>
       <c r="D65" t="s">
-        <v>73</v>
+        <v>287</v>
       </c>
       <c r="E65">
-        <v>57680</v>
+        <v>57725</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G65" s="5">
-        <v>45975</v>
+        <v>46006</v>
       </c>
       <c r="H65" s="5">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I65" s="5">
-        <v>46029</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B66" t="s">
-        <v>300</v>
+        <v>35</v>
       </c>
       <c r="C66" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D66" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="E66">
-        <v>57666</v>
+        <v>57726</v>
       </c>
       <c r="F66" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="5">
-        <v>45966</v>
+        <v>46006</v>
       </c>
       <c r="H66" s="5">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I66" s="5">
-        <v>46057</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B67" t="s">
-        <v>300</v>
+        <v>35</v>
       </c>
       <c r="C67" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="D67" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="E67">
-        <v>53313</v>
+        <v>57727</v>
       </c>
       <c r="F67" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G67" s="5">
-        <v>46057</v>
+        <v>46006</v>
       </c>
       <c r="H67" s="5">
+        <v>46023</v>
+      </c>
+      <c r="I67" s="5">
         <v>46062</v>
-      </c>
-      <c r="I67" s="5">
-        <v>46057</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B68" t="s">
-        <v>437</v>
+        <v>35</v>
       </c>
       <c r="C68" t="s">
-        <v>438</v>
+        <v>292</v>
       </c>
       <c r="D68" t="s">
-        <v>439</v>
+        <v>293</v>
       </c>
       <c r="E68">
-        <v>57815</v>
+        <v>57728</v>
       </c>
       <c r="F68" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G68" s="5">
-        <v>46078</v>
-      </c>
-      <c r="H68" t="s">
-        <v>65</v>
+        <v>46006</v>
+      </c>
+      <c r="H68" s="5">
+        <v>46023</v>
       </c>
       <c r="I68" s="5">
-        <v>46083</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B69" t="s">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="C69" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="D69" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="E69">
-        <v>50710</v>
+        <v>57728</v>
       </c>
       <c r="F69" t="s">
         <v>107</v>
       </c>
       <c r="G69" s="5">
-        <v>46062</v>
+        <v>46097</v>
       </c>
       <c r="H69" s="5">
-        <v>46066</v>
+        <v>46098</v>
       </c>
       <c r="I69" s="5">
-        <v>46062</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="C70" t="s">
-        <v>76</v>
+        <v>524</v>
       </c>
       <c r="D70" t="s">
-        <v>77</v>
+        <v>525</v>
       </c>
       <c r="E70">
-        <v>57545</v>
+        <v>55856</v>
       </c>
       <c r="F70" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G70" s="5">
-        <v>45939</v>
+        <v>46097</v>
       </c>
       <c r="H70" s="5">
-        <v>45962</v>
+        <v>46098</v>
       </c>
       <c r="I70" s="5">
-        <v>46034</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B71" t="s">
         <v>35</v>
       </c>
       <c r="C71" t="s">
-        <v>376</v>
+        <v>431</v>
       </c>
       <c r="D71" t="s">
-        <v>377</v>
+        <v>432</v>
       </c>
       <c r="E71">
-        <v>50789</v>
+        <v>57762</v>
       </c>
       <c r="F71" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="G71" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H71" t="s">
-        <v>358</v>
+        <v>46037</v>
+      </c>
+      <c r="H71" s="5">
+        <v>46054</v>
       </c>
       <c r="I71" s="5">
-        <v>46078</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B72" t="s">
         <v>35</v>
       </c>
       <c r="C72" t="s">
-        <v>378</v>
+        <v>294</v>
       </c>
       <c r="D72" t="s">
-        <v>379</v>
+        <v>295</v>
       </c>
       <c r="E72">
-        <v>50793</v>
+        <v>57729</v>
       </c>
       <c r="F72" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="G72" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H72" t="s">
-        <v>358</v>
+        <v>46006</v>
+      </c>
+      <c r="H72" s="5">
+        <v>46023</v>
       </c>
       <c r="I72" s="5">
-        <v>46078</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B73" t="s">
         <v>35</v>
       </c>
       <c r="C73" t="s">
-        <v>380</v>
+        <v>294</v>
       </c>
       <c r="D73" t="s">
-        <v>381</v>
+        <v>295</v>
       </c>
       <c r="E73">
-        <v>50790</v>
+        <v>57729</v>
       </c>
       <c r="F73" t="s">
-        <v>357</v>
+        <v>107</v>
       </c>
       <c r="G73" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H73" t="s">
-        <v>358</v>
+        <v>46097</v>
+      </c>
+      <c r="H73" s="5">
+        <v>46098</v>
       </c>
       <c r="I73" s="5">
-        <v>46078</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B74" t="s">
         <v>35</v>
       </c>
       <c r="C74" t="s">
-        <v>382</v>
+        <v>296</v>
       </c>
       <c r="D74" t="s">
-        <v>383</v>
+        <v>297</v>
       </c>
       <c r="E74">
-        <v>50799</v>
+        <v>57730</v>
       </c>
       <c r="F74" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="G74" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H74" t="s">
-        <v>358</v>
+        <v>46006</v>
+      </c>
+      <c r="H74" s="5">
+        <v>46023</v>
       </c>
       <c r="I74" s="5">
-        <v>46078</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B75" t="s">
         <v>35</v>
       </c>
       <c r="C75" t="s">
-        <v>384</v>
+        <v>296</v>
       </c>
       <c r="D75" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="E75">
-        <v>50803</v>
+        <v>57807</v>
       </c>
       <c r="F75" t="s">
-        <v>357</v>
+        <v>64</v>
       </c>
       <c r="G75" s="5">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="H75" t="s">
-        <v>358</v>
+        <v>65</v>
       </c>
       <c r="I75" s="5">
-        <v>46078</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="B76" t="s">
         <v>35</v>
       </c>
       <c r="C76" t="s">
-        <v>120</v>
+        <v>433</v>
       </c>
       <c r="D76" t="s">
-        <v>121</v>
+        <v>434</v>
       </c>
       <c r="E76">
-        <v>50812</v>
+        <v>57763</v>
       </c>
       <c r="F76" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G76" s="5">
-        <v>46028</v>
+        <v>46037</v>
       </c>
       <c r="H76" s="5">
-        <v>46047</v>
+        <v>46054</v>
       </c>
       <c r="I76" s="5">
-        <v>46028</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="B77" t="s">
-        <v>440</v>
+        <v>35</v>
       </c>
       <c r="C77" t="s">
-        <v>441</v>
+        <v>298</v>
       </c>
       <c r="D77" t="s">
-        <v>442</v>
+        <v>299</v>
       </c>
       <c r="E77">
-        <v>53490</v>
+        <v>57731</v>
       </c>
       <c r="F77" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G77" s="5">
-        <v>46091</v>
+        <v>46006</v>
       </c>
       <c r="H77" s="5">
-        <v>46096</v>
+        <v>46023</v>
       </c>
       <c r="I77" s="5">
-        <v>46091</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="B78" t="s">
-        <v>440</v>
+        <v>35</v>
       </c>
       <c r="C78" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="D78" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E78">
-        <v>54546</v>
+        <v>57764</v>
       </c>
       <c r="F78" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G78" s="5">
-        <v>46091</v>
+        <v>46037</v>
       </c>
       <c r="H78" s="5">
-        <v>46096</v>
+        <v>46054</v>
       </c>
       <c r="I78" s="5">
         <v>46091</v>
@@ -4868,698 +5009,698 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="C79" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="D79" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="E79">
-        <v>57692</v>
+        <v>57680</v>
       </c>
       <c r="F79" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G79" s="5">
-        <v>45987</v>
+        <v>45975</v>
       </c>
       <c r="H79" s="5">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="I79" s="5">
-        <v>46043</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="B80" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="C80" t="s">
-        <v>125</v>
+        <v>526</v>
       </c>
       <c r="D80" t="s">
-        <v>126</v>
+        <v>527</v>
       </c>
       <c r="E80">
-        <v>57693</v>
+        <v>56374</v>
       </c>
       <c r="F80" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G80" s="5">
-        <v>45987</v>
+        <v>46097</v>
       </c>
       <c r="H80" s="5">
-        <v>46006</v>
+        <v>46098</v>
       </c>
       <c r="I80" s="5">
-        <v>46043</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="B81" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="C81" t="s">
-        <v>127</v>
+        <v>528</v>
       </c>
       <c r="D81" t="s">
-        <v>128</v>
+        <v>529</v>
       </c>
       <c r="E81">
-        <v>57694</v>
+        <v>57186</v>
       </c>
       <c r="F81" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G81" s="5">
-        <v>45987</v>
+        <v>46097</v>
       </c>
       <c r="H81" s="5">
-        <v>46006</v>
+        <v>46098</v>
       </c>
       <c r="I81" s="5">
-        <v>46043</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C82" t="s">
-        <v>80</v>
+        <v>530</v>
       </c>
       <c r="D82" t="s">
-        <v>81</v>
+        <v>531</v>
       </c>
       <c r="E82">
-        <v>57684</v>
+        <v>52865</v>
       </c>
       <c r="F82" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G82" s="5">
-        <v>45975</v>
+        <v>46097</v>
       </c>
       <c r="H82" s="5">
-        <v>45992</v>
+        <v>46098</v>
       </c>
       <c r="I82" s="5">
-        <v>46035</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="C83" t="s">
-        <v>129</v>
+        <v>301</v>
       </c>
       <c r="D83" t="s">
-        <v>130</v>
+        <v>302</v>
       </c>
       <c r="E83">
-        <v>57696</v>
+        <v>57666</v>
       </c>
       <c r="F83" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="5">
-        <v>45989</v>
+        <v>45966</v>
       </c>
       <c r="H83" s="5">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="I83" s="5">
-        <v>46050</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="C84" t="s">
-        <v>129</v>
+        <v>303</v>
       </c>
       <c r="D84" t="s">
-        <v>130</v>
+        <v>304</v>
       </c>
       <c r="E84">
-        <v>57696</v>
+        <v>53313</v>
       </c>
       <c r="F84" t="s">
         <v>107</v>
       </c>
       <c r="G84" s="5">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="H84" s="5">
         <v>46062</v>
       </c>
       <c r="I84" s="5">
-        <v>46059</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="B85" t="s">
-        <v>35</v>
+        <v>437</v>
       </c>
       <c r="C85" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D85" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="E85">
-        <v>57746</v>
+        <v>57815</v>
       </c>
       <c r="F85" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="G85" s="5">
-        <v>46020</v>
-      </c>
-      <c r="H85" s="5">
-        <v>46037</v>
+        <v>46078</v>
+      </c>
+      <c r="H85" t="s">
+        <v>65</v>
       </c>
       <c r="I85" s="5">
-        <v>46097</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="B86" t="s">
-        <v>131</v>
+        <v>305</v>
       </c>
       <c r="C86" t="s">
-        <v>123</v>
+        <v>306</v>
       </c>
       <c r="D86" t="s">
-        <v>132</v>
+        <v>307</v>
       </c>
       <c r="E86">
-        <v>57616</v>
+        <v>50710</v>
       </c>
       <c r="F86" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G86" s="5">
-        <v>45954</v>
+        <v>46062</v>
       </c>
       <c r="H86" s="5">
-        <v>45976</v>
+        <v>46066</v>
       </c>
       <c r="I86" s="5">
-        <v>46048</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="B87" t="s">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="C87" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="D87" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E87">
-        <v>57588</v>
+        <v>57545</v>
       </c>
       <c r="F87" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="G87" s="5">
-        <v>45951</v>
+        <v>45939</v>
       </c>
       <c r="H87" s="5">
-        <v>45976</v>
+        <v>45962</v>
       </c>
       <c r="I87" s="5">
-        <v>46048</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="B88" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C88" t="s">
-        <v>135</v>
+        <v>376</v>
       </c>
       <c r="D88" t="s">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="E88">
-        <v>57589</v>
+        <v>50789</v>
       </c>
       <c r="F88" t="s">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="G88" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H88" s="5">
-        <v>45976</v>
+        <v>46077</v>
+      </c>
+      <c r="H88" t="s">
+        <v>358</v>
       </c>
       <c r="I88" s="5">
-        <v>46048</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="B89" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C89" t="s">
-        <v>137</v>
+        <v>378</v>
       </c>
       <c r="D89" t="s">
-        <v>138</v>
+        <v>379</v>
       </c>
       <c r="E89">
-        <v>57640</v>
+        <v>50793</v>
       </c>
       <c r="F89" t="s">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="G89" s="5">
-        <v>45963</v>
-      </c>
-      <c r="H89" s="5">
-        <v>45992</v>
+        <v>46077</v>
+      </c>
+      <c r="H89" t="s">
+        <v>358</v>
       </c>
       <c r="I89" s="5">
-        <v>46048</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="B90" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C90" t="s">
-        <v>139</v>
+        <v>380</v>
       </c>
       <c r="D90" t="s">
-        <v>140</v>
+        <v>381</v>
       </c>
       <c r="E90">
-        <v>57584</v>
+        <v>50790</v>
       </c>
       <c r="F90" t="s">
-        <v>141</v>
+        <v>357</v>
       </c>
       <c r="G90" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H90" s="5">
-        <v>45976</v>
+        <v>46077</v>
+      </c>
+      <c r="H90" t="s">
+        <v>358</v>
       </c>
       <c r="I90" s="5">
-        <v>46048</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="B91" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C91" t="s">
-        <v>142</v>
+        <v>382</v>
       </c>
       <c r="D91" t="s">
-        <v>143</v>
+        <v>383</v>
       </c>
       <c r="E91">
-        <v>57585</v>
+        <v>50799</v>
       </c>
       <c r="F91" t="s">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="G91" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H91" s="5">
-        <v>45976</v>
+        <v>46077</v>
+      </c>
+      <c r="H91" t="s">
+        <v>358</v>
       </c>
       <c r="I91" s="5">
-        <v>46048</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="B92" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C92" t="s">
-        <v>144</v>
+        <v>384</v>
       </c>
       <c r="D92" t="s">
-        <v>145</v>
+        <v>385</v>
       </c>
       <c r="E92">
-        <v>57586</v>
+        <v>50803</v>
       </c>
       <c r="F92" t="s">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="G92" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H92" s="5">
-        <v>45976</v>
+        <v>46077</v>
+      </c>
+      <c r="H92" t="s">
+        <v>358</v>
       </c>
       <c r="I92" s="5">
-        <v>46048</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="B93" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="C93" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="D93" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="E93">
-        <v>57587</v>
+        <v>50812</v>
       </c>
       <c r="F93" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G93" s="5">
-        <v>45951</v>
+        <v>46028</v>
       </c>
       <c r="H93" s="5">
-        <v>45976</v>
+        <v>46047</v>
       </c>
       <c r="I93" s="5">
-        <v>46048</v>
+        <v>46028</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B94" t="s">
-        <v>308</v>
+        <v>440</v>
       </c>
       <c r="C94" t="s">
-        <v>309</v>
+        <v>441</v>
       </c>
       <c r="D94" t="s">
-        <v>310</v>
+        <v>442</v>
       </c>
       <c r="E94">
-        <v>57777</v>
+        <v>53490</v>
       </c>
       <c r="F94" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G94" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H94" t="s">
-        <v>65</v>
+        <v>46091</v>
+      </c>
+      <c r="H94" s="5">
+        <v>46096</v>
       </c>
       <c r="I94" s="5">
-        <v>46055</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B95" t="s">
-        <v>308</v>
+        <v>440</v>
       </c>
       <c r="C95" t="s">
-        <v>311</v>
+        <v>443</v>
       </c>
       <c r="D95" t="s">
-        <v>312</v>
+        <v>444</v>
       </c>
       <c r="E95">
-        <v>57778</v>
+        <v>54546</v>
       </c>
       <c r="F95" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G95" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H95" t="s">
-        <v>65</v>
+        <v>46091</v>
+      </c>
+      <c r="H95" s="5">
+        <v>46096</v>
       </c>
       <c r="I95" s="5">
-        <v>46055</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B96" t="s">
-        <v>308</v>
+        <v>122</v>
       </c>
       <c r="C96" t="s">
-        <v>313</v>
+        <v>123</v>
       </c>
       <c r="D96" t="s">
-        <v>314</v>
+        <v>124</v>
       </c>
       <c r="E96">
-        <v>57775</v>
+        <v>57692</v>
       </c>
       <c r="F96" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G96" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H96" t="s">
-        <v>65</v>
+        <v>45987</v>
+      </c>
+      <c r="H96" s="5">
+        <v>46006</v>
       </c>
       <c r="I96" s="5">
-        <v>46055</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>308</v>
+        <v>122</v>
       </c>
       <c r="C97" t="s">
-        <v>315</v>
+        <v>125</v>
       </c>
       <c r="D97" t="s">
-        <v>316</v>
+        <v>126</v>
       </c>
       <c r="E97">
-        <v>57776</v>
+        <v>57693</v>
       </c>
       <c r="F97" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G97" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H97" t="s">
-        <v>65</v>
+        <v>45987</v>
+      </c>
+      <c r="H97" s="5">
+        <v>46006</v>
       </c>
       <c r="I97" s="5">
-        <v>46055</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>317</v>
+        <v>122</v>
       </c>
       <c r="C98" t="s">
-        <v>318</v>
+        <v>127</v>
       </c>
       <c r="D98" t="s">
-        <v>319</v>
+        <v>128</v>
       </c>
       <c r="E98">
-        <v>57782</v>
+        <v>57694</v>
       </c>
       <c r="F98" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G98" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H98" t="s">
-        <v>65</v>
+        <v>45987</v>
+      </c>
+      <c r="H98" s="5">
+        <v>46006</v>
       </c>
       <c r="I98" s="5">
-        <v>46055</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B99" t="s">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="C99" t="s">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="D99" t="s">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="E99">
-        <v>57780</v>
+        <v>57684</v>
       </c>
       <c r="F99" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G99" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H99" t="s">
-        <v>65</v>
+        <v>45975</v>
+      </c>
+      <c r="H99" s="5">
+        <v>45992</v>
       </c>
       <c r="I99" s="5">
-        <v>46055</v>
+        <v>46035</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B100" t="s">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="C100" t="s">
-        <v>386</v>
+        <v>532</v>
       </c>
       <c r="D100" t="s">
-        <v>387</v>
+        <v>533</v>
       </c>
       <c r="E100">
-        <v>57703</v>
+        <v>57788</v>
       </c>
       <c r="F100" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G100" s="5">
-        <v>45993</v>
+        <v>46055</v>
       </c>
       <c r="H100" s="5">
-        <v>46023</v>
+        <v>46068</v>
       </c>
       <c r="I100" s="5">
-        <v>46070</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B101" t="s">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="C101" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="D101" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="E101">
-        <v>57781</v>
+        <v>57696</v>
       </c>
       <c r="F101" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G101" s="5">
-        <v>46083</v>
+        <v>45989</v>
       </c>
       <c r="H101" s="5">
-        <v>46096</v>
+        <v>46006</v>
       </c>
       <c r="I101" s="5">
-        <v>46083</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B102" t="s">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="C102" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="D102" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="E102">
-        <v>57781</v>
+        <v>57696</v>
       </c>
       <c r="F102" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G102" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H102" t="s">
-        <v>65</v>
+        <v>46059</v>
+      </c>
+      <c r="H102" s="5">
+        <v>46062</v>
       </c>
       <c r="I102" s="5">
-        <v>46052</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -5567,28 +5708,28 @@
         <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="C103" t="s">
-        <v>152</v>
+        <v>445</v>
       </c>
       <c r="D103" t="s">
-        <v>153</v>
+        <v>446</v>
       </c>
       <c r="E103">
-        <v>57618</v>
+        <v>57746</v>
       </c>
       <c r="F103" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G103" s="5">
-        <v>45954</v>
+        <v>46020</v>
       </c>
       <c r="H103" s="5">
-        <v>45976</v>
+        <v>46037</v>
       </c>
       <c r="I103" s="5">
-        <v>46070</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -5596,28 +5737,28 @@
         <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="C104" t="s">
-        <v>322</v>
+        <v>123</v>
       </c>
       <c r="D104" t="s">
-        <v>323</v>
+        <v>132</v>
       </c>
       <c r="E104">
-        <v>55992</v>
+        <v>57616</v>
       </c>
       <c r="F104" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G104" s="5">
-        <v>46057</v>
+        <v>45954</v>
       </c>
       <c r="H104" s="5">
-        <v>46062</v>
+        <v>45976</v>
       </c>
       <c r="I104" s="5">
-        <v>46057</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -5625,28 +5766,28 @@
         <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="C105" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="D105" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="E105">
-        <v>57641</v>
+        <v>57588</v>
       </c>
       <c r="F105" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="G105" s="5">
-        <v>45963</v>
+        <v>45951</v>
       </c>
       <c r="H105" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I105" s="5">
-        <v>46042</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -5654,28 +5795,28 @@
         <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="C106" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D106" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="E106">
-        <v>57645</v>
+        <v>57589</v>
       </c>
       <c r="F106" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="5">
-        <v>45964</v>
+        <v>45951</v>
       </c>
       <c r="H106" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I106" s="5">
-        <v>46042</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -5683,22 +5824,22 @@
         <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C107" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="D107" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="E107">
-        <v>57646</v>
+        <v>57640</v>
       </c>
       <c r="F107" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="5">
-        <v>45964</v>
+        <v>45963</v>
       </c>
       <c r="H107" s="5">
         <v>45992</v>
@@ -5712,25 +5853,25 @@
         <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="D108" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="E108">
-        <v>57647</v>
+        <v>57584</v>
       </c>
       <c r="F108" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="G108" s="5">
-        <v>45964</v>
+        <v>45951</v>
       </c>
       <c r="H108" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I108" s="5">
         <v>46048</v>
@@ -5741,25 +5882,25 @@
         <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="C109" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="D109" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="E109">
-        <v>57648</v>
+        <v>57585</v>
       </c>
       <c r="F109" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G109" s="5">
-        <v>45964</v>
+        <v>45951</v>
       </c>
       <c r="H109" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I109" s="5">
         <v>46048</v>
@@ -5770,28 +5911,28 @@
         <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="C110" t="s">
-        <v>324</v>
+        <v>144</v>
       </c>
       <c r="D110" t="s">
-        <v>325</v>
+        <v>145</v>
       </c>
       <c r="E110">
-        <v>56446</v>
+        <v>57586</v>
       </c>
       <c r="F110" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="G110" s="5">
-        <v>46038</v>
+        <v>45951</v>
       </c>
       <c r="H110" s="5">
-        <v>46055</v>
+        <v>45976</v>
       </c>
       <c r="I110" s="5">
-        <v>46038</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -5799,28 +5940,28 @@
         <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="C111" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D111" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="E111">
-        <v>57652</v>
+        <v>57587</v>
       </c>
       <c r="F111" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="G111" s="5">
-        <v>45964</v>
+        <v>45951</v>
       </c>
       <c r="H111" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I111" s="5">
-        <v>46042</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -5828,28 +5969,28 @@
         <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>167</v>
+        <v>308</v>
       </c>
       <c r="C112" t="s">
-        <v>170</v>
+        <v>309</v>
       </c>
       <c r="D112" t="s">
-        <v>171</v>
+        <v>310</v>
       </c>
       <c r="E112">
-        <v>57653</v>
+        <v>57777</v>
       </c>
       <c r="F112" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="G112" s="5">
-        <v>45964</v>
-      </c>
-      <c r="H112" s="5">
-        <v>45992</v>
+        <v>46049</v>
+      </c>
+      <c r="H112" t="s">
+        <v>65</v>
       </c>
       <c r="I112" s="5">
-        <v>46042</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -5857,28 +5998,28 @@
         <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>167</v>
+        <v>308</v>
       </c>
       <c r="C113" t="s">
-        <v>172</v>
+        <v>311</v>
       </c>
       <c r="D113" t="s">
-        <v>173</v>
+        <v>312</v>
       </c>
       <c r="E113">
-        <v>57579</v>
+        <v>57778</v>
       </c>
       <c r="F113" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G113" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H113" s="5">
-        <v>45976</v>
+        <v>46049</v>
+      </c>
+      <c r="H113" t="s">
+        <v>65</v>
       </c>
       <c r="I113" s="5">
-        <v>46042</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -5886,28 +6027,28 @@
         <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>388</v>
+        <v>308</v>
       </c>
       <c r="C114" t="s">
-        <v>447</v>
+        <v>313</v>
       </c>
       <c r="D114" t="s">
-        <v>448</v>
+        <v>314</v>
       </c>
       <c r="E114">
-        <v>56879</v>
+        <v>57775</v>
       </c>
       <c r="F114" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G114" s="5">
-        <v>46083</v>
-      </c>
-      <c r="H114" s="5">
-        <v>46096</v>
+        <v>46049</v>
+      </c>
+      <c r="H114" t="s">
+        <v>65</v>
       </c>
       <c r="I114" s="5">
-        <v>46083</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -5915,28 +6056,28 @@
         <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>388</v>
+        <v>308</v>
       </c>
       <c r="C115" t="s">
-        <v>389</v>
+        <v>315</v>
       </c>
       <c r="D115" t="s">
-        <v>390</v>
+        <v>316</v>
       </c>
       <c r="E115">
-        <v>57659</v>
+        <v>57776</v>
       </c>
       <c r="F115" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G115" s="5">
-        <v>45964</v>
-      </c>
-      <c r="H115" s="5">
-        <v>45992</v>
+        <v>46049</v>
+      </c>
+      <c r="H115" t="s">
+        <v>65</v>
       </c>
       <c r="I115" s="5">
-        <v>46078</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -5944,28 +6085,28 @@
         <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>174</v>
+        <v>317</v>
       </c>
       <c r="C116" t="s">
-        <v>449</v>
+        <v>318</v>
       </c>
       <c r="D116" t="s">
-        <v>450</v>
+        <v>319</v>
       </c>
       <c r="E116">
-        <v>55922</v>
+        <v>57782</v>
       </c>
       <c r="F116" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G116" s="5">
-        <v>46083</v>
-      </c>
-      <c r="H116" s="5">
-        <v>46096</v>
+        <v>46049</v>
+      </c>
+      <c r="H116" t="s">
+        <v>65</v>
       </c>
       <c r="I116" s="5">
-        <v>46083</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -5973,28 +6114,28 @@
         <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="C117" t="s">
-        <v>175</v>
+        <v>320</v>
       </c>
       <c r="D117" t="s">
-        <v>176</v>
+        <v>321</v>
       </c>
       <c r="E117">
-        <v>57238</v>
+        <v>57780</v>
       </c>
       <c r="F117" t="s">
-        <v>141</v>
+        <v>64</v>
       </c>
       <c r="G117" s="5">
-        <v>45817</v>
-      </c>
-      <c r="H117" s="5">
-        <v>45839</v>
+        <v>46049</v>
+      </c>
+      <c r="H117" t="s">
+        <v>65</v>
       </c>
       <c r="I117" s="5">
-        <v>46048</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -6002,28 +6143,28 @@
         <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="C118" t="s">
-        <v>175</v>
+        <v>386</v>
       </c>
       <c r="D118" t="s">
-        <v>176</v>
+        <v>387</v>
       </c>
       <c r="E118">
-        <v>57238</v>
+        <v>57703</v>
       </c>
       <c r="F118" t="s">
-        <v>177</v>
+        <v>10</v>
       </c>
       <c r="G118" s="5">
-        <v>45951</v>
+        <v>45993</v>
       </c>
       <c r="H118" s="5">
-        <v>45976</v>
+        <v>46023</v>
       </c>
       <c r="I118" s="5">
-        <v>46048</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -6031,28 +6172,28 @@
         <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="C119" t="s">
-        <v>391</v>
+        <v>149</v>
       </c>
       <c r="D119" t="s">
-        <v>392</v>
+        <v>150</v>
       </c>
       <c r="E119">
-        <v>57700</v>
+        <v>57781</v>
       </c>
       <c r="F119" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G119" s="5">
-        <v>45992</v>
+        <v>46083</v>
       </c>
       <c r="H119" s="5">
-        <v>46006</v>
+        <v>46096</v>
       </c>
       <c r="I119" s="5">
-        <v>46070</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -6060,28 +6201,28 @@
         <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="C120" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D120" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E120">
-        <v>57583</v>
+        <v>57781</v>
       </c>
       <c r="F120" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G120" s="5">
-        <v>45951</v>
-      </c>
-      <c r="H120" s="5">
-        <v>45976</v>
+        <v>46049</v>
+      </c>
+      <c r="H120" t="s">
+        <v>65</v>
       </c>
       <c r="I120" s="5">
-        <v>46042</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -6089,28 +6230,28 @@
         <v>17</v>
       </c>
       <c r="B121" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="C121" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="D121" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E121">
-        <v>57581</v>
+        <v>57618</v>
       </c>
       <c r="F121" t="s">
         <v>10</v>
       </c>
       <c r="G121" s="5">
-        <v>45951</v>
+        <v>45954</v>
       </c>
       <c r="H121" s="5">
         <v>45976</v>
       </c>
       <c r="I121" s="5">
-        <v>46042</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -6118,28 +6259,28 @@
         <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="C122" t="s">
-        <v>389</v>
+        <v>322</v>
       </c>
       <c r="D122" t="s">
-        <v>393</v>
+        <v>323</v>
       </c>
       <c r="E122">
-        <v>57658</v>
+        <v>55992</v>
       </c>
       <c r="F122" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G122" s="5">
-        <v>45964</v>
+        <v>46057</v>
       </c>
       <c r="H122" s="5">
-        <v>45992</v>
+        <v>46062</v>
       </c>
       <c r="I122" s="5">
-        <v>46078</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -6147,28 +6288,28 @@
         <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="C123" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="D123" t="s">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="E123">
-        <v>57736</v>
+        <v>57641</v>
       </c>
       <c r="F123" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="G123" s="5">
-        <v>46007</v>
-      </c>
-      <c r="H123" t="s">
-        <v>65</v>
+        <v>45963</v>
+      </c>
+      <c r="H123" s="5">
+        <v>45992</v>
       </c>
       <c r="I123" s="5">
-        <v>46027</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -6176,28 +6317,28 @@
         <v>17</v>
       </c>
       <c r="B124" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="C124" t="s">
-        <v>451</v>
+        <v>158</v>
       </c>
       <c r="D124" t="s">
-        <v>452</v>
+        <v>159</v>
       </c>
       <c r="E124">
-        <v>57440</v>
+        <v>57645</v>
       </c>
       <c r="F124" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G124" s="5">
-        <v>46083</v>
+        <v>45964</v>
       </c>
       <c r="H124" s="5">
-        <v>46096</v>
+        <v>45992</v>
       </c>
       <c r="I124" s="5">
-        <v>46083</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -6205,28 +6346,28 @@
         <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="C125" t="s">
-        <v>453</v>
+        <v>161</v>
       </c>
       <c r="D125" t="s">
-        <v>454</v>
+        <v>162</v>
       </c>
       <c r="E125">
-        <v>57829</v>
+        <v>57646</v>
       </c>
       <c r="F125" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G125" s="5">
-        <v>46083</v>
-      </c>
-      <c r="H125" t="s">
-        <v>65</v>
+        <v>45964</v>
+      </c>
+      <c r="H125" s="5">
+        <v>45992</v>
       </c>
       <c r="I125" s="5">
-        <v>46096</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -6234,28 +6375,28 @@
         <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="C126" t="s">
-        <v>455</v>
+        <v>163</v>
       </c>
       <c r="D126" t="s">
-        <v>456</v>
+        <v>164</v>
       </c>
       <c r="E126">
-        <v>57830</v>
+        <v>57647</v>
       </c>
       <c r="F126" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G126" s="5">
-        <v>46083</v>
-      </c>
-      <c r="H126" t="s">
-        <v>65</v>
+        <v>45964</v>
+      </c>
+      <c r="H126" s="5">
+        <v>45992</v>
       </c>
       <c r="I126" s="5">
-        <v>46096</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -6263,28 +6404,28 @@
         <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="C127" t="s">
-        <v>457</v>
+        <v>165</v>
       </c>
       <c r="D127" t="s">
-        <v>458</v>
+        <v>166</v>
       </c>
       <c r="E127">
-        <v>55583</v>
+        <v>57648</v>
       </c>
       <c r="F127" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G127" s="5">
-        <v>46083</v>
+        <v>45964</v>
       </c>
       <c r="H127" s="5">
-        <v>46096</v>
+        <v>45992</v>
       </c>
       <c r="I127" s="5">
-        <v>46083</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -6292,28 +6433,28 @@
         <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C128" t="s">
-        <v>184</v>
+        <v>324</v>
       </c>
       <c r="D128" t="s">
-        <v>185</v>
+        <v>325</v>
       </c>
       <c r="E128">
-        <v>57642</v>
+        <v>56446</v>
       </c>
       <c r="F128" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G128" s="5">
-        <v>45963</v>
+        <v>46038</v>
       </c>
       <c r="H128" s="5">
-        <v>45992</v>
+        <v>46055</v>
       </c>
       <c r="I128" s="5">
-        <v>46048</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
@@ -6321,16 +6462,16 @@
         <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C129" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="D129" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="E129">
-        <v>57655</v>
+        <v>57652</v>
       </c>
       <c r="F129" t="s">
         <v>10</v>
@@ -6342,7 +6483,7 @@
         <v>45992</v>
       </c>
       <c r="I129" s="5">
-        <v>46048</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -6350,16 +6491,16 @@
         <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C130" t="s">
-        <v>394</v>
+        <v>534</v>
       </c>
       <c r="D130" t="s">
-        <v>395</v>
+        <v>535</v>
       </c>
       <c r="E130">
-        <v>57698</v>
+        <v>57699</v>
       </c>
       <c r="F130" t="s">
         <v>10</v>
@@ -6371,7 +6512,7 @@
         <v>46006</v>
       </c>
       <c r="I130" s="5">
-        <v>46070</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -6379,28 +6520,28 @@
         <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C131" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="D131" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="E131">
-        <v>57582</v>
+        <v>57653</v>
       </c>
       <c r="F131" t="s">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="G131" s="5">
-        <v>45951</v>
+        <v>45964</v>
       </c>
       <c r="H131" s="5">
-        <v>45976</v>
+        <v>45992</v>
       </c>
       <c r="I131" s="5">
-        <v>46048</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -6408,28 +6549,28 @@
         <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C132" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="D132" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="E132">
-        <v>57654</v>
+        <v>57579</v>
       </c>
       <c r="F132" t="s">
         <v>10</v>
       </c>
       <c r="G132" s="5">
-        <v>45964</v>
+        <v>45951</v>
       </c>
       <c r="H132" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I132" s="5">
-        <v>46048</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
@@ -6437,28 +6578,28 @@
         <v>17</v>
       </c>
       <c r="B133" t="s">
-        <v>183</v>
+        <v>388</v>
       </c>
       <c r="C133" t="s">
-        <v>326</v>
+        <v>447</v>
       </c>
       <c r="D133" t="s">
-        <v>327</v>
+        <v>448</v>
       </c>
       <c r="E133">
-        <v>57779</v>
+        <v>56879</v>
       </c>
       <c r="F133" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G133" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H133" t="s">
-        <v>65</v>
+        <v>46083</v>
+      </c>
+      <c r="H133" s="5">
+        <v>46096</v>
       </c>
       <c r="I133" s="5">
-        <v>46055</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
@@ -6466,538 +6607,538 @@
         <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C134" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="D134" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="E134">
-        <v>56119</v>
+        <v>57659</v>
       </c>
       <c r="F134" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="G134" s="5">
-        <v>46070</v>
+        <v>45964</v>
       </c>
       <c r="H134" s="5">
-        <v>46072</v>
+        <v>45992</v>
       </c>
       <c r="I134" s="5">
-        <v>46070</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B135" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
       <c r="C135" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="D135" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="E135">
-        <v>57840</v>
+        <v>55922</v>
       </c>
       <c r="F135" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G135" s="5">
-        <v>46086</v>
-      </c>
-      <c r="H135" t="s">
-        <v>65</v>
+        <v>46083</v>
+      </c>
+      <c r="H135" s="5">
+        <v>46096</v>
       </c>
       <c r="I135" s="5">
-        <v>46096</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
       <c r="C136" t="s">
-        <v>461</v>
+        <v>175</v>
       </c>
       <c r="D136" t="s">
-        <v>462</v>
+        <v>176</v>
       </c>
       <c r="E136">
-        <v>57841</v>
+        <v>57238</v>
       </c>
       <c r="F136" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="G136" s="5">
-        <v>46086</v>
-      </c>
-      <c r="H136" t="s">
-        <v>65</v>
+        <v>45817</v>
+      </c>
+      <c r="H136" s="5">
+        <v>45839</v>
       </c>
       <c r="I136" s="5">
-        <v>46096</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B137" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
       <c r="C137" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="D137" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="E137">
-        <v>57407</v>
+        <v>57238</v>
       </c>
       <c r="F137" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="G137" s="5">
-        <v>46029</v>
+        <v>45951</v>
       </c>
       <c r="H137" s="5">
-        <v>46047</v>
+        <v>45976</v>
       </c>
       <c r="I137" s="5">
-        <v>46029</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B138" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="C138" t="s">
-        <v>87</v>
+        <v>391</v>
       </c>
       <c r="D138" t="s">
-        <v>88</v>
+        <v>392</v>
       </c>
       <c r="E138">
-        <v>57682</v>
+        <v>57700</v>
       </c>
       <c r="F138" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="G138" s="5">
-        <v>45975</v>
+        <v>45992</v>
       </c>
       <c r="H138" s="5">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="I138" s="5">
-        <v>46036</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B139" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="C139" t="s">
-        <v>463</v>
+        <v>179</v>
       </c>
       <c r="D139" t="s">
-        <v>464</v>
+        <v>180</v>
       </c>
       <c r="E139">
-        <v>57842</v>
+        <v>57583</v>
       </c>
       <c r="F139" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G139" s="5">
-        <v>46087</v>
-      </c>
-      <c r="H139" t="s">
-        <v>65</v>
+        <v>45951</v>
+      </c>
+      <c r="H139" s="5">
+        <v>45976</v>
       </c>
       <c r="I139" s="5">
-        <v>46096</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B140" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="C140" t="s">
-        <v>465</v>
+        <v>181</v>
       </c>
       <c r="D140" t="s">
-        <v>466</v>
+        <v>182</v>
       </c>
       <c r="E140">
-        <v>57845</v>
+        <v>57581</v>
       </c>
       <c r="F140" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G140" s="5">
-        <v>46087</v>
-      </c>
-      <c r="H140" t="s">
-        <v>65</v>
+        <v>45951</v>
+      </c>
+      <c r="H140" s="5">
+        <v>45976</v>
       </c>
       <c r="I140" s="5">
-        <v>46096</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B141" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="C141" t="s">
-        <v>467</v>
+        <v>389</v>
       </c>
       <c r="D141" t="s">
-        <v>468</v>
+        <v>393</v>
       </c>
       <c r="E141">
-        <v>57524</v>
+        <v>57658</v>
       </c>
       <c r="F141" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G141" s="5">
-        <v>46086</v>
+        <v>45964</v>
       </c>
       <c r="H141" s="5">
-        <v>46096</v>
+        <v>45992</v>
       </c>
       <c r="I141" s="5">
-        <v>46086</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B142" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C142" t="s">
-        <v>467</v>
+        <v>84</v>
       </c>
       <c r="D142" t="s">
-        <v>468</v>
+        <v>85</v>
       </c>
       <c r="E142">
-        <v>57847</v>
+        <v>57736</v>
       </c>
       <c r="F142" t="s">
         <v>64</v>
       </c>
       <c r="G142" s="5">
-        <v>46087</v>
+        <v>46007</v>
       </c>
       <c r="H142" t="s">
         <v>65</v>
       </c>
       <c r="I142" s="5">
-        <v>46096</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B143" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C143" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="D143" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="E143">
-        <v>57843</v>
+        <v>57440</v>
       </c>
       <c r="F143" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G143" s="5">
-        <v>46087</v>
-      </c>
-      <c r="H143" t="s">
-        <v>65</v>
+        <v>46083</v>
+      </c>
+      <c r="H143" s="5">
+        <v>46096</v>
       </c>
       <c r="I143" s="5">
-        <v>46096</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B144" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C144" t="s">
-        <v>194</v>
+        <v>453</v>
       </c>
       <c r="D144" t="s">
-        <v>195</v>
+        <v>454</v>
       </c>
       <c r="E144">
-        <v>57406</v>
+        <v>57829</v>
       </c>
       <c r="F144" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G144" s="5">
-        <v>46029</v>
-      </c>
-      <c r="H144" s="5">
-        <v>46047</v>
+        <v>46083</v>
+      </c>
+      <c r="H144" t="s">
+        <v>65</v>
       </c>
       <c r="I144" s="5">
-        <v>46029</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B145" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C145" t="s">
-        <v>194</v>
+        <v>455</v>
       </c>
       <c r="D145" t="s">
-        <v>195</v>
+        <v>456</v>
       </c>
       <c r="E145">
-        <v>57784</v>
+        <v>57830</v>
       </c>
       <c r="F145" t="s">
         <v>64</v>
       </c>
       <c r="G145" s="5">
-        <v>46050</v>
+        <v>46083</v>
       </c>
       <c r="H145" t="s">
         <v>65</v>
       </c>
       <c r="I145" s="5">
-        <v>46055</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B146" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C146" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="D146" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="E146">
-        <v>57844</v>
+        <v>55583</v>
       </c>
       <c r="F146" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G146" s="5">
-        <v>46087</v>
-      </c>
-      <c r="H146" t="s">
-        <v>65</v>
+        <v>46083</v>
+      </c>
+      <c r="H146" s="5">
+        <v>46096</v>
       </c>
       <c r="I146" s="5">
-        <v>46096</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B147" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="C147" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="D147" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="E147">
-        <v>57683</v>
+        <v>57642</v>
       </c>
       <c r="F147" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="G147" s="5">
-        <v>45975</v>
+        <v>45963</v>
       </c>
       <c r="H147" s="5">
         <v>45992</v>
       </c>
       <c r="I147" s="5">
-        <v>46036</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="C148" t="s">
-        <v>473</v>
+        <v>186</v>
       </c>
       <c r="D148" t="s">
-        <v>474</v>
+        <v>187</v>
       </c>
       <c r="E148">
-        <v>57846</v>
+        <v>57655</v>
       </c>
       <c r="F148" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G148" s="5">
-        <v>46087</v>
-      </c>
-      <c r="H148" t="s">
-        <v>65</v>
+        <v>45964</v>
+      </c>
+      <c r="H148" s="5">
+        <v>45992</v>
       </c>
       <c r="I148" s="5">
-        <v>46096</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B149" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="C149" t="s">
-        <v>91</v>
+        <v>394</v>
       </c>
       <c r="D149" t="s">
-        <v>92</v>
+        <v>395</v>
       </c>
       <c r="E149">
-        <v>57681</v>
+        <v>57698</v>
       </c>
       <c r="F149" t="s">
         <v>10</v>
       </c>
       <c r="G149" s="5">
-        <v>45975</v>
+        <v>45992</v>
       </c>
       <c r="H149" s="5">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="I149" s="5">
-        <v>46036</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B150" t="s">
-        <v>328</v>
+        <v>183</v>
       </c>
       <c r="C150" t="s">
-        <v>329</v>
+        <v>188</v>
       </c>
       <c r="D150" t="s">
-        <v>330</v>
+        <v>189</v>
       </c>
       <c r="E150">
-        <v>57772</v>
+        <v>57582</v>
       </c>
       <c r="F150" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="G150" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H150" t="s">
-        <v>65</v>
+        <v>45951</v>
+      </c>
+      <c r="H150" s="5">
+        <v>45976</v>
       </c>
       <c r="I150" s="5">
-        <v>46055</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B151" t="s">
-        <v>328</v>
+        <v>183</v>
       </c>
       <c r="C151" t="s">
-        <v>331</v>
+        <v>190</v>
       </c>
       <c r="D151" t="s">
-        <v>332</v>
+        <v>191</v>
       </c>
       <c r="E151">
-        <v>57773</v>
+        <v>57654</v>
       </c>
       <c r="F151" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G151" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H151" t="s">
-        <v>65</v>
+        <v>45964</v>
+      </c>
+      <c r="H151" s="5">
+        <v>45992</v>
       </c>
       <c r="I151" s="5">
-        <v>46055</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B152" t="s">
-        <v>328</v>
+        <v>183</v>
       </c>
       <c r="C152" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D152" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="E152">
-        <v>57774</v>
+        <v>57779</v>
       </c>
       <c r="F152" t="s">
         <v>64</v>
@@ -7014,2119 +7155,2844 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B153" t="s">
-        <v>35</v>
+        <v>396</v>
       </c>
       <c r="C153" t="s">
-        <v>335</v>
+        <v>397</v>
       </c>
       <c r="D153" t="s">
-        <v>336</v>
+        <v>398</v>
       </c>
       <c r="E153">
-        <v>53987</v>
+        <v>56119</v>
       </c>
       <c r="F153" t="s">
         <v>107</v>
       </c>
       <c r="G153" s="5">
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="H153" s="5">
-        <v>46062</v>
+        <v>46072</v>
       </c>
       <c r="I153" s="5">
-        <v>46059</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B154" t="s">
         <v>35</v>
       </c>
       <c r="C154" t="s">
-        <v>337</v>
+        <v>459</v>
       </c>
       <c r="D154" t="s">
-        <v>338</v>
+        <v>460</v>
       </c>
       <c r="E154">
-        <v>55109</v>
+        <v>57840</v>
       </c>
       <c r="F154" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G154" s="5">
-        <v>46059</v>
-      </c>
-      <c r="H154" s="5">
-        <v>46062</v>
+        <v>46086</v>
+      </c>
+      <c r="H154" t="s">
+        <v>65</v>
       </c>
       <c r="I154" s="5">
-        <v>46059</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B155" t="s">
         <v>35</v>
       </c>
       <c r="C155" t="s">
-        <v>339</v>
+        <v>461</v>
       </c>
       <c r="D155" t="s">
-        <v>340</v>
+        <v>462</v>
       </c>
       <c r="E155">
-        <v>56415</v>
+        <v>57841</v>
       </c>
       <c r="F155" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G155" s="5">
-        <v>46059</v>
-      </c>
-      <c r="H155" s="5">
-        <v>46062</v>
+        <v>46086</v>
+      </c>
+      <c r="H155" t="s">
+        <v>65</v>
       </c>
       <c r="I155" s="5">
-        <v>46059</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B156" t="s">
         <v>35</v>
       </c>
       <c r="C156" t="s">
-        <v>341</v>
+        <v>192</v>
       </c>
       <c r="D156" t="s">
-        <v>342</v>
+        <v>193</v>
       </c>
       <c r="E156">
-        <v>57704</v>
+        <v>57407</v>
       </c>
       <c r="F156" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G156" s="5">
-        <v>45995</v>
+        <v>46029</v>
       </c>
       <c r="H156" s="5">
-        <v>46023</v>
+        <v>46047</v>
       </c>
       <c r="I156" s="5">
-        <v>46062</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B157" t="s">
         <v>35</v>
       </c>
       <c r="C157" t="s">
-        <v>196</v>
+        <v>87</v>
       </c>
       <c r="D157" t="s">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="E157">
-        <v>55810</v>
+        <v>57682</v>
       </c>
       <c r="F157" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G157" s="5">
-        <v>46029</v>
+        <v>45975</v>
       </c>
       <c r="H157" s="5">
-        <v>46047</v>
+        <v>45992</v>
       </c>
       <c r="I157" s="5">
-        <v>46029</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B158" t="s">
         <v>35</v>
       </c>
       <c r="C158" t="s">
-        <v>36</v>
+        <v>463</v>
       </c>
       <c r="D158" t="s">
-        <v>37</v>
+        <v>464</v>
       </c>
       <c r="E158">
-        <v>57626</v>
+        <v>57842</v>
       </c>
       <c r="F158" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G158" s="5">
-        <v>45958</v>
-      </c>
-      <c r="H158" s="5">
-        <v>45976</v>
+        <v>46087</v>
+      </c>
+      <c r="H158" t="s">
+        <v>65</v>
       </c>
       <c r="I158" s="5">
-        <v>46023</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B159" t="s">
         <v>35</v>
       </c>
       <c r="C159" t="s">
-        <v>343</v>
+        <v>465</v>
       </c>
       <c r="D159" t="s">
-        <v>344</v>
+        <v>466</v>
       </c>
       <c r="E159">
-        <v>56750</v>
+        <v>57845</v>
       </c>
       <c r="F159" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G159" s="5">
-        <v>46059</v>
-      </c>
-      <c r="H159" s="5">
-        <v>46062</v>
+        <v>46087</v>
+      </c>
+      <c r="H159" t="s">
+        <v>65</v>
       </c>
       <c r="I159" s="5">
-        <v>46059</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B160" t="s">
         <v>35</v>
       </c>
       <c r="C160" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D160" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="E160">
-        <v>57006</v>
+        <v>57524</v>
       </c>
       <c r="F160" t="s">
         <v>107</v>
       </c>
       <c r="G160" s="5">
-        <v>46090</v>
+        <v>46086</v>
       </c>
       <c r="H160" s="5">
         <v>46096</v>
       </c>
       <c r="I160" s="5">
-        <v>46090</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B161" t="s">
         <v>35</v>
       </c>
       <c r="C161" t="s">
-        <v>399</v>
+        <v>467</v>
       </c>
       <c r="D161" t="s">
-        <v>400</v>
+        <v>468</v>
       </c>
       <c r="E161">
-        <v>57607</v>
+        <v>57847</v>
       </c>
       <c r="F161" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="G161" s="5">
-        <v>45952</v>
-      </c>
-      <c r="H161" s="5">
-        <v>45976</v>
+        <v>46087</v>
+      </c>
+      <c r="H161" t="s">
+        <v>65</v>
       </c>
       <c r="I161" s="5">
-        <v>46071</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B162" t="s">
         <v>35</v>
       </c>
       <c r="C162" t="s">
-        <v>399</v>
+        <v>469</v>
       </c>
       <c r="D162" t="s">
-        <v>400</v>
+        <v>470</v>
       </c>
       <c r="E162">
-        <v>57607</v>
+        <v>57843</v>
       </c>
       <c r="F162" t="s">
-        <v>401</v>
+        <v>64</v>
       </c>
       <c r="G162" s="5">
-        <v>46009</v>
-      </c>
-      <c r="H162" s="5">
-        <v>46037</v>
+        <v>46087</v>
+      </c>
+      <c r="H162" t="s">
+        <v>65</v>
       </c>
       <c r="I162" s="5">
-        <v>46071</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B163" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="C163" t="s">
-        <v>345</v>
+        <v>194</v>
       </c>
       <c r="D163" t="s">
-        <v>346</v>
+        <v>195</v>
       </c>
       <c r="E163">
-        <v>54040</v>
+        <v>57406</v>
       </c>
       <c r="F163" t="s">
         <v>107</v>
       </c>
       <c r="G163" s="5">
-        <v>46062</v>
+        <v>46029</v>
       </c>
       <c r="H163" s="5">
-        <v>46066</v>
+        <v>46047</v>
       </c>
       <c r="I163" s="5">
-        <v>46062</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B164" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="C164" t="s">
-        <v>94</v>
+        <v>194</v>
       </c>
       <c r="D164" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="E164">
-        <v>57685</v>
+        <v>57784</v>
       </c>
       <c r="F164" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G164" s="5">
-        <v>45975</v>
-      </c>
-      <c r="H164" s="5">
-        <v>45992</v>
+        <v>46050</v>
+      </c>
+      <c r="H164" t="s">
+        <v>65</v>
       </c>
       <c r="I164" s="5">
-        <v>46029</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B165" t="s">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="C165" t="s">
-        <v>199</v>
+        <v>536</v>
       </c>
       <c r="D165" t="s">
-        <v>200</v>
+        <v>537</v>
       </c>
       <c r="E165">
-        <v>51497</v>
+        <v>57861</v>
       </c>
       <c r="F165" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G165" s="5">
-        <v>46030</v>
-      </c>
-      <c r="H165" s="5">
-        <v>46047</v>
+        <v>46097</v>
+      </c>
+      <c r="H165" t="s">
+        <v>65</v>
       </c>
       <c r="I165" s="5">
-        <v>46030</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B166" t="s">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="C166" t="s">
-        <v>202</v>
+        <v>538</v>
       </c>
       <c r="D166" t="s">
-        <v>203</v>
+        <v>539</v>
       </c>
       <c r="E166">
-        <v>51493</v>
+        <v>57862</v>
       </c>
       <c r="F166" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G166" s="5">
-        <v>46030</v>
-      </c>
-      <c r="H166" s="5">
-        <v>46047</v>
+        <v>46097</v>
+      </c>
+      <c r="H166" t="s">
+        <v>65</v>
       </c>
       <c r="I166" s="5">
-        <v>46030</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B167" t="s">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="C167" t="s">
-        <v>204</v>
+        <v>471</v>
       </c>
       <c r="D167" t="s">
-        <v>205</v>
+        <v>472</v>
       </c>
       <c r="E167">
-        <v>51495</v>
+        <v>57844</v>
       </c>
       <c r="F167" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G167" s="5">
-        <v>46030</v>
-      </c>
-      <c r="H167" s="5">
-        <v>46047</v>
+        <v>46087</v>
+      </c>
+      <c r="H167" t="s">
+        <v>65</v>
       </c>
       <c r="I167" s="5">
-        <v>46030</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B168" t="s">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="C168" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="D168" t="s">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="E168">
-        <v>51496</v>
+        <v>57683</v>
       </c>
       <c r="F168" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G168" s="5">
-        <v>46030</v>
+        <v>45975</v>
       </c>
       <c r="H168" s="5">
-        <v>46047</v>
+        <v>45992</v>
       </c>
       <c r="I168" s="5">
-        <v>46030</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B169" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C169" t="s">
-        <v>40</v>
+        <v>473</v>
       </c>
       <c r="D169" t="s">
-        <v>41</v>
+        <v>474</v>
       </c>
       <c r="E169">
-        <v>57619</v>
+        <v>57846</v>
       </c>
       <c r="F169" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G169" s="5">
-        <v>45957</v>
-      </c>
-      <c r="H169" s="5">
-        <v>45976</v>
+        <v>46087</v>
+      </c>
+      <c r="H169" t="s">
+        <v>65</v>
       </c>
       <c r="I169" s="5">
-        <v>46023</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B170" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C170" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D170" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="E170">
-        <v>57620</v>
+        <v>57681</v>
       </c>
       <c r="F170" t="s">
         <v>10</v>
       </c>
       <c r="G170" s="5">
-        <v>45957</v>
+        <v>45975</v>
       </c>
       <c r="H170" s="5">
-        <v>45976</v>
+        <v>45992</v>
       </c>
       <c r="I170" s="5">
-        <v>46023</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B171" t="s">
-        <v>39</v>
+        <v>328</v>
       </c>
       <c r="C171" t="s">
-        <v>40</v>
+        <v>329</v>
       </c>
       <c r="D171" t="s">
-        <v>41</v>
+        <v>330</v>
       </c>
       <c r="E171">
-        <v>57625</v>
+        <v>57772</v>
       </c>
       <c r="F171" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G171" s="5">
-        <v>45958</v>
-      </c>
-      <c r="H171" s="5">
-        <v>45976</v>
+        <v>46049</v>
+      </c>
+      <c r="H171" t="s">
+        <v>65</v>
       </c>
       <c r="I171" s="5">
-        <v>46023</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B172" t="s">
-        <v>39</v>
+        <v>328</v>
       </c>
       <c r="C172" t="s">
-        <v>40</v>
+        <v>331</v>
       </c>
       <c r="D172" t="s">
-        <v>41</v>
+        <v>332</v>
       </c>
       <c r="E172">
-        <v>57637</v>
+        <v>57773</v>
       </c>
       <c r="F172" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G172" s="5">
-        <v>45961</v>
-      </c>
-      <c r="H172" s="5">
-        <v>45976</v>
+        <v>46049</v>
+      </c>
+      <c r="H172" t="s">
+        <v>65</v>
       </c>
       <c r="I172" s="5">
-        <v>46023</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B173" t="s">
-        <v>39</v>
+        <v>328</v>
       </c>
       <c r="C173" t="s">
-        <v>42</v>
+        <v>333</v>
       </c>
       <c r="D173" t="s">
-        <v>43</v>
+        <v>334</v>
       </c>
       <c r="E173">
-        <v>57621</v>
+        <v>57774</v>
       </c>
       <c r="F173" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G173" s="5">
-        <v>45957</v>
-      </c>
-      <c r="H173" s="5">
-        <v>45976</v>
+        <v>46049</v>
+      </c>
+      <c r="H173" t="s">
+        <v>65</v>
       </c>
       <c r="I173" s="5">
-        <v>46023</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>208</v>
+        <v>34</v>
       </c>
       <c r="B174" t="s">
-        <v>209</v>
+        <v>35</v>
       </c>
       <c r="C174" t="s">
-        <v>210</v>
+        <v>335</v>
       </c>
       <c r="D174" t="s">
-        <v>211</v>
+        <v>336</v>
       </c>
       <c r="E174">
-        <v>57701</v>
+        <v>53987</v>
       </c>
       <c r="F174" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G174" s="5">
-        <v>45992</v>
+        <v>46059</v>
       </c>
       <c r="H174" s="5">
-        <v>46006</v>
+        <v>46062</v>
       </c>
       <c r="I174" s="5">
-        <v>46043</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>347</v>
+        <v>34</v>
       </c>
       <c r="B175" t="s">
         <v>35</v>
       </c>
       <c r="C175" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D175" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="E175">
-        <v>57490</v>
+        <v>55109</v>
       </c>
       <c r="F175" t="s">
         <v>107</v>
       </c>
       <c r="G175" s="5">
-        <v>46048</v>
+        <v>46059</v>
       </c>
       <c r="H175" s="5">
-        <v>46055</v>
+        <v>46062</v>
       </c>
       <c r="I175" s="5">
-        <v>46048</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>347</v>
+        <v>34</v>
       </c>
       <c r="B176" t="s">
         <v>35</v>
       </c>
       <c r="C176" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="D176" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="E176">
-        <v>51528</v>
+        <v>56415</v>
       </c>
       <c r="F176" t="s">
         <v>107</v>
       </c>
       <c r="G176" s="5">
-        <v>46048</v>
+        <v>46059</v>
       </c>
       <c r="H176" s="5">
-        <v>46055</v>
+        <v>46062</v>
       </c>
       <c r="I176" s="5">
-        <v>46048</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>347</v>
+        <v>34</v>
       </c>
       <c r="B177" t="s">
         <v>35</v>
       </c>
       <c r="C177" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="D177" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="E177">
-        <v>51522</v>
+        <v>57704</v>
       </c>
       <c r="F177" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G177" s="5">
-        <v>46048</v>
+        <v>45995</v>
       </c>
       <c r="H177" s="5">
-        <v>46055</v>
+        <v>46023</v>
       </c>
       <c r="I177" s="5">
-        <v>46048</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B178" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C178" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D178" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="E178">
-        <v>56438</v>
+        <v>55810</v>
       </c>
       <c r="F178" t="s">
         <v>107</v>
       </c>
       <c r="G178" s="5">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="H178" s="5">
         <v>46047</v>
       </c>
       <c r="I178" s="5">
-        <v>46030</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B179" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C179" t="s">
-        <v>402</v>
+        <v>36</v>
       </c>
       <c r="D179" t="s">
-        <v>403</v>
+        <v>37</v>
       </c>
       <c r="E179">
-        <v>57743</v>
+        <v>57626</v>
       </c>
       <c r="F179" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G179" s="5">
-        <v>46013</v>
+        <v>45958</v>
       </c>
       <c r="H179" s="5">
-        <v>46037</v>
+        <v>45976</v>
       </c>
       <c r="I179" s="5">
-        <v>46077</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B180" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C180" t="s">
-        <v>97</v>
+        <v>343</v>
       </c>
       <c r="D180" t="s">
-        <v>98</v>
+        <v>344</v>
       </c>
       <c r="E180">
-        <v>57671</v>
+        <v>56750</v>
       </c>
       <c r="F180" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G180" s="5">
-        <v>45974</v>
+        <v>46059</v>
       </c>
       <c r="H180" s="5">
-        <v>45992</v>
+        <v>46062</v>
       </c>
       <c r="I180" s="5">
-        <v>46029</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B181" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C181" t="s">
-        <v>214</v>
+        <v>475</v>
       </c>
       <c r="D181" t="s">
-        <v>215</v>
+        <v>476</v>
       </c>
       <c r="E181">
-        <v>51696</v>
+        <v>57006</v>
       </c>
       <c r="F181" t="s">
         <v>107</v>
       </c>
       <c r="G181" s="5">
-        <v>46029</v>
+        <v>46090</v>
       </c>
       <c r="H181" s="5">
-        <v>46047</v>
+        <v>46096</v>
       </c>
       <c r="I181" s="5">
-        <v>46029</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B182" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C182" t="s">
-        <v>216</v>
+        <v>399</v>
       </c>
       <c r="D182" t="s">
-        <v>217</v>
+        <v>400</v>
       </c>
       <c r="E182">
-        <v>51693</v>
+        <v>57607</v>
       </c>
       <c r="F182" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G182" s="5">
-        <v>46029</v>
+        <v>45952</v>
       </c>
       <c r="H182" s="5">
-        <v>46047</v>
+        <v>45976</v>
       </c>
       <c r="I182" s="5">
-        <v>46029</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B183" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="C183" t="s">
-        <v>218</v>
+        <v>399</v>
       </c>
       <c r="D183" t="s">
-        <v>219</v>
+        <v>400</v>
       </c>
       <c r="E183">
-        <v>51697</v>
+        <v>57607</v>
       </c>
       <c r="F183" t="s">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="G183" s="5">
-        <v>46029</v>
+        <v>46009</v>
       </c>
       <c r="H183" s="5">
-        <v>46047</v>
+        <v>46037</v>
       </c>
       <c r="I183" s="5">
-        <v>46029</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B184" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C184" t="s">
-        <v>220</v>
+        <v>345</v>
       </c>
       <c r="D184" t="s">
-        <v>221</v>
+        <v>346</v>
       </c>
       <c r="E184">
-        <v>51687</v>
+        <v>54040</v>
       </c>
       <c r="F184" t="s">
         <v>107</v>
       </c>
       <c r="G184" s="5">
-        <v>46030</v>
+        <v>46062</v>
       </c>
       <c r="H184" s="5">
-        <v>46047</v>
+        <v>46066</v>
       </c>
       <c r="I184" s="5">
-        <v>46030</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B185" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C185" t="s">
-        <v>220</v>
+        <v>94</v>
       </c>
       <c r="D185" t="s">
-        <v>221</v>
+        <v>95</v>
       </c>
       <c r="E185">
-        <v>57756</v>
+        <v>57685</v>
       </c>
       <c r="F185" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G185" s="5">
+        <v>45975</v>
+      </c>
+      <c r="H185" s="5">
+        <v>45992</v>
+      </c>
+      <c r="I185" s="5">
         <v>46029</v>
-      </c>
-      <c r="H185" t="s">
-        <v>65</v>
-      </c>
-      <c r="I185" s="5">
-        <v>46047</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B186" t="s">
-        <v>354</v>
+        <v>198</v>
       </c>
       <c r="C186" t="s">
-        <v>355</v>
+        <v>199</v>
       </c>
       <c r="D186" t="s">
-        <v>356</v>
+        <v>200</v>
       </c>
       <c r="E186">
-        <v>53634</v>
+        <v>51497</v>
       </c>
       <c r="F186" t="s">
-        <v>357</v>
+        <v>107</v>
       </c>
       <c r="G186" s="5">
-        <v>46063</v>
-      </c>
-      <c r="H186" t="s">
-        <v>358</v>
+        <v>46030</v>
+      </c>
+      <c r="H186" s="5">
+        <v>46047</v>
       </c>
       <c r="I186" s="5">
-        <v>46063</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B187" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="C187" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="D187" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="E187">
-        <v>53224</v>
+        <v>51493</v>
       </c>
       <c r="F187" t="s">
         <v>107</v>
       </c>
       <c r="G187" s="5">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="H187" s="5">
         <v>46047</v>
       </c>
       <c r="I187" s="5">
-        <v>46031</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B188" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="C188" t="s">
-        <v>359</v>
+        <v>204</v>
       </c>
       <c r="D188" t="s">
-        <v>360</v>
+        <v>205</v>
       </c>
       <c r="E188">
-        <v>57708</v>
+        <v>51495</v>
       </c>
       <c r="F188" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G188" s="5">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="H188" s="5">
-        <v>46023</v>
+        <v>46047</v>
       </c>
       <c r="I188" s="5">
-        <v>46063</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B189" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="C189" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="D189" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="E189">
-        <v>55787</v>
+        <v>51496</v>
       </c>
       <c r="F189" t="s">
         <v>107</v>
       </c>
       <c r="G189" s="5">
-        <v>46027</v>
+        <v>46030</v>
       </c>
       <c r="H189" s="5">
         <v>46047</v>
       </c>
       <c r="I189" s="5">
-        <v>46027</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B190" t="s">
-        <v>225</v>
+        <v>39</v>
       </c>
       <c r="C190" t="s">
-        <v>477</v>
+        <v>40</v>
       </c>
       <c r="D190" t="s">
-        <v>478</v>
+        <v>41</v>
       </c>
       <c r="E190">
-        <v>57766</v>
+        <v>57619</v>
       </c>
       <c r="F190" t="s">
         <v>10</v>
       </c>
       <c r="G190" s="5">
-        <v>46037</v>
+        <v>45957</v>
       </c>
       <c r="H190" s="5">
-        <v>46054</v>
+        <v>45976</v>
       </c>
       <c r="I190" s="5">
-        <v>46092</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B191" t="s">
-        <v>225</v>
+        <v>39</v>
       </c>
       <c r="C191" t="s">
-        <v>479</v>
+        <v>40</v>
       </c>
       <c r="D191" t="s">
-        <v>480</v>
+        <v>41</v>
       </c>
       <c r="E191">
-        <v>57767</v>
+        <v>57620</v>
       </c>
       <c r="F191" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G191" s="5">
-        <v>46037</v>
+        <v>45957</v>
       </c>
       <c r="H191" s="5">
-        <v>46054</v>
+        <v>45976</v>
       </c>
       <c r="I191" s="5">
-        <v>46092</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>361</v>
+        <v>38</v>
       </c>
       <c r="B192" t="s">
-        <v>362</v>
+        <v>39</v>
       </c>
       <c r="C192" t="s">
-        <v>363</v>
+        <v>40</v>
       </c>
       <c r="D192" t="s">
-        <v>364</v>
+        <v>41</v>
       </c>
       <c r="E192">
-        <v>52702</v>
+        <v>57625</v>
       </c>
       <c r="F192" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G192" s="5">
-        <v>46057</v>
+        <v>45958</v>
       </c>
       <c r="H192" s="5">
-        <v>46062</v>
+        <v>45976</v>
       </c>
       <c r="I192" s="5">
-        <v>46057</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>361</v>
+        <v>38</v>
       </c>
       <c r="B193" t="s">
-        <v>362</v>
+        <v>39</v>
       </c>
       <c r="C193" t="s">
-        <v>365</v>
+        <v>40</v>
       </c>
       <c r="D193" t="s">
-        <v>366</v>
+        <v>41</v>
       </c>
       <c r="E193">
-        <v>51793</v>
+        <v>57637</v>
       </c>
       <c r="F193" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G193" s="5">
-        <v>46057</v>
+        <v>45961</v>
       </c>
       <c r="H193" s="5">
-        <v>46062</v>
+        <v>45976</v>
       </c>
       <c r="I193" s="5">
-        <v>46057</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>361</v>
+        <v>38</v>
       </c>
       <c r="B194" t="s">
-        <v>362</v>
+        <v>39</v>
       </c>
       <c r="C194" t="s">
-        <v>367</v>
+        <v>42</v>
       </c>
       <c r="D194" t="s">
-        <v>368</v>
+        <v>43</v>
       </c>
       <c r="E194">
-        <v>51802</v>
+        <v>57621</v>
       </c>
       <c r="F194" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G194" s="5">
-        <v>46057</v>
+        <v>45957</v>
       </c>
       <c r="H194" s="5">
-        <v>46062</v>
+        <v>45976</v>
       </c>
       <c r="I194" s="5">
-        <v>46057</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>361</v>
+        <v>208</v>
       </c>
       <c r="B195" t="s">
-        <v>362</v>
+        <v>209</v>
       </c>
       <c r="C195" t="s">
-        <v>369</v>
+        <v>210</v>
       </c>
       <c r="D195" t="s">
-        <v>370</v>
+        <v>211</v>
       </c>
       <c r="E195">
-        <v>51798</v>
+        <v>57701</v>
       </c>
       <c r="F195" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G195" s="5">
-        <v>46057</v>
+        <v>45992</v>
       </c>
       <c r="H195" s="5">
-        <v>46062</v>
+        <v>46006</v>
       </c>
       <c r="I195" s="5">
-        <v>46057</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="B196" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C196" t="s">
-        <v>404</v>
+        <v>348</v>
       </c>
       <c r="D196" t="s">
-        <v>405</v>
+        <v>349</v>
       </c>
       <c r="E196">
-        <v>51799</v>
+        <v>57490</v>
       </c>
       <c r="F196" t="s">
         <v>107</v>
       </c>
       <c r="G196" s="5">
-        <v>46076</v>
+        <v>46048</v>
       </c>
       <c r="H196" s="5">
-        <v>46082</v>
+        <v>46055</v>
       </c>
       <c r="I196" s="5">
-        <v>46076</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="B197" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C197" t="s">
-        <v>406</v>
+        <v>350</v>
       </c>
       <c r="D197" t="s">
-        <v>407</v>
+        <v>351</v>
       </c>
       <c r="E197">
-        <v>51800</v>
+        <v>51528</v>
       </c>
       <c r="F197" t="s">
         <v>107</v>
       </c>
       <c r="G197" s="5">
-        <v>46076</v>
+        <v>46048</v>
       </c>
       <c r="H197" s="5">
-        <v>46082</v>
+        <v>46055</v>
       </c>
       <c r="I197" s="5">
-        <v>46076</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="B198" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C198" t="s">
-        <v>408</v>
+        <v>352</v>
       </c>
       <c r="D198" t="s">
-        <v>409</v>
+        <v>353</v>
       </c>
       <c r="E198">
-        <v>51803</v>
+        <v>51522</v>
       </c>
       <c r="F198" t="s">
         <v>107</v>
       </c>
       <c r="G198" s="5">
-        <v>46076</v>
+        <v>46048</v>
       </c>
       <c r="H198" s="5">
-        <v>46082</v>
+        <v>46055</v>
       </c>
       <c r="I198" s="5">
-        <v>46076</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B199" t="s">
-        <v>362</v>
+        <v>96</v>
       </c>
       <c r="C199" t="s">
-        <v>410</v>
+        <v>212</v>
       </c>
       <c r="D199" t="s">
-        <v>411</v>
+        <v>213</v>
       </c>
       <c r="E199">
-        <v>51807</v>
+        <v>56438</v>
       </c>
       <c r="F199" t="s">
         <v>107</v>
       </c>
       <c r="G199" s="5">
-        <v>46076</v>
+        <v>46030</v>
       </c>
       <c r="H199" s="5">
-        <v>46082</v>
+        <v>46047</v>
       </c>
       <c r="I199" s="5">
-        <v>46076</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B200" t="s">
-        <v>362</v>
+        <v>96</v>
       </c>
       <c r="C200" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="D200" t="s">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="E200">
-        <v>52701</v>
+        <v>57743</v>
       </c>
       <c r="F200" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G200" s="5">
-        <v>46057</v>
+        <v>46013</v>
       </c>
       <c r="H200" s="5">
-        <v>46062</v>
+        <v>46037</v>
       </c>
       <c r="I200" s="5">
-        <v>46057</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B201" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="C201" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="D201" t="s">
-        <v>481</v>
+        <v>98</v>
       </c>
       <c r="E201">
-        <v>57591</v>
+        <v>57671</v>
       </c>
       <c r="F201" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G201" s="5">
-        <v>46087</v>
+        <v>45974</v>
       </c>
       <c r="H201" s="5">
-        <v>46096</v>
+        <v>45992</v>
       </c>
       <c r="I201" s="5">
-        <v>46087</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B202" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="C202" t="s">
-        <v>482</v>
+        <v>214</v>
       </c>
       <c r="D202" t="s">
-        <v>483</v>
+        <v>215</v>
       </c>
       <c r="E202">
-        <v>57097</v>
+        <v>51696</v>
       </c>
       <c r="F202" t="s">
         <v>107</v>
       </c>
       <c r="G202" s="5">
-        <v>46087</v>
+        <v>46029</v>
       </c>
       <c r="H202" s="5">
-        <v>46096</v>
+        <v>46047</v>
       </c>
       <c r="I202" s="5">
-        <v>46087</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B203" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="C203" t="s">
-        <v>484</v>
+        <v>216</v>
       </c>
       <c r="D203" t="s">
-        <v>485</v>
+        <v>217</v>
       </c>
       <c r="E203">
-        <v>57272</v>
+        <v>51693</v>
       </c>
       <c r="F203" t="s">
         <v>107</v>
       </c>
       <c r="G203" s="5">
-        <v>46087</v>
+        <v>46029</v>
       </c>
       <c r="H203" s="5">
-        <v>46096</v>
+        <v>46047</v>
       </c>
       <c r="I203" s="5">
-        <v>46087</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B204" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="C204" t="s">
-        <v>100</v>
+        <v>218</v>
       </c>
       <c r="D204" t="s">
-        <v>101</v>
+        <v>219</v>
       </c>
       <c r="E204">
-        <v>57604</v>
+        <v>51697</v>
       </c>
       <c r="F204" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G204" s="5">
-        <v>45952</v>
+        <v>46029</v>
       </c>
       <c r="H204" s="5">
-        <v>45976</v>
+        <v>46047</v>
       </c>
       <c r="I204" s="5">
-        <v>46038</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B205" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="C205" t="s">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="D205" t="s">
-        <v>103</v>
+        <v>221</v>
       </c>
       <c r="E205">
-        <v>57606</v>
+        <v>51687</v>
       </c>
       <c r="F205" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G205" s="5">
-        <v>45952</v>
+        <v>46030</v>
       </c>
       <c r="H205" s="5">
-        <v>45976</v>
+        <v>46047</v>
       </c>
       <c r="I205" s="5">
-        <v>46038</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="B206" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="C206" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D206" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E206">
-        <v>57088</v>
+        <v>57756</v>
       </c>
       <c r="F206" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G206" s="5">
         <v>46029</v>
       </c>
-      <c r="H206" s="5">
+      <c r="H206" t="s">
+        <v>65</v>
+      </c>
+      <c r="I206" s="5">
         <v>46047</v>
-      </c>
-      <c r="I206" s="5">
-        <v>46029</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="B207" t="s">
-        <v>231</v>
+        <v>354</v>
       </c>
       <c r="C207" t="s">
-        <v>232</v>
+        <v>355</v>
       </c>
       <c r="D207" t="s">
-        <v>233</v>
+        <v>356</v>
       </c>
       <c r="E207">
-        <v>56876</v>
+        <v>53634</v>
       </c>
       <c r="F207" t="s">
-        <v>107</v>
+        <v>357</v>
       </c>
       <c r="G207" s="5">
-        <v>46029</v>
-      </c>
-      <c r="H207" s="5">
-        <v>46047</v>
+        <v>46063</v>
+      </c>
+      <c r="H207" t="s">
+        <v>358</v>
       </c>
       <c r="I207" s="5">
-        <v>46029</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B208" t="s">
-        <v>35</v>
+        <v>222</v>
       </c>
       <c r="C208" t="s">
-        <v>45</v>
+        <v>223</v>
       </c>
       <c r="D208" t="s">
-        <v>46</v>
+        <v>224</v>
       </c>
       <c r="E208">
-        <v>57639</v>
+        <v>53224</v>
       </c>
       <c r="F208" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G208" s="5">
-        <v>45961</v>
+        <v>46031</v>
       </c>
       <c r="H208" s="5">
-        <v>45976</v>
+        <v>46047</v>
       </c>
       <c r="I208" s="5">
-        <v>46023</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B209" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="C209" t="s">
-        <v>412</v>
+        <v>359</v>
       </c>
       <c r="D209" t="s">
-        <v>413</v>
+        <v>360</v>
       </c>
       <c r="E209">
-        <v>56505</v>
+        <v>57708</v>
       </c>
       <c r="F209" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G209" s="5">
-        <v>46071</v>
+        <v>46001</v>
       </c>
       <c r="H209" s="5">
-        <v>46082</v>
+        <v>46023</v>
       </c>
       <c r="I209" s="5">
-        <v>46071</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B210" t="s">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="C210" t="s">
-        <v>28</v>
+        <v>226</v>
       </c>
       <c r="D210" t="s">
-        <v>29</v>
+        <v>227</v>
       </c>
       <c r="E210">
-        <v>57419</v>
+        <v>55787</v>
       </c>
       <c r="F210" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G210" s="5">
-        <v>45895</v>
+        <v>46027</v>
       </c>
       <c r="H210" s="5">
-        <v>45915</v>
+        <v>46047</v>
       </c>
       <c r="I210" s="5">
-        <v>46023</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B211" t="s">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="C211" t="s">
-        <v>28</v>
+        <v>477</v>
       </c>
       <c r="D211" t="s">
-        <v>29</v>
+        <v>478</v>
       </c>
       <c r="E211">
-        <v>57420</v>
+        <v>57766</v>
       </c>
       <c r="F211" t="s">
         <v>10</v>
       </c>
       <c r="G211" s="5">
-        <v>45895</v>
+        <v>46037</v>
       </c>
       <c r="H211" s="5">
-        <v>45915</v>
+        <v>46054</v>
       </c>
       <c r="I211" s="5">
-        <v>46023</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B212" t="s">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="C212" t="s">
-        <v>30</v>
+        <v>479</v>
       </c>
       <c r="D212" t="s">
-        <v>31</v>
+        <v>480</v>
       </c>
       <c r="E212">
-        <v>57418</v>
+        <v>57767</v>
       </c>
       <c r="F212" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G212" s="5">
-        <v>45895</v>
+        <v>46037</v>
       </c>
       <c r="H212" s="5">
-        <v>45915</v>
+        <v>46054</v>
       </c>
       <c r="I212" s="5">
-        <v>46023</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B213" t="s">
-        <v>27</v>
+        <v>362</v>
       </c>
       <c r="C213" t="s">
-        <v>32</v>
+        <v>363</v>
       </c>
       <c r="D213" t="s">
-        <v>33</v>
+        <v>364</v>
       </c>
       <c r="E213">
-        <v>57417</v>
+        <v>52702</v>
       </c>
       <c r="F213" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G213" s="5">
-        <v>45895</v>
+        <v>46057</v>
       </c>
       <c r="H213" s="5">
-        <v>45915</v>
+        <v>46062</v>
       </c>
       <c r="I213" s="5">
-        <v>46023</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B214" t="s">
-        <v>27</v>
+        <v>362</v>
       </c>
       <c r="C214" t="s">
-        <v>32</v>
+        <v>365</v>
       </c>
       <c r="D214" t="s">
-        <v>33</v>
+        <v>366</v>
       </c>
       <c r="E214">
-        <v>57421</v>
+        <v>51793</v>
       </c>
       <c r="F214" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G214" s="5">
-        <v>45895</v>
+        <v>46057</v>
       </c>
       <c r="H214" s="5">
-        <v>45915</v>
+        <v>46062</v>
       </c>
       <c r="I214" s="5">
-        <v>46023</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B215" t="s">
-        <v>234</v>
+        <v>362</v>
       </c>
       <c r="C215" t="s">
-        <v>234</v>
+        <v>367</v>
       </c>
       <c r="D215" t="s">
-        <v>235</v>
+        <v>368</v>
       </c>
       <c r="E215">
-        <v>57760</v>
+        <v>51802</v>
       </c>
       <c r="F215" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G215" s="5">
-        <v>46035</v>
-      </c>
-      <c r="H215" t="s">
-        <v>65</v>
+        <v>46057</v>
+      </c>
+      <c r="H215" s="5">
+        <v>46062</v>
       </c>
       <c r="I215" s="5">
-        <v>46047</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B216" t="s">
-        <v>14</v>
+        <v>362</v>
       </c>
       <c r="C216" t="s">
-        <v>14</v>
+        <v>369</v>
       </c>
       <c r="D216" t="s">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="E216">
-        <v>57459</v>
+        <v>51798</v>
       </c>
       <c r="F216" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G216" s="5">
-        <v>45902</v>
+        <v>46057</v>
       </c>
       <c r="H216" s="5">
-        <v>45915</v>
+        <v>46062</v>
       </c>
       <c r="I216" s="5">
-        <v>46023</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B217" t="s">
-        <v>14</v>
+        <v>362</v>
       </c>
       <c r="C217" t="s">
-        <v>14</v>
+        <v>404</v>
       </c>
       <c r="D217" t="s">
-        <v>15</v>
+        <v>405</v>
       </c>
       <c r="E217">
-        <v>57485</v>
+        <v>51799</v>
       </c>
       <c r="F217" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G217" s="5">
-        <v>45911</v>
+        <v>46076</v>
       </c>
       <c r="H217" s="5">
-        <v>45931</v>
+        <v>46082</v>
       </c>
       <c r="I217" s="5">
-        <v>46023</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B218" t="s">
-        <v>14</v>
+        <v>362</v>
       </c>
       <c r="C218" t="s">
-        <v>14</v>
+        <v>406</v>
       </c>
       <c r="D218" t="s">
-        <v>15</v>
+        <v>407</v>
       </c>
       <c r="E218">
-        <v>57486</v>
+        <v>51800</v>
       </c>
       <c r="F218" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G218" s="5">
-        <v>45911</v>
+        <v>46076</v>
       </c>
       <c r="H218" s="5">
-        <v>45931</v>
+        <v>46082</v>
       </c>
       <c r="I218" s="5">
-        <v>46023</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="B219" t="s">
-        <v>486</v>
+        <v>362</v>
       </c>
       <c r="C219" t="s">
-        <v>487</v>
+        <v>408</v>
       </c>
       <c r="D219" t="s">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="E219">
-        <v>57758</v>
+        <v>51803</v>
       </c>
       <c r="F219" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G219" s="5">
-        <v>46030</v>
+        <v>46076</v>
       </c>
       <c r="H219" s="5">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="I219" s="5">
-        <v>46091</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="B220" t="s">
-        <v>489</v>
+        <v>362</v>
       </c>
       <c r="C220" t="s">
-        <v>490</v>
+        <v>410</v>
       </c>
       <c r="D220" t="s">
-        <v>491</v>
+        <v>411</v>
       </c>
       <c r="E220">
-        <v>57738</v>
+        <v>51807</v>
       </c>
       <c r="F220" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G220" s="5">
-        <v>46010</v>
+        <v>46076</v>
       </c>
       <c r="H220" s="5">
-        <v>46037</v>
+        <v>46082</v>
       </c>
       <c r="I220" s="5">
-        <v>46077</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="B221" t="s">
-        <v>489</v>
+        <v>362</v>
       </c>
       <c r="C221" t="s">
-        <v>492</v>
+        <v>540</v>
       </c>
       <c r="D221" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
       <c r="E221">
-        <v>57739</v>
+        <v>51810</v>
       </c>
       <c r="F221" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G221" s="5">
-        <v>46010</v>
+        <v>46094</v>
       </c>
       <c r="H221" s="5">
-        <v>46037</v>
+        <v>46098</v>
       </c>
       <c r="I221" s="5">
-        <v>46077</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="B222" t="s">
-        <v>489</v>
+        <v>362</v>
       </c>
       <c r="C222" t="s">
-        <v>494</v>
+        <v>542</v>
       </c>
       <c r="D222" t="s">
-        <v>495</v>
+        <v>543</v>
       </c>
       <c r="E222">
-        <v>57744</v>
+        <v>51814</v>
       </c>
       <c r="F222" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G222" s="5">
-        <v>46014</v>
+        <v>46094</v>
       </c>
       <c r="H222" s="5">
-        <v>46037</v>
+        <v>46098</v>
       </c>
       <c r="I222" s="5">
-        <v>46074</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="B223" t="s">
-        <v>489</v>
+        <v>362</v>
       </c>
       <c r="C223" t="s">
-        <v>496</v>
+        <v>544</v>
       </c>
       <c r="D223" t="s">
-        <v>497</v>
+        <v>545</v>
       </c>
       <c r="E223">
-        <v>57742</v>
+        <v>53472</v>
       </c>
       <c r="F223" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G223" s="5">
-        <v>46010</v>
+        <v>46094</v>
       </c>
       <c r="H223" s="5">
-        <v>46037</v>
+        <v>46098</v>
       </c>
       <c r="I223" s="5">
-        <v>46074</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="B224" t="s">
-        <v>237</v>
+        <v>362</v>
       </c>
       <c r="C224" t="s">
-        <v>238</v>
+        <v>546</v>
       </c>
       <c r="D224" t="s">
-        <v>239</v>
+        <v>547</v>
       </c>
       <c r="E224">
-        <v>57324</v>
+        <v>53473</v>
       </c>
       <c r="F224" t="s">
         <v>107</v>
       </c>
       <c r="G224" s="5">
-        <v>46030</v>
+        <v>46094</v>
       </c>
       <c r="H224" s="5">
-        <v>46047</v>
+        <v>46098</v>
       </c>
       <c r="I224" s="5">
-        <v>46030</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>361</v>
+      </c>
+      <c r="B225" t="s">
+        <v>362</v>
+      </c>
+      <c r="C225" t="s">
+        <v>371</v>
+      </c>
+      <c r="D225" t="s">
+        <v>372</v>
+      </c>
+      <c r="E225">
+        <v>52701</v>
+      </c>
+      <c r="F225" t="s">
+        <v>107</v>
+      </c>
+      <c r="G225" s="5">
+        <v>46057</v>
+      </c>
+      <c r="H225" s="5">
+        <v>46062</v>
+      </c>
+      <c r="I225" s="5">
+        <v>46057</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>99</v>
+      </c>
+      <c r="B226" t="s">
+        <v>35</v>
+      </c>
+      <c r="C226" t="s">
+        <v>123</v>
+      </c>
+      <c r="D226" t="s">
+        <v>481</v>
+      </c>
+      <c r="E226">
+        <v>57591</v>
+      </c>
+      <c r="F226" t="s">
+        <v>107</v>
+      </c>
+      <c r="G226" s="5">
+        <v>46087</v>
+      </c>
+      <c r="H226" s="5">
+        <v>46096</v>
+      </c>
+      <c r="I226" s="5">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>99</v>
+      </c>
+      <c r="B227" t="s">
+        <v>35</v>
+      </c>
+      <c r="C227" t="s">
+        <v>482</v>
+      </c>
+      <c r="D227" t="s">
+        <v>483</v>
+      </c>
+      <c r="E227">
+        <v>57097</v>
+      </c>
+      <c r="F227" t="s">
+        <v>107</v>
+      </c>
+      <c r="G227" s="5">
+        <v>46087</v>
+      </c>
+      <c r="H227" s="5">
+        <v>46096</v>
+      </c>
+      <c r="I227" s="5">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>99</v>
+      </c>
+      <c r="B228" t="s">
+        <v>35</v>
+      </c>
+      <c r="C228" t="s">
+        <v>484</v>
+      </c>
+      <c r="D228" t="s">
+        <v>485</v>
+      </c>
+      <c r="E228">
+        <v>57272</v>
+      </c>
+      <c r="F228" t="s">
+        <v>107</v>
+      </c>
+      <c r="G228" s="5">
+        <v>46087</v>
+      </c>
+      <c r="H228" s="5">
+        <v>46096</v>
+      </c>
+      <c r="I228" s="5">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>99</v>
+      </c>
+      <c r="B229" t="s">
+        <v>35</v>
+      </c>
+      <c r="C229" t="s">
+        <v>100</v>
+      </c>
+      <c r="D229" t="s">
+        <v>101</v>
+      </c>
+      <c r="E229">
+        <v>57604</v>
+      </c>
+      <c r="F229" t="s">
+        <v>10</v>
+      </c>
+      <c r="G229" s="5">
+        <v>45952</v>
+      </c>
+      <c r="H229" s="5">
+        <v>45976</v>
+      </c>
+      <c r="I229" s="5">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>99</v>
+      </c>
+      <c r="B230" t="s">
+        <v>35</v>
+      </c>
+      <c r="C230" t="s">
+        <v>102</v>
+      </c>
+      <c r="D230" t="s">
+        <v>103</v>
+      </c>
+      <c r="E230">
+        <v>57606</v>
+      </c>
+      <c r="F230" t="s">
+        <v>10</v>
+      </c>
+      <c r="G230" s="5">
+        <v>45952</v>
+      </c>
+      <c r="H230" s="5">
+        <v>45976</v>
+      </c>
+      <c r="I230" s="5">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>228</v>
+      </c>
+      <c r="B231" t="s">
+        <v>35</v>
+      </c>
+      <c r="C231" t="s">
+        <v>229</v>
+      </c>
+      <c r="D231" t="s">
+        <v>230</v>
+      </c>
+      <c r="E231">
+        <v>57088</v>
+      </c>
+      <c r="F231" t="s">
+        <v>107</v>
+      </c>
+      <c r="G231" s="5">
+        <v>46029</v>
+      </c>
+      <c r="H231" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I231" s="5">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>228</v>
+      </c>
+      <c r="B232" t="s">
+        <v>231</v>
+      </c>
+      <c r="C232" t="s">
+        <v>232</v>
+      </c>
+      <c r="D232" t="s">
+        <v>233</v>
+      </c>
+      <c r="E232">
+        <v>56876</v>
+      </c>
+      <c r="F232" t="s">
+        <v>107</v>
+      </c>
+      <c r="G232" s="5">
+        <v>46029</v>
+      </c>
+      <c r="H232" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I232" s="5">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>44</v>
+      </c>
+      <c r="B233" t="s">
+        <v>35</v>
+      </c>
+      <c r="C233" t="s">
+        <v>45</v>
+      </c>
+      <c r="D233" t="s">
+        <v>46</v>
+      </c>
+      <c r="E233">
+        <v>57639</v>
+      </c>
+      <c r="F233" t="s">
+        <v>19</v>
+      </c>
+      <c r="G233" s="5">
+        <v>45961</v>
+      </c>
+      <c r="H233" s="5">
+        <v>45976</v>
+      </c>
+      <c r="I233" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>44</v>
+      </c>
+      <c r="B234" t="s">
+        <v>35</v>
+      </c>
+      <c r="C234" t="s">
+        <v>412</v>
+      </c>
+      <c r="D234" t="s">
+        <v>413</v>
+      </c>
+      <c r="E234">
+        <v>56505</v>
+      </c>
+      <c r="F234" t="s">
+        <v>107</v>
+      </c>
+      <c r="G234" s="5">
+        <v>46071</v>
+      </c>
+      <c r="H234" s="5">
+        <v>46082</v>
+      </c>
+      <c r="I234" s="5">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>12</v>
+      </c>
+      <c r="B235" t="s">
+        <v>27</v>
+      </c>
+      <c r="C235" t="s">
+        <v>28</v>
+      </c>
+      <c r="D235" t="s">
+        <v>29</v>
+      </c>
+      <c r="E235">
+        <v>57419</v>
+      </c>
+      <c r="F235" t="s">
+        <v>10</v>
+      </c>
+      <c r="G235" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H235" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I235" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>12</v>
+      </c>
+      <c r="B236" t="s">
+        <v>27</v>
+      </c>
+      <c r="C236" t="s">
+        <v>28</v>
+      </c>
+      <c r="D236" t="s">
+        <v>29</v>
+      </c>
+      <c r="E236">
+        <v>57420</v>
+      </c>
+      <c r="F236" t="s">
+        <v>10</v>
+      </c>
+      <c r="G236" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H236" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I236" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>12</v>
+      </c>
+      <c r="B237" t="s">
+        <v>27</v>
+      </c>
+      <c r="C237" t="s">
+        <v>30</v>
+      </c>
+      <c r="D237" t="s">
+        <v>31</v>
+      </c>
+      <c r="E237">
+        <v>57418</v>
+      </c>
+      <c r="F237" t="s">
+        <v>10</v>
+      </c>
+      <c r="G237" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H237" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I237" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>12</v>
+      </c>
+      <c r="B238" t="s">
+        <v>27</v>
+      </c>
+      <c r="C238" t="s">
+        <v>32</v>
+      </c>
+      <c r="D238" t="s">
+        <v>33</v>
+      </c>
+      <c r="E238">
+        <v>57417</v>
+      </c>
+      <c r="F238" t="s">
+        <v>10</v>
+      </c>
+      <c r="G238" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H238" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I238" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>12</v>
+      </c>
+      <c r="B239" t="s">
+        <v>27</v>
+      </c>
+      <c r="C239" t="s">
+        <v>32</v>
+      </c>
+      <c r="D239" t="s">
+        <v>33</v>
+      </c>
+      <c r="E239">
+        <v>57421</v>
+      </c>
+      <c r="F239" t="s">
+        <v>10</v>
+      </c>
+      <c r="G239" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H239" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I239" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>12</v>
+      </c>
+      <c r="B240" t="s">
+        <v>234</v>
+      </c>
+      <c r="C240" t="s">
+        <v>234</v>
+      </c>
+      <c r="D240" t="s">
+        <v>235</v>
+      </c>
+      <c r="E240">
+        <v>57760</v>
+      </c>
+      <c r="F240" t="s">
+        <v>64</v>
+      </c>
+      <c r="G240" s="5">
+        <v>46035</v>
+      </c>
+      <c r="H240" t="s">
+        <v>65</v>
+      </c>
+      <c r="I240" s="5">
+        <v>46047</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>12</v>
+      </c>
+      <c r="B241" t="s">
+        <v>14</v>
+      </c>
+      <c r="C241" t="s">
+        <v>14</v>
+      </c>
+      <c r="D241" t="s">
+        <v>15</v>
+      </c>
+      <c r="E241">
+        <v>57459</v>
+      </c>
+      <c r="F241" t="s">
+        <v>10</v>
+      </c>
+      <c r="G241" s="5">
+        <v>45902</v>
+      </c>
+      <c r="H241" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I241" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>12</v>
+      </c>
+      <c r="B242" t="s">
+        <v>14</v>
+      </c>
+      <c r="C242" t="s">
+        <v>14</v>
+      </c>
+      <c r="D242" t="s">
+        <v>15</v>
+      </c>
+      <c r="E242">
+        <v>57485</v>
+      </c>
+      <c r="F242" t="s">
+        <v>10</v>
+      </c>
+      <c r="G242" s="5">
+        <v>45911</v>
+      </c>
+      <c r="H242" s="5">
+        <v>45931</v>
+      </c>
+      <c r="I242" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>12</v>
+      </c>
+      <c r="B243" t="s">
+        <v>14</v>
+      </c>
+      <c r="C243" t="s">
+        <v>14</v>
+      </c>
+      <c r="D243" t="s">
+        <v>15</v>
+      </c>
+      <c r="E243">
+        <v>57486</v>
+      </c>
+      <c r="F243" t="s">
+        <v>10</v>
+      </c>
+      <c r="G243" s="5">
+        <v>45911</v>
+      </c>
+      <c r="H243" s="5">
+        <v>45931</v>
+      </c>
+      <c r="I243" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>236</v>
+      </c>
+      <c r="B244" t="s">
+        <v>486</v>
+      </c>
+      <c r="C244" t="s">
+        <v>487</v>
+      </c>
+      <c r="D244" t="s">
+        <v>488</v>
+      </c>
+      <c r="E244">
+        <v>57758</v>
+      </c>
+      <c r="F244" t="s">
+        <v>10</v>
+      </c>
+      <c r="G244" s="5">
+        <v>46030</v>
+      </c>
+      <c r="H244" s="5">
+        <v>46054</v>
+      </c>
+      <c r="I244" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>236</v>
+      </c>
+      <c r="B245" t="s">
+        <v>489</v>
+      </c>
+      <c r="C245" t="s">
+        <v>490</v>
+      </c>
+      <c r="D245" t="s">
+        <v>491</v>
+      </c>
+      <c r="E245">
+        <v>57738</v>
+      </c>
+      <c r="F245" t="s">
+        <v>141</v>
+      </c>
+      <c r="G245" s="5">
+        <v>46010</v>
+      </c>
+      <c r="H245" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I245" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>236</v>
+      </c>
+      <c r="B246" t="s">
+        <v>489</v>
+      </c>
+      <c r="C246" t="s">
+        <v>492</v>
+      </c>
+      <c r="D246" t="s">
+        <v>493</v>
+      </c>
+      <c r="E246">
+        <v>57739</v>
+      </c>
+      <c r="F246" t="s">
+        <v>141</v>
+      </c>
+      <c r="G246" s="5">
+        <v>46010</v>
+      </c>
+      <c r="H246" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I246" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>236</v>
+      </c>
+      <c r="B247" t="s">
+        <v>489</v>
+      </c>
+      <c r="C247" t="s">
+        <v>494</v>
+      </c>
+      <c r="D247" t="s">
+        <v>495</v>
+      </c>
+      <c r="E247">
+        <v>57744</v>
+      </c>
+      <c r="F247" t="s">
+        <v>82</v>
+      </c>
+      <c r="G247" s="5">
+        <v>46014</v>
+      </c>
+      <c r="H247" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I247" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>236</v>
+      </c>
+      <c r="B248" t="s">
+        <v>489</v>
+      </c>
+      <c r="C248" t="s">
+        <v>496</v>
+      </c>
+      <c r="D248" t="s">
+        <v>497</v>
+      </c>
+      <c r="E248">
+        <v>57742</v>
+      </c>
+      <c r="F248" t="s">
+        <v>82</v>
+      </c>
+      <c r="G248" s="5">
+        <v>46010</v>
+      </c>
+      <c r="H248" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I248" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>236</v>
+      </c>
+      <c r="B249" t="s">
+        <v>237</v>
+      </c>
+      <c r="C249" t="s">
+        <v>238</v>
+      </c>
+      <c r="D249" t="s">
+        <v>239</v>
+      </c>
+      <c r="E249">
+        <v>57324</v>
+      </c>
+      <c r="F249" t="s">
+        <v>107</v>
+      </c>
+      <c r="G249" s="5">
+        <v>46030</v>
+      </c>
+      <c r="H249" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I249" s="5">
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
         <v>498</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B250" t="s">
         <v>35</v>
       </c>
-      <c r="C225" t="s">
+      <c r="C250" t="s">
         <v>499</v>
       </c>
-      <c r="D225" t="s">
+      <c r="D250" t="s">
         <v>500</v>
       </c>
-      <c r="E225">
+      <c r="E250">
         <v>57686</v>
       </c>
-      <c r="F225" t="s">
+      <c r="F250" t="s">
         <v>10</v>
       </c>
-      <c r="G225" s="5">
+      <c r="G250" s="5">
         <v>45976</v>
       </c>
-      <c r="H225" s="5">
+      <c r="H250" s="5">
         <v>46006</v>
       </c>
-      <c r="I225" s="5">
-        <v>46043</v>
+      <c r="I250" s="5">
+        <v>46097</v>
       </c>
     </row>
   </sheetData>

--- a/Utah_Index_of_Changes.xlsx
+++ b/Utah_Index_of_Changes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Shared drives\DAS_Rules_DAR\Index of Changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DB68CF-7E16-456E-B633-3D711C8EC43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19992BD-F88E-4B63-A373-7B94E136F441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AB629357-4CE5-4584-B8BD-0FC25277305B}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="607">
   <si>
     <t>Published Date</t>
   </si>
@@ -1684,6 +1684,183 @@
   </si>
   <si>
     <t>R661-25</t>
+  </si>
+  <si>
+    <t>Emerald Ash Borer Quarantine</t>
+  </si>
+  <si>
+    <t>Spongy Moth Quarantine</t>
+  </si>
+  <si>
+    <t>R68-14</t>
+  </si>
+  <si>
+    <t>Karnal Bunt Quarantine</t>
+  </si>
+  <si>
+    <t>R68-18</t>
+  </si>
+  <si>
+    <t>Paraprofessional/Paraeducator Programs, Assignments, and Qualifications</t>
+  </si>
+  <si>
+    <t>R277-324</t>
+  </si>
+  <si>
+    <t>Funding for Charter School Students With Disabilities on an IEP</t>
+  </si>
+  <si>
+    <t>R277-479</t>
+  </si>
+  <si>
+    <t>High School Course Grading Requirements</t>
+  </si>
+  <si>
+    <t>R277-717</t>
+  </si>
+  <si>
+    <t>State Council on Military Children</t>
+  </si>
+  <si>
+    <t>R277-929</t>
+  </si>
+  <si>
+    <t>Waste Management and Radiation Control, Waste Management</t>
+  </si>
+  <si>
+    <t>Cleanup Action and Risk-Based Closure Standards</t>
+  </si>
+  <si>
+    <t>R315-101</t>
+  </si>
+  <si>
+    <t>Substance Abuse and Mental Health, State Hospital</t>
+  </si>
+  <si>
+    <t>Forensic Mental Health Facility</t>
+  </si>
+  <si>
+    <t>R525-8</t>
+  </si>
+  <si>
+    <t>Utah Data Research Center</t>
+  </si>
+  <si>
+    <t>R765-1001</t>
+  </si>
+  <si>
+    <t>Data Breaches</t>
+  </si>
+  <si>
+    <t>R765-1010</t>
+  </si>
+  <si>
+    <t>Utah Engineering and Computer Science Scholarship Program</t>
+  </si>
+  <si>
+    <t>R765-608</t>
+  </si>
+  <si>
+    <t>Oil, Gas and Mining; Abandoned Mine Reclamation</t>
+  </si>
+  <si>
+    <t>Abandoned Mine Reclamation Regulation Definitions</t>
+  </si>
+  <si>
+    <t>R643-870</t>
+  </si>
+  <si>
+    <t>Abandoned Mine Reclamation Fund</t>
+  </si>
+  <si>
+    <t>R643-872</t>
+  </si>
+  <si>
+    <t>General Reclamation Requirements</t>
+  </si>
+  <si>
+    <t>R643-874</t>
+  </si>
+  <si>
+    <t>Noncoal Reclamation</t>
+  </si>
+  <si>
+    <t>R643-875</t>
+  </si>
+  <si>
+    <t>R643-877</t>
+  </si>
+  <si>
+    <t>Acquisition, Management, and Disposition of Lands and Water</t>
+  </si>
+  <si>
+    <t>R643-879</t>
+  </si>
+  <si>
+    <t>Reclamation on Private Land</t>
+  </si>
+  <si>
+    <t>R643-882</t>
+  </si>
+  <si>
+    <t>State Reclamation Plan</t>
+  </si>
+  <si>
+    <t>R643-884</t>
+  </si>
+  <si>
+    <t>State Reclamation Grants</t>
+  </si>
+  <si>
+    <t>R643-886</t>
+  </si>
+  <si>
+    <t>Special Conditions of Parole</t>
+  </si>
+  <si>
+    <t>R671-402</t>
+  </si>
+  <si>
+    <t>Driver License</t>
+  </si>
+  <si>
+    <t>Refugee, Asylee, or Covered Humanitarian Parolee Knowledge Test in Applicant's Native Language</t>
+  </si>
+  <si>
+    <t>R708-46</t>
+  </si>
+  <si>
+    <t>School and Institutional Trust Lands</t>
+  </si>
+  <si>
+    <t>Prohibited and Restricted Uses of Trust Lands</t>
+  </si>
+  <si>
+    <t>R850-12</t>
+  </si>
+  <si>
+    <t>Program Development</t>
+  </si>
+  <si>
+    <t>Establishment, Designation and Operation of Tollways</t>
+  </si>
+  <si>
+    <t>R926-9</t>
+  </si>
+  <si>
+    <t>Marda Dillree Corridor Preservation Fund</t>
+  </si>
+  <si>
+    <t>R940-7</t>
+  </si>
+  <si>
+    <t>County Recorder Standards</t>
+  </si>
+  <si>
+    <t>R255. Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HB 351 (2023) created and granted the County Recorder Standards Board with rulemaking authority. </t>
   </si>
 </sst>
 </file>
@@ -2383,8 +2560,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}" name="IndexofChanges2026" displayName="IndexofChanges2026" ref="A1:I250" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A1:I250" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}" name="IndexofChanges2026" displayName="IndexofChanges2026" ref="A1:I280" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A1:I280" xr:uid="{927DF3B7-FBC8-4A66-A8E3-73FF6D7BB25F}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A5D7328E-E900-42CC-861B-C0B93E9FA323}" name="Agency Name" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{6813DE60-D8C9-46E4-9980-0485DD9243AF}" name="Title Name"/>
@@ -2401,7 +2578,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{191C1026-42B8-4344-AC71-C8E2042CFE8C}" name="TitleAndRuleNumberChanges2026" displayName="TitleAndRuleNumberChanges2026" ref="A1:E2" insertRow="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{191C1026-42B8-4344-AC71-C8E2042CFE8C}" name="TitleAndRuleNumberChanges2026" displayName="TitleAndRuleNumberChanges2026" ref="A1:E2" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E2" xr:uid="{191C1026-42B8-4344-AC71-C8E2042CFE8C}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{82436A75-E093-4342-9AB0-13A6B5DDFCCA}" name="Old Agency" dataDxfId="4"/>
@@ -2731,7 +2908,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I250"/>
+  <dimension ref="A1:I280"/>
   <sheetFormatPr defaultColWidth="32.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.28515625" bestFit="1" customWidth="1"/>
@@ -3072,25 +3249,25 @@
         <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>501</v>
+        <v>548</v>
       </c>
       <c r="D12" t="s">
         <v>502</v>
       </c>
       <c r="E12">
-        <v>54512</v>
+        <v>57769</v>
       </c>
       <c r="F12" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G12" s="5">
-        <v>46097</v>
+        <v>46037</v>
       </c>
       <c r="H12" s="5">
-        <v>46104</v>
+        <v>46054</v>
       </c>
       <c r="I12" s="5">
-        <v>46097</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -3098,28 +3275,28 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>501</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>502</v>
       </c>
       <c r="E13">
-        <v>55403</v>
+        <v>54512</v>
       </c>
       <c r="F13" t="s">
         <v>107</v>
       </c>
       <c r="G13" s="5">
-        <v>46030</v>
+        <v>46097</v>
       </c>
       <c r="H13" s="5">
-        <v>46047</v>
+        <v>46104</v>
       </c>
       <c r="I13" s="5">
-        <v>46030</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -3127,28 +3304,28 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>549</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>550</v>
       </c>
       <c r="E14">
-        <v>55041</v>
+        <v>57771</v>
       </c>
       <c r="F14" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="G14" s="5">
-        <v>46030</v>
+        <v>46038</v>
       </c>
       <c r="H14" s="5">
-        <v>46047</v>
+        <v>46068</v>
       </c>
       <c r="I14" s="5">
-        <v>46030</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -3156,28 +3333,28 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>551</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>552</v>
       </c>
       <c r="E15">
-        <v>55034</v>
+        <v>57768</v>
       </c>
       <c r="F15" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="G15" s="5">
-        <v>46030</v>
+        <v>46037</v>
       </c>
       <c r="H15" s="5">
-        <v>46047</v>
+        <v>46054</v>
       </c>
       <c r="I15" s="5">
-        <v>46030</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -3188,25 +3365,25 @@
         <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>414</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>415</v>
+        <v>106</v>
       </c>
       <c r="E16">
-        <v>57525</v>
+        <v>55403</v>
       </c>
       <c r="F16" t="s">
         <v>107</v>
       </c>
       <c r="G16" s="5">
-        <v>46084</v>
+        <v>46030</v>
       </c>
       <c r="H16" s="5">
-        <v>46096</v>
+        <v>46047</v>
       </c>
       <c r="I16" s="5">
-        <v>46084</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -3214,28 +3391,28 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="E17">
-        <v>57488</v>
+        <v>55041</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G17" s="5">
-        <v>45912</v>
+        <v>46030</v>
       </c>
       <c r="H17" s="5">
-        <v>45931</v>
+        <v>46047</v>
       </c>
       <c r="I17" s="5">
-        <v>46029</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -3243,28 +3420,28 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="E18">
-        <v>57488</v>
+        <v>55034</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="G18" s="5">
-        <v>45966</v>
+        <v>46030</v>
       </c>
       <c r="H18" s="5">
-        <v>45992</v>
+        <v>46047</v>
       </c>
       <c r="I18" s="5">
-        <v>46029</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -3272,28 +3449,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>414</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>415</v>
       </c>
       <c r="E19">
-        <v>57403</v>
+        <v>57525</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G19" s="5">
-        <v>45887</v>
+        <v>46084</v>
       </c>
       <c r="H19" s="5">
-        <v>45915</v>
+        <v>46096</v>
       </c>
       <c r="I19" s="5">
-        <v>46029</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -3304,22 +3481,22 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E20">
-        <v>57403</v>
+        <v>57488</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G20" s="5">
-        <v>45966</v>
+        <v>45912</v>
       </c>
       <c r="H20" s="5">
-        <v>45992</v>
+        <v>45931</v>
       </c>
       <c r="I20" s="5">
         <v>46029</v>
@@ -3327,22 +3504,22 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="E21">
-        <v>57665</v>
+        <v>57488</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G21" s="5">
         <v>45966</v>
@@ -3351,94 +3528,94 @@
         <v>45992</v>
       </c>
       <c r="I21" s="5">
-        <v>46052</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>416</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>417</v>
+        <v>55</v>
       </c>
       <c r="E22">
-        <v>54255</v>
+        <v>57403</v>
       </c>
       <c r="F22" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G22" s="5">
-        <v>46093</v>
+        <v>45887</v>
       </c>
       <c r="H22" s="5">
-        <v>46096</v>
+        <v>45915</v>
       </c>
       <c r="I22" s="5">
-        <v>46093</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>416</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>417</v>
+        <v>55</v>
       </c>
       <c r="E23">
-        <v>57852</v>
+        <v>57403</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="G23" s="5">
-        <v>46093</v>
-      </c>
-      <c r="H23" t="s">
-        <v>65</v>
+        <v>45966</v>
+      </c>
+      <c r="H23" s="5">
+        <v>45992</v>
       </c>
       <c r="I23" s="5">
-        <v>46096</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E24">
-        <v>57528</v>
+        <v>57665</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G24" s="5">
-        <v>45930</v>
+        <v>45966</v>
       </c>
       <c r="H24" s="5">
-        <v>45945</v>
+        <v>45992</v>
       </c>
       <c r="I24" s="5">
-        <v>46023</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -3446,28 +3623,28 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>503</v>
+        <v>416</v>
       </c>
       <c r="D25" t="s">
-        <v>504</v>
+        <v>417</v>
       </c>
       <c r="E25">
-        <v>57192</v>
+        <v>54255</v>
       </c>
       <c r="F25" t="s">
         <v>107</v>
       </c>
       <c r="G25" s="5">
-        <v>46083</v>
+        <v>46093</v>
       </c>
       <c r="H25" s="5">
-        <v>46104</v>
+        <v>46096</v>
       </c>
       <c r="I25" s="5">
-        <v>46083</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -3475,28 +3652,28 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>505</v>
+        <v>416</v>
       </c>
       <c r="D26" t="s">
-        <v>506</v>
+        <v>417</v>
       </c>
       <c r="E26">
-        <v>57787</v>
+        <v>57852</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G26" s="5">
-        <v>46051</v>
-      </c>
-      <c r="H26" s="5">
-        <v>46068</v>
+        <v>46093</v>
+      </c>
+      <c r="H26" t="s">
+        <v>65</v>
       </c>
       <c r="I26" s="5">
-        <v>46105</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -3504,28 +3681,28 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>373</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>374</v>
+        <v>26</v>
       </c>
       <c r="E27">
-        <v>57754</v>
+        <v>57528</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G27" s="5">
-        <v>46027</v>
+        <v>45930</v>
       </c>
       <c r="H27" s="5">
-        <v>46037</v>
+        <v>45945</v>
       </c>
       <c r="I27" s="5">
-        <v>46077</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -3536,25 +3713,25 @@
         <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D28" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="E28">
-        <v>57745</v>
+        <v>57192</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G28" s="5">
-        <v>46014</v>
+        <v>46083</v>
       </c>
       <c r="H28" s="5">
-        <v>46068</v>
+        <v>46104</v>
       </c>
       <c r="I28" s="5">
-        <v>46111</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -3565,25 +3742,25 @@
         <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>505</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>506</v>
       </c>
       <c r="E29">
-        <v>57661</v>
+        <v>57787</v>
       </c>
       <c r="F29" t="s">
         <v>10</v>
       </c>
       <c r="G29" s="5">
-        <v>45965</v>
+        <v>46051</v>
       </c>
       <c r="H29" s="5">
-        <v>45992</v>
+        <v>46068</v>
       </c>
       <c r="I29" s="5">
-        <v>46037</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -3594,25 +3771,25 @@
         <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="D30" t="s">
-        <v>419</v>
+        <v>374</v>
       </c>
       <c r="E30">
-        <v>57633</v>
+        <v>57754</v>
       </c>
       <c r="F30" t="s">
         <v>10</v>
       </c>
       <c r="G30" s="5">
-        <v>45965</v>
+        <v>46027</v>
       </c>
       <c r="H30" s="5">
-        <v>45992</v>
+        <v>46037</v>
       </c>
       <c r="I30" s="5">
-        <v>46111</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -3623,25 +3800,25 @@
         <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>420</v>
+        <v>507</v>
       </c>
       <c r="D31" t="s">
-        <v>421</v>
+        <v>508</v>
       </c>
       <c r="E31">
-        <v>50288</v>
+        <v>57745</v>
       </c>
       <c r="F31" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G31" s="5">
-        <v>46083</v>
+        <v>46014</v>
       </c>
       <c r="H31" s="5">
-        <v>46096</v>
+        <v>46068</v>
       </c>
       <c r="I31" s="5">
-        <v>46083</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -3652,25 +3829,25 @@
         <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>509</v>
+        <v>57</v>
       </c>
       <c r="D32" t="s">
-        <v>510</v>
+        <v>58</v>
       </c>
       <c r="E32">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="F32" t="s">
         <v>10</v>
       </c>
       <c r="G32" s="5">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H32" s="5">
         <v>45992</v>
       </c>
       <c r="I32" s="5">
-        <v>46111</v>
+        <v>46037</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -3681,22 +3858,22 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>509</v>
+        <v>418</v>
       </c>
       <c r="D33" t="s">
-        <v>510</v>
+        <v>419</v>
       </c>
       <c r="E33">
-        <v>57657</v>
+        <v>57633</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G33" s="5">
-        <v>46045</v>
+        <v>45965</v>
       </c>
       <c r="H33" s="5">
-        <v>46068</v>
+        <v>45992</v>
       </c>
       <c r="I33" s="5">
         <v>46111</v>
@@ -3710,25 +3887,25 @@
         <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>420</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>421</v>
       </c>
       <c r="E34">
-        <v>56871</v>
+        <v>50288</v>
       </c>
       <c r="F34" t="s">
         <v>107</v>
       </c>
       <c r="G34" s="5">
-        <v>46029</v>
+        <v>46083</v>
       </c>
       <c r="H34" s="5">
-        <v>46047</v>
+        <v>46096</v>
       </c>
       <c r="I34" s="5">
-        <v>46029</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -3739,25 +3916,25 @@
         <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>509</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>510</v>
       </c>
       <c r="E35">
-        <v>50314</v>
+        <v>57657</v>
       </c>
       <c r="F35" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G35" s="5">
-        <v>46029</v>
+        <v>45964</v>
       </c>
       <c r="H35" s="5">
-        <v>46047</v>
+        <v>45992</v>
       </c>
       <c r="I35" s="5">
-        <v>46029</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -3768,25 +3945,25 @@
         <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="D36" t="s">
-        <v>423</v>
+        <v>510</v>
       </c>
       <c r="E36">
-        <v>56813</v>
+        <v>57657</v>
       </c>
       <c r="F36" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="G36" s="5">
-        <v>46083</v>
+        <v>46045</v>
       </c>
       <c r="H36" s="5">
-        <v>46096</v>
+        <v>46068</v>
       </c>
       <c r="I36" s="5">
-        <v>46083</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -3794,260 +3971,260 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>511</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>512</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>513</v>
+        <v>116</v>
       </c>
       <c r="E37">
-        <v>57786</v>
+        <v>56871</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G37" s="5">
-        <v>46051</v>
+        <v>46029</v>
       </c>
       <c r="H37" s="5">
-        <v>46068</v>
+        <v>46047</v>
       </c>
       <c r="I37" s="5">
-        <v>46105</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>514</v>
+        <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>515</v>
+        <v>117</v>
       </c>
       <c r="D38" t="s">
-        <v>516</v>
+        <v>118</v>
       </c>
       <c r="E38">
-        <v>54815</v>
+        <v>50314</v>
       </c>
       <c r="F38" t="s">
         <v>107</v>
       </c>
       <c r="G38" s="5">
-        <v>46097</v>
+        <v>46029</v>
       </c>
       <c r="H38" s="5">
-        <v>46104</v>
+        <v>46047</v>
       </c>
       <c r="I38" s="5">
-        <v>46097</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>517</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>518</v>
+        <v>422</v>
       </c>
       <c r="D39" t="s">
-        <v>519</v>
+        <v>423</v>
       </c>
       <c r="E39">
-        <v>57674</v>
+        <v>56813</v>
       </c>
       <c r="F39" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G39" s="5">
-        <v>45974</v>
+        <v>46083</v>
       </c>
       <c r="H39" s="5">
-        <v>45992</v>
+        <v>46096</v>
       </c>
       <c r="I39" s="5">
-        <v>46038</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>517</v>
+        <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>511</v>
       </c>
       <c r="C40" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="D40" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="E40">
-        <v>57672</v>
+        <v>57786</v>
       </c>
       <c r="F40" t="s">
         <v>10</v>
       </c>
       <c r="G40" s="5">
-        <v>45974</v>
+        <v>46051</v>
       </c>
       <c r="H40" s="5">
-        <v>45992</v>
+        <v>46068</v>
       </c>
       <c r="I40" s="5">
-        <v>46038</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>424</v>
+        <v>514</v>
       </c>
       <c r="B41" t="s">
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>425</v>
+        <v>515</v>
       </c>
       <c r="D41" t="s">
-        <v>426</v>
+        <v>516</v>
       </c>
       <c r="E41">
-        <v>55794</v>
+        <v>54815</v>
       </c>
       <c r="F41" t="s">
         <v>107</v>
       </c>
       <c r="G41" s="5">
-        <v>46087</v>
+        <v>46097</v>
       </c>
       <c r="H41" s="5">
-        <v>46096</v>
+        <v>46104</v>
       </c>
       <c r="I41" s="5">
-        <v>46087</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>424</v>
+        <v>517</v>
       </c>
       <c r="B42" t="s">
         <v>35</v>
       </c>
       <c r="C42" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D42" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E42">
-        <v>50375</v>
+        <v>57674</v>
       </c>
       <c r="F42" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G42" s="5">
-        <v>46087</v>
+        <v>45974</v>
       </c>
       <c r="H42" s="5">
-        <v>46098</v>
+        <v>45992</v>
       </c>
       <c r="I42" s="5">
-        <v>46087</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>258</v>
+        <v>517</v>
       </c>
       <c r="B43" t="s">
-        <v>259</v>
+        <v>35</v>
       </c>
       <c r="C43" t="s">
-        <v>260</v>
+        <v>520</v>
       </c>
       <c r="D43" t="s">
-        <v>261</v>
+        <v>521</v>
       </c>
       <c r="E43">
-        <v>57687</v>
+        <v>57672</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G43" s="5">
-        <v>45980</v>
+        <v>45974</v>
       </c>
       <c r="H43" s="5">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="I43" s="5">
-        <v>46066</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>258</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s">
-        <v>259</v>
+        <v>35</v>
       </c>
       <c r="C44" t="s">
-        <v>262</v>
+        <v>425</v>
       </c>
       <c r="D44" t="s">
-        <v>263</v>
+        <v>426</v>
       </c>
       <c r="E44">
-        <v>57688</v>
+        <v>55794</v>
       </c>
       <c r="F44" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G44" s="5">
-        <v>45980</v>
+        <v>46087</v>
       </c>
       <c r="H44" s="5">
-        <v>46006</v>
+        <v>46096</v>
       </c>
       <c r="I44" s="5">
-        <v>46066</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>258</v>
+        <v>424</v>
       </c>
       <c r="B45" t="s">
-        <v>259</v>
+        <v>35</v>
       </c>
       <c r="C45" t="s">
-        <v>264</v>
+        <v>522</v>
       </c>
       <c r="D45" t="s">
-        <v>265</v>
+        <v>523</v>
       </c>
       <c r="E45">
-        <v>57689</v>
+        <v>50375</v>
       </c>
       <c r="F45" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G45" s="5">
-        <v>45980</v>
+        <v>46087</v>
       </c>
       <c r="H45" s="5">
-        <v>46006</v>
+        <v>46098</v>
       </c>
       <c r="I45" s="5">
-        <v>46066</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -4058,13 +4235,13 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="E46">
-        <v>57690</v>
+        <v>57687</v>
       </c>
       <c r="F46" t="s">
         <v>19</v>
@@ -4084,25 +4261,25 @@
         <v>258</v>
       </c>
       <c r="B47" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C47" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="E47">
-        <v>57564</v>
+        <v>57688</v>
       </c>
       <c r="F47" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="G47" s="5">
-        <v>45947</v>
+        <v>45980</v>
       </c>
       <c r="H47" s="5">
-        <v>45976</v>
+        <v>46006</v>
       </c>
       <c r="I47" s="5">
         <v>46066</v>
@@ -4113,25 +4290,25 @@
         <v>258</v>
       </c>
       <c r="B48" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C48" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D48" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E48">
-        <v>57565</v>
+        <v>57689</v>
       </c>
       <c r="F48" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="G48" s="5">
-        <v>45947</v>
+        <v>45980</v>
       </c>
       <c r="H48" s="5">
-        <v>45976</v>
+        <v>46006</v>
       </c>
       <c r="I48" s="5">
         <v>46066</v>
@@ -4142,25 +4319,25 @@
         <v>258</v>
       </c>
       <c r="B49" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C49" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D49" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E49">
-        <v>57566</v>
+        <v>57690</v>
       </c>
       <c r="F49" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="G49" s="5">
-        <v>45947</v>
+        <v>45980</v>
       </c>
       <c r="H49" s="5">
-        <v>45976</v>
+        <v>46006</v>
       </c>
       <c r="I49" s="5">
         <v>46066</v>
@@ -4174,13 +4351,13 @@
         <v>268</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D50" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E50">
-        <v>57567</v>
+        <v>57564</v>
       </c>
       <c r="F50" t="s">
         <v>82</v>
@@ -4197,89 +4374,89 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="C51" t="s">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="D51" t="s">
-        <v>61</v>
+        <v>271</v>
       </c>
       <c r="E51">
-        <v>57677</v>
+        <v>57565</v>
       </c>
       <c r="F51" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G51" s="5">
-        <v>45975</v>
+        <v>45947</v>
       </c>
       <c r="H51" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I51" s="5">
-        <v>46029</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="C52" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="D52" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E52">
-        <v>57719</v>
+        <v>57566</v>
       </c>
       <c r="F52" t="s">
         <v>82</v>
       </c>
       <c r="G52" s="5">
-        <v>46006</v>
+        <v>45947</v>
       </c>
       <c r="H52" s="5">
-        <v>46023</v>
+        <v>45976</v>
       </c>
       <c r="I52" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="C53" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E53">
-        <v>57720</v>
+        <v>57567</v>
       </c>
       <c r="F53" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="G53" s="5">
-        <v>46006</v>
+        <v>45947</v>
       </c>
       <c r="H53" s="5">
-        <v>46023</v>
+        <v>45976</v>
       </c>
       <c r="I53" s="5">
-        <v>46062</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -4290,25 +4467,25 @@
         <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>427</v>
+        <v>60</v>
       </c>
       <c r="D54" t="s">
-        <v>428</v>
+        <v>61</v>
       </c>
       <c r="E54">
-        <v>57849</v>
+        <v>57677</v>
       </c>
       <c r="F54" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G54" s="5">
-        <v>46087</v>
-      </c>
-      <c r="H54" t="s">
-        <v>65</v>
+        <v>45975</v>
+      </c>
+      <c r="H54" s="5">
+        <v>45992</v>
       </c>
       <c r="I54" s="5">
-        <v>46096</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -4319,16 +4496,16 @@
         <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D55" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E55">
-        <v>57721</v>
+        <v>57719</v>
       </c>
       <c r="F55" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G55" s="5">
         <v>46006</v>
@@ -4348,16 +4525,16 @@
         <v>35</v>
       </c>
       <c r="C56" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D56" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E56">
-        <v>57722</v>
+        <v>57720</v>
       </c>
       <c r="F56" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="G56" s="5">
         <v>46006</v>
@@ -4377,25 +4554,25 @@
         <v>35</v>
       </c>
       <c r="C57" t="s">
-        <v>282</v>
+        <v>427</v>
       </c>
       <c r="D57" t="s">
-        <v>283</v>
+        <v>428</v>
       </c>
       <c r="E57">
-        <v>57723</v>
+        <v>57849</v>
       </c>
       <c r="F57" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G57" s="5">
-        <v>46006</v>
-      </c>
-      <c r="H57" s="5">
-        <v>46023</v>
+        <v>46087</v>
+      </c>
+      <c r="H57" t="s">
+        <v>65</v>
       </c>
       <c r="I57" s="5">
-        <v>46062</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -4406,13 +4583,13 @@
         <v>35</v>
       </c>
       <c r="C58" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D58" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E58">
-        <v>57724</v>
+        <v>57721</v>
       </c>
       <c r="F58" t="s">
         <v>10</v>
@@ -4435,25 +4612,25 @@
         <v>35</v>
       </c>
       <c r="C59" t="s">
-        <v>62</v>
+        <v>280</v>
       </c>
       <c r="D59" t="s">
-        <v>63</v>
+        <v>281</v>
       </c>
       <c r="E59">
-        <v>57737</v>
+        <v>57722</v>
       </c>
       <c r="F59" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G59" s="5">
-        <v>46008</v>
-      </c>
-      <c r="H59" t="s">
-        <v>65</v>
+        <v>46006</v>
+      </c>
+      <c r="H59" s="5">
+        <v>46023</v>
       </c>
       <c r="I59" s="5">
-        <v>46027</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -4464,25 +4641,25 @@
         <v>35</v>
       </c>
       <c r="C60" t="s">
-        <v>62</v>
+        <v>282</v>
       </c>
       <c r="D60" t="s">
-        <v>63</v>
+        <v>283</v>
       </c>
       <c r="E60">
-        <v>57765</v>
+        <v>57723</v>
       </c>
       <c r="F60" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G60" s="5">
-        <v>46037</v>
-      </c>
-      <c r="H60" t="s">
-        <v>65</v>
+        <v>46006</v>
+      </c>
+      <c r="H60" s="5">
+        <v>46023</v>
       </c>
       <c r="I60" s="5">
-        <v>46047</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -4493,25 +4670,25 @@
         <v>35</v>
       </c>
       <c r="C61" t="s">
-        <v>429</v>
+        <v>284</v>
       </c>
       <c r="D61" t="s">
-        <v>430</v>
+        <v>285</v>
       </c>
       <c r="E61">
-        <v>57761</v>
+        <v>57724</v>
       </c>
       <c r="F61" t="s">
         <v>10</v>
       </c>
       <c r="G61" s="5">
-        <v>46037</v>
+        <v>46006</v>
       </c>
       <c r="H61" s="5">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="I61" s="5">
-        <v>46091</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -4522,25 +4699,25 @@
         <v>35</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D62" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E62">
-        <v>57678</v>
+        <v>57737</v>
       </c>
       <c r="F62" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G62" s="5">
-        <v>45975</v>
-      </c>
-      <c r="H62" s="5">
-        <v>45992</v>
+        <v>46008</v>
+      </c>
+      <c r="H62" t="s">
+        <v>65</v>
       </c>
       <c r="I62" s="5">
-        <v>46029</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -4551,25 +4728,25 @@
         <v>35</v>
       </c>
       <c r="C63" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D63" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E63">
-        <v>57679</v>
+        <v>57765</v>
       </c>
       <c r="F63" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G63" s="5">
-        <v>45975</v>
-      </c>
-      <c r="H63" s="5">
-        <v>45992</v>
+        <v>46037</v>
+      </c>
+      <c r="H63" t="s">
+        <v>65</v>
       </c>
       <c r="I63" s="5">
-        <v>46029</v>
+        <v>46047</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -4580,25 +4757,25 @@
         <v>35</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>429</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>430</v>
       </c>
       <c r="E64">
-        <v>57735</v>
+        <v>57761</v>
       </c>
       <c r="F64" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G64" s="5">
-        <v>46007</v>
-      </c>
-      <c r="H64" t="s">
-        <v>65</v>
+        <v>46037</v>
+      </c>
+      <c r="H64" s="5">
+        <v>46054</v>
       </c>
       <c r="I64" s="5">
-        <v>46027</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -4609,25 +4786,25 @@
         <v>35</v>
       </c>
       <c r="C65" t="s">
-        <v>286</v>
+        <v>66</v>
       </c>
       <c r="D65" t="s">
-        <v>287</v>
+        <v>67</v>
       </c>
       <c r="E65">
-        <v>57725</v>
+        <v>57678</v>
       </c>
       <c r="F65" t="s">
         <v>10</v>
       </c>
       <c r="G65" s="5">
-        <v>46006</v>
+        <v>45975</v>
       </c>
       <c r="H65" s="5">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="I65" s="5">
-        <v>46062</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -4638,25 +4815,25 @@
         <v>35</v>
       </c>
       <c r="C66" t="s">
-        <v>288</v>
+        <v>553</v>
       </c>
       <c r="D66" t="s">
-        <v>289</v>
+        <v>554</v>
       </c>
       <c r="E66">
-        <v>57726</v>
+        <v>57795</v>
       </c>
       <c r="F66" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="5">
-        <v>46006</v>
+        <v>46070</v>
       </c>
       <c r="H66" s="5">
-        <v>46023</v>
+        <v>46082</v>
       </c>
       <c r="I66" s="5">
-        <v>46062</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -4667,25 +4844,25 @@
         <v>35</v>
       </c>
       <c r="C67" t="s">
-        <v>290</v>
+        <v>68</v>
       </c>
       <c r="D67" t="s">
-        <v>291</v>
+        <v>69</v>
       </c>
       <c r="E67">
-        <v>57727</v>
+        <v>57679</v>
       </c>
       <c r="F67" t="s">
         <v>10</v>
       </c>
       <c r="G67" s="5">
-        <v>46006</v>
+        <v>45975</v>
       </c>
       <c r="H67" s="5">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="I67" s="5">
-        <v>46062</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -4696,25 +4873,25 @@
         <v>35</v>
       </c>
       <c r="C68" t="s">
-        <v>292</v>
+        <v>70</v>
       </c>
       <c r="D68" t="s">
-        <v>293</v>
+        <v>71</v>
       </c>
       <c r="E68">
-        <v>57728</v>
+        <v>57735</v>
       </c>
       <c r="F68" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G68" s="5">
-        <v>46006</v>
-      </c>
-      <c r="H68" s="5">
-        <v>46023</v>
+        <v>46007</v>
+      </c>
+      <c r="H68" t="s">
+        <v>65</v>
       </c>
       <c r="I68" s="5">
-        <v>46062</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -4725,25 +4902,25 @@
         <v>35</v>
       </c>
       <c r="C69" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D69" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E69">
-        <v>57728</v>
+        <v>57725</v>
       </c>
       <c r="F69" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G69" s="5">
-        <v>46097</v>
+        <v>46006</v>
       </c>
       <c r="H69" s="5">
-        <v>46098</v>
+        <v>46023</v>
       </c>
       <c r="I69" s="5">
-        <v>46097</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -4754,25 +4931,25 @@
         <v>35</v>
       </c>
       <c r="C70" t="s">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="D70" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
       <c r="E70">
-        <v>55856</v>
+        <v>57796</v>
       </c>
       <c r="F70" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G70" s="5">
-        <v>46097</v>
+        <v>46070</v>
       </c>
       <c r="H70" s="5">
-        <v>46098</v>
+        <v>46082</v>
       </c>
       <c r="I70" s="5">
-        <v>46097</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -4783,25 +4960,25 @@
         <v>35</v>
       </c>
       <c r="C71" t="s">
-        <v>431</v>
+        <v>288</v>
       </c>
       <c r="D71" t="s">
-        <v>432</v>
+        <v>289</v>
       </c>
       <c r="E71">
-        <v>57762</v>
+        <v>57726</v>
       </c>
       <c r="F71" t="s">
         <v>10</v>
       </c>
       <c r="G71" s="5">
-        <v>46037</v>
+        <v>46006</v>
       </c>
       <c r="H71" s="5">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="I71" s="5">
-        <v>46091</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -4812,13 +4989,13 @@
         <v>35</v>
       </c>
       <c r="C72" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D72" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E72">
-        <v>57729</v>
+        <v>57727</v>
       </c>
       <c r="F72" t="s">
         <v>10</v>
@@ -4841,25 +5018,25 @@
         <v>35</v>
       </c>
       <c r="C73" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D73" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E73">
-        <v>57729</v>
+        <v>57728</v>
       </c>
       <c r="F73" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G73" s="5">
-        <v>46097</v>
+        <v>46006</v>
       </c>
       <c r="H73" s="5">
-        <v>46098</v>
+        <v>46023</v>
       </c>
       <c r="I73" s="5">
-        <v>46097</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -4870,25 +5047,25 @@
         <v>35</v>
       </c>
       <c r="C74" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D74" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E74">
-        <v>57730</v>
+        <v>57728</v>
       </c>
       <c r="F74" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G74" s="5">
-        <v>46006</v>
+        <v>46097</v>
       </c>
       <c r="H74" s="5">
-        <v>46023</v>
+        <v>46098</v>
       </c>
       <c r="I74" s="5">
-        <v>46062</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -4899,25 +5076,25 @@
         <v>35</v>
       </c>
       <c r="C75" t="s">
-        <v>296</v>
+        <v>524</v>
       </c>
       <c r="D75" t="s">
-        <v>297</v>
+        <v>525</v>
       </c>
       <c r="E75">
-        <v>57807</v>
+        <v>55856</v>
       </c>
       <c r="F75" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G75" s="5">
-        <v>46073</v>
-      </c>
-      <c r="H75" t="s">
-        <v>65</v>
+        <v>46097</v>
+      </c>
+      <c r="H75" s="5">
+        <v>46098</v>
       </c>
       <c r="I75" s="5">
-        <v>46082</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -4928,13 +5105,13 @@
         <v>35</v>
       </c>
       <c r="C76" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D76" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E76">
-        <v>57763</v>
+        <v>57762</v>
       </c>
       <c r="F76" t="s">
         <v>10</v>
@@ -4957,13 +5134,13 @@
         <v>35</v>
       </c>
       <c r="C77" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D77" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E77">
-        <v>57731</v>
+        <v>57729</v>
       </c>
       <c r="F77" t="s">
         <v>10</v>
@@ -4986,25 +5163,25 @@
         <v>35</v>
       </c>
       <c r="C78" t="s">
-        <v>435</v>
+        <v>294</v>
       </c>
       <c r="D78" t="s">
-        <v>436</v>
+        <v>295</v>
       </c>
       <c r="E78">
-        <v>57764</v>
+        <v>57729</v>
       </c>
       <c r="F78" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G78" s="5">
-        <v>46037</v>
+        <v>46097</v>
       </c>
       <c r="H78" s="5">
-        <v>46054</v>
+        <v>46098</v>
       </c>
       <c r="I78" s="5">
-        <v>46091</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -5015,25 +5192,25 @@
         <v>35</v>
       </c>
       <c r="C79" t="s">
-        <v>72</v>
+        <v>294</v>
       </c>
       <c r="D79" t="s">
-        <v>73</v>
+        <v>295</v>
       </c>
       <c r="E79">
-        <v>57680</v>
+        <v>57797</v>
       </c>
       <c r="F79" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G79" s="5">
-        <v>45975</v>
+        <v>46070</v>
       </c>
       <c r="H79" s="5">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="I79" s="5">
-        <v>46029</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -5044,25 +5221,25 @@
         <v>35</v>
       </c>
       <c r="C80" t="s">
-        <v>526</v>
+        <v>296</v>
       </c>
       <c r="D80" t="s">
-        <v>527</v>
+        <v>297</v>
       </c>
       <c r="E80">
-        <v>56374</v>
+        <v>57730</v>
       </c>
       <c r="F80" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G80" s="5">
-        <v>46097</v>
+        <v>46006</v>
       </c>
       <c r="H80" s="5">
-        <v>46098</v>
+        <v>46023</v>
       </c>
       <c r="I80" s="5">
-        <v>46097</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -5073,25 +5250,25 @@
         <v>35</v>
       </c>
       <c r="C81" t="s">
-        <v>528</v>
+        <v>296</v>
       </c>
       <c r="D81" t="s">
-        <v>529</v>
+        <v>297</v>
       </c>
       <c r="E81">
-        <v>57186</v>
+        <v>57807</v>
       </c>
       <c r="F81" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G81" s="5">
-        <v>46097</v>
-      </c>
-      <c r="H81" s="5">
-        <v>46098</v>
+        <v>46073</v>
+      </c>
+      <c r="H81" t="s">
+        <v>65</v>
       </c>
       <c r="I81" s="5">
-        <v>46097</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -5102,866 +5279,866 @@
         <v>35</v>
       </c>
       <c r="C82" t="s">
-        <v>530</v>
+        <v>433</v>
       </c>
       <c r="D82" t="s">
-        <v>531</v>
+        <v>434</v>
       </c>
       <c r="E82">
-        <v>52865</v>
+        <v>57763</v>
       </c>
       <c r="F82" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G82" s="5">
-        <v>46097</v>
+        <v>46037</v>
       </c>
       <c r="H82" s="5">
-        <v>46098</v>
+        <v>46054</v>
       </c>
       <c r="I82" s="5">
-        <v>46097</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B83" t="s">
-        <v>300</v>
+        <v>35</v>
       </c>
       <c r="C83" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D83" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E83">
-        <v>57666</v>
+        <v>57731</v>
       </c>
       <c r="F83" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="5">
-        <v>45966</v>
+        <v>46006</v>
       </c>
       <c r="H83" s="5">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I83" s="5">
-        <v>46057</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B84" t="s">
-        <v>300</v>
+        <v>35</v>
       </c>
       <c r="C84" t="s">
-        <v>303</v>
+        <v>557</v>
       </c>
       <c r="D84" t="s">
-        <v>304</v>
+        <v>558</v>
       </c>
       <c r="E84">
-        <v>53313</v>
+        <v>57798</v>
       </c>
       <c r="F84" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G84" s="5">
-        <v>46057</v>
+        <v>46070</v>
       </c>
       <c r="H84" s="5">
-        <v>46062</v>
+        <v>46082</v>
       </c>
       <c r="I84" s="5">
-        <v>46057</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B85" t="s">
-        <v>437</v>
+        <v>35</v>
       </c>
       <c r="C85" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D85" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E85">
-        <v>57815</v>
+        <v>57764</v>
       </c>
       <c r="F85" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G85" s="5">
-        <v>46078</v>
-      </c>
-      <c r="H85" t="s">
-        <v>65</v>
+        <v>46037</v>
+      </c>
+      <c r="H85" s="5">
+        <v>46054</v>
       </c>
       <c r="I85" s="5">
-        <v>46083</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B86" t="s">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="C86" t="s">
-        <v>306</v>
+        <v>72</v>
       </c>
       <c r="D86" t="s">
-        <v>307</v>
+        <v>73</v>
       </c>
       <c r="E86">
-        <v>50710</v>
+        <v>57680</v>
       </c>
       <c r="F86" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G86" s="5">
-        <v>46062</v>
+        <v>45975</v>
       </c>
       <c r="H86" s="5">
-        <v>46066</v>
+        <v>45992</v>
       </c>
       <c r="I86" s="5">
-        <v>46062</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B87" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="C87" t="s">
-        <v>76</v>
+        <v>526</v>
       </c>
       <c r="D87" t="s">
-        <v>77</v>
+        <v>527</v>
       </c>
       <c r="E87">
-        <v>57545</v>
+        <v>56374</v>
       </c>
       <c r="F87" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G87" s="5">
-        <v>45939</v>
+        <v>46097</v>
       </c>
       <c r="H87" s="5">
-        <v>45962</v>
+        <v>46098</v>
       </c>
       <c r="I87" s="5">
-        <v>46034</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B88" t="s">
         <v>35</v>
       </c>
       <c r="C88" t="s">
-        <v>376</v>
+        <v>528</v>
       </c>
       <c r="D88" t="s">
-        <v>377</v>
+        <v>529</v>
       </c>
       <c r="E88">
-        <v>50789</v>
+        <v>57186</v>
       </c>
       <c r="F88" t="s">
-        <v>357</v>
+        <v>107</v>
       </c>
       <c r="G88" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H88" t="s">
-        <v>358</v>
+        <v>46097</v>
+      </c>
+      <c r="H88" s="5">
+        <v>46098</v>
       </c>
       <c r="I88" s="5">
-        <v>46078</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B89" t="s">
         <v>35</v>
       </c>
       <c r="C89" t="s">
-        <v>378</v>
+        <v>530</v>
       </c>
       <c r="D89" t="s">
-        <v>379</v>
+        <v>531</v>
       </c>
       <c r="E89">
-        <v>50793</v>
+        <v>52865</v>
       </c>
       <c r="F89" t="s">
-        <v>357</v>
+        <v>107</v>
       </c>
       <c r="G89" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H89" t="s">
-        <v>358</v>
+        <v>46097</v>
+      </c>
+      <c r="H89" s="5">
+        <v>46098</v>
       </c>
       <c r="I89" s="5">
-        <v>46078</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="B90" t="s">
         <v>35</v>
       </c>
       <c r="C90" t="s">
-        <v>380</v>
+        <v>559</v>
       </c>
       <c r="D90" t="s">
-        <v>381</v>
+        <v>560</v>
       </c>
       <c r="E90">
-        <v>50790</v>
+        <v>57799</v>
       </c>
       <c r="F90" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="G90" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H90" t="s">
-        <v>358</v>
+        <v>46070</v>
+      </c>
+      <c r="H90" s="5">
+        <v>46082</v>
       </c>
       <c r="I90" s="5">
-        <v>46078</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>375</v>
+        <v>74</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>300</v>
       </c>
       <c r="C91" t="s">
-        <v>382</v>
+        <v>301</v>
       </c>
       <c r="D91" t="s">
-        <v>383</v>
+        <v>302</v>
       </c>
       <c r="E91">
-        <v>50799</v>
+        <v>57666</v>
       </c>
       <c r="F91" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="G91" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H91" t="s">
-        <v>358</v>
+        <v>45966</v>
+      </c>
+      <c r="H91" s="5">
+        <v>45992</v>
       </c>
       <c r="I91" s="5">
-        <v>46078</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>375</v>
+        <v>74</v>
       </c>
       <c r="B92" t="s">
-        <v>35</v>
+        <v>300</v>
       </c>
       <c r="C92" t="s">
-        <v>384</v>
+        <v>303</v>
       </c>
       <c r="D92" t="s">
-        <v>385</v>
+        <v>304</v>
       </c>
       <c r="E92">
-        <v>50803</v>
+        <v>53313</v>
       </c>
       <c r="F92" t="s">
-        <v>357</v>
+        <v>107</v>
       </c>
       <c r="G92" s="5">
-        <v>46077</v>
-      </c>
-      <c r="H92" t="s">
-        <v>358</v>
+        <v>46057</v>
+      </c>
+      <c r="H92" s="5">
+        <v>46062</v>
       </c>
       <c r="I92" s="5">
-        <v>46078</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="B93" t="s">
-        <v>35</v>
+        <v>437</v>
       </c>
       <c r="C93" t="s">
-        <v>120</v>
+        <v>438</v>
       </c>
       <c r="D93" t="s">
-        <v>121</v>
+        <v>439</v>
       </c>
       <c r="E93">
-        <v>50812</v>
+        <v>57815</v>
       </c>
       <c r="F93" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G93" s="5">
-        <v>46028</v>
-      </c>
-      <c r="H93" s="5">
-        <v>46047</v>
+        <v>46078</v>
+      </c>
+      <c r="H93" t="s">
+        <v>65</v>
       </c>
       <c r="I93" s="5">
-        <v>46028</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="B94" t="s">
-        <v>440</v>
+        <v>305</v>
       </c>
       <c r="C94" t="s">
-        <v>441</v>
+        <v>306</v>
       </c>
       <c r="D94" t="s">
-        <v>442</v>
+        <v>307</v>
       </c>
       <c r="E94">
-        <v>53490</v>
+        <v>50710</v>
       </c>
       <c r="F94" t="s">
         <v>107</v>
       </c>
       <c r="G94" s="5">
-        <v>46091</v>
+        <v>46062</v>
       </c>
       <c r="H94" s="5">
-        <v>46096</v>
+        <v>46066</v>
       </c>
       <c r="I94" s="5">
-        <v>46091</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="B95" t="s">
-        <v>440</v>
+        <v>75</v>
       </c>
       <c r="C95" t="s">
-        <v>443</v>
+        <v>76</v>
       </c>
       <c r="D95" t="s">
-        <v>444</v>
+        <v>77</v>
       </c>
       <c r="E95">
-        <v>54546</v>
+        <v>57545</v>
       </c>
       <c r="F95" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G95" s="5">
-        <v>46091</v>
+        <v>45939</v>
       </c>
       <c r="H95" s="5">
-        <v>46096</v>
+        <v>45962</v>
       </c>
       <c r="I95" s="5">
-        <v>46091</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="B96" t="s">
-        <v>122</v>
+        <v>561</v>
       </c>
       <c r="C96" t="s">
-        <v>123</v>
+        <v>562</v>
       </c>
       <c r="D96" t="s">
-        <v>124</v>
+        <v>563</v>
       </c>
       <c r="E96">
-        <v>57692</v>
+        <v>57803</v>
       </c>
       <c r="F96" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="5">
-        <v>45987</v>
+        <v>46070</v>
       </c>
       <c r="H96" s="5">
-        <v>46006</v>
+        <v>46082</v>
       </c>
       <c r="I96" s="5">
-        <v>46043</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>16</v>
+        <v>375</v>
       </c>
       <c r="B97" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="C97" t="s">
-        <v>125</v>
+        <v>376</v>
       </c>
       <c r="D97" t="s">
-        <v>126</v>
+        <v>377</v>
       </c>
       <c r="E97">
-        <v>57693</v>
+        <v>50789</v>
       </c>
       <c r="F97" t="s">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="G97" s="5">
-        <v>45987</v>
-      </c>
-      <c r="H97" s="5">
-        <v>46006</v>
+        <v>46077</v>
+      </c>
+      <c r="H97" t="s">
+        <v>358</v>
       </c>
       <c r="I97" s="5">
-        <v>46043</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>16</v>
+        <v>375</v>
       </c>
       <c r="B98" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="C98" t="s">
-        <v>127</v>
+        <v>378</v>
       </c>
       <c r="D98" t="s">
-        <v>128</v>
+        <v>379</v>
       </c>
       <c r="E98">
-        <v>57694</v>
+        <v>50793</v>
       </c>
       <c r="F98" t="s">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="G98" s="5">
-        <v>45987</v>
-      </c>
-      <c r="H98" s="5">
-        <v>46006</v>
+        <v>46077</v>
+      </c>
+      <c r="H98" t="s">
+        <v>358</v>
       </c>
       <c r="I98" s="5">
-        <v>46043</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>78</v>
+        <v>375</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C99" t="s">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="D99" t="s">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="E99">
-        <v>57684</v>
+        <v>50790</v>
       </c>
       <c r="F99" t="s">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="G99" s="5">
-        <v>45975</v>
-      </c>
-      <c r="H99" s="5">
-        <v>45992</v>
+        <v>46077</v>
+      </c>
+      <c r="H99" t="s">
+        <v>358</v>
       </c>
       <c r="I99" s="5">
-        <v>46035</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>78</v>
+        <v>375</v>
       </c>
       <c r="B100" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C100" t="s">
-        <v>532</v>
+        <v>382</v>
       </c>
       <c r="D100" t="s">
-        <v>533</v>
+        <v>383</v>
       </c>
       <c r="E100">
-        <v>57788</v>
+        <v>50799</v>
       </c>
       <c r="F100" t="s">
-        <v>19</v>
+        <v>357</v>
       </c>
       <c r="G100" s="5">
-        <v>46055</v>
-      </c>
-      <c r="H100" s="5">
-        <v>46068</v>
+        <v>46077</v>
+      </c>
+      <c r="H100" t="s">
+        <v>358</v>
       </c>
       <c r="I100" s="5">
-        <v>46108</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>78</v>
+        <v>375</v>
       </c>
       <c r="B101" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C101" t="s">
-        <v>129</v>
+        <v>384</v>
       </c>
       <c r="D101" t="s">
-        <v>130</v>
+        <v>385</v>
       </c>
       <c r="E101">
-        <v>57696</v>
+        <v>50803</v>
       </c>
       <c r="F101" t="s">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="G101" s="5">
-        <v>45989</v>
-      </c>
-      <c r="H101" s="5">
-        <v>46006</v>
+        <v>46077</v>
+      </c>
+      <c r="H101" t="s">
+        <v>358</v>
       </c>
       <c r="I101" s="5">
-        <v>46050</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="B102" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C102" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D102" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E102">
-        <v>57696</v>
+        <v>50812</v>
       </c>
       <c r="F102" t="s">
         <v>107</v>
       </c>
       <c r="G102" s="5">
-        <v>46059</v>
+        <v>46028</v>
       </c>
       <c r="H102" s="5">
-        <v>46062</v>
+        <v>46047</v>
       </c>
       <c r="I102" s="5">
-        <v>46059</v>
+        <v>46028</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>440</v>
       </c>
       <c r="C103" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D103" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E103">
-        <v>57746</v>
+        <v>53490</v>
       </c>
       <c r="F103" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G103" s="5">
-        <v>46020</v>
+        <v>46091</v>
       </c>
       <c r="H103" s="5">
-        <v>46037</v>
+        <v>46096</v>
       </c>
       <c r="I103" s="5">
-        <v>46097</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B104" t="s">
-        <v>131</v>
+        <v>440</v>
       </c>
       <c r="C104" t="s">
-        <v>123</v>
+        <v>443</v>
       </c>
       <c r="D104" t="s">
-        <v>132</v>
+        <v>444</v>
       </c>
       <c r="E104">
-        <v>57616</v>
+        <v>54546</v>
       </c>
       <c r="F104" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G104" s="5">
-        <v>45954</v>
+        <v>46091</v>
       </c>
       <c r="H104" s="5">
-        <v>45976</v>
+        <v>46096</v>
       </c>
       <c r="I104" s="5">
-        <v>46048</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B105" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C105" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D105" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E105">
-        <v>57588</v>
+        <v>57692</v>
       </c>
       <c r="F105" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="G105" s="5">
-        <v>45951</v>
+        <v>45987</v>
       </c>
       <c r="H105" s="5">
-        <v>45976</v>
+        <v>46006</v>
       </c>
       <c r="I105" s="5">
-        <v>46048</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B106" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C106" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D106" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="E106">
-        <v>57589</v>
+        <v>57693</v>
       </c>
       <c r="F106" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="5">
-        <v>45951</v>
+        <v>45987</v>
       </c>
       <c r="H106" s="5">
-        <v>45976</v>
+        <v>46006</v>
       </c>
       <c r="I106" s="5">
-        <v>46048</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B107" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C107" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D107" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E107">
-        <v>57640</v>
+        <v>57694</v>
       </c>
       <c r="F107" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="5">
-        <v>45963</v>
+        <v>45987</v>
       </c>
       <c r="H107" s="5">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="I107" s="5">
-        <v>46048</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B108" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="C108" t="s">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="D108" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="E108">
-        <v>57584</v>
+        <v>57684</v>
       </c>
       <c r="F108" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="G108" s="5">
-        <v>45951</v>
+        <v>45975</v>
       </c>
       <c r="H108" s="5">
-        <v>45976</v>
+        <v>45992</v>
       </c>
       <c r="I108" s="5">
-        <v>46048</v>
+        <v>46035</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B109" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="C109" t="s">
-        <v>142</v>
+        <v>532</v>
       </c>
       <c r="D109" t="s">
-        <v>143</v>
+        <v>533</v>
       </c>
       <c r="E109">
-        <v>57585</v>
+        <v>57788</v>
       </c>
       <c r="F109" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="G109" s="5">
-        <v>45951</v>
+        <v>46055</v>
       </c>
       <c r="H109" s="5">
-        <v>45976</v>
+        <v>46068</v>
       </c>
       <c r="I109" s="5">
-        <v>46048</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B110" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="C110" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D110" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="E110">
-        <v>57586</v>
+        <v>57696</v>
       </c>
       <c r="F110" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="G110" s="5">
-        <v>45951</v>
+        <v>45989</v>
       </c>
       <c r="H110" s="5">
-        <v>45976</v>
+        <v>46006</v>
       </c>
       <c r="I110" s="5">
-        <v>46048</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B111" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="C111" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="D111" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="E111">
-        <v>57587</v>
+        <v>57696</v>
       </c>
       <c r="F111" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G111" s="5">
-        <v>45951</v>
+        <v>46059</v>
       </c>
       <c r="H111" s="5">
-        <v>45976</v>
+        <v>46062</v>
       </c>
       <c r="I111" s="5">
-        <v>46048</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -5969,28 +6146,28 @@
         <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>308</v>
+        <v>35</v>
       </c>
       <c r="C112" t="s">
-        <v>309</v>
+        <v>445</v>
       </c>
       <c r="D112" t="s">
-        <v>310</v>
+        <v>446</v>
       </c>
       <c r="E112">
-        <v>57777</v>
+        <v>57746</v>
       </c>
       <c r="F112" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="G112" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H112" t="s">
-        <v>65</v>
+        <v>46020</v>
+      </c>
+      <c r="H112" s="5">
+        <v>46037</v>
       </c>
       <c r="I112" s="5">
-        <v>46055</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -5998,28 +6175,28 @@
         <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>308</v>
+        <v>131</v>
       </c>
       <c r="C113" t="s">
-        <v>311</v>
+        <v>123</v>
       </c>
       <c r="D113" t="s">
-        <v>312</v>
+        <v>132</v>
       </c>
       <c r="E113">
-        <v>57778</v>
+        <v>57616</v>
       </c>
       <c r="F113" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G113" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H113" t="s">
-        <v>65</v>
+        <v>45954</v>
+      </c>
+      <c r="H113" s="5">
+        <v>45976</v>
       </c>
       <c r="I113" s="5">
-        <v>46055</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -6027,28 +6204,28 @@
         <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>308</v>
+        <v>131</v>
       </c>
       <c r="C114" t="s">
-        <v>313</v>
+        <v>133</v>
       </c>
       <c r="D114" t="s">
-        <v>314</v>
+        <v>134</v>
       </c>
       <c r="E114">
-        <v>57775</v>
+        <v>57588</v>
       </c>
       <c r="F114" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G114" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H114" t="s">
-        <v>65</v>
+        <v>45951</v>
+      </c>
+      <c r="H114" s="5">
+        <v>45976</v>
       </c>
       <c r="I114" s="5">
-        <v>46055</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -6056,28 +6233,28 @@
         <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>308</v>
+        <v>131</v>
       </c>
       <c r="C115" t="s">
-        <v>315</v>
+        <v>135</v>
       </c>
       <c r="D115" t="s">
-        <v>316</v>
+        <v>136</v>
       </c>
       <c r="E115">
-        <v>57776</v>
+        <v>57589</v>
       </c>
       <c r="F115" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G115" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H115" t="s">
-        <v>65</v>
+        <v>45951</v>
+      </c>
+      <c r="H115" s="5">
+        <v>45976</v>
       </c>
       <c r="I115" s="5">
-        <v>46055</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -6085,28 +6262,28 @@
         <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>317</v>
+        <v>131</v>
       </c>
       <c r="C116" t="s">
-        <v>318</v>
+        <v>137</v>
       </c>
       <c r="D116" t="s">
-        <v>319</v>
+        <v>138</v>
       </c>
       <c r="E116">
-        <v>57782</v>
+        <v>57640</v>
       </c>
       <c r="F116" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G116" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H116" t="s">
-        <v>65</v>
+        <v>45963</v>
+      </c>
+      <c r="H116" s="5">
+        <v>45992</v>
       </c>
       <c r="I116" s="5">
-        <v>46055</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -6114,28 +6291,28 @@
         <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="C117" t="s">
-        <v>320</v>
+        <v>139</v>
       </c>
       <c r="D117" t="s">
-        <v>321</v>
+        <v>140</v>
       </c>
       <c r="E117">
-        <v>57780</v>
+        <v>57584</v>
       </c>
       <c r="F117" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="G117" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H117" t="s">
-        <v>65</v>
+        <v>45951</v>
+      </c>
+      <c r="H117" s="5">
+        <v>45976</v>
       </c>
       <c r="I117" s="5">
-        <v>46055</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -6143,28 +6320,28 @@
         <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="C118" t="s">
-        <v>386</v>
+        <v>142</v>
       </c>
       <c r="D118" t="s">
-        <v>387</v>
+        <v>143</v>
       </c>
       <c r="E118">
-        <v>57703</v>
+        <v>57585</v>
       </c>
       <c r="F118" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G118" s="5">
-        <v>45993</v>
+        <v>45951</v>
       </c>
       <c r="H118" s="5">
-        <v>46023</v>
+        <v>45976</v>
       </c>
       <c r="I118" s="5">
-        <v>46070</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -6172,28 +6349,28 @@
         <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="C119" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D119" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E119">
-        <v>57781</v>
+        <v>57586</v>
       </c>
       <c r="F119" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="G119" s="5">
-        <v>46083</v>
+        <v>45951</v>
       </c>
       <c r="H119" s="5">
-        <v>46096</v>
+        <v>45976</v>
       </c>
       <c r="I119" s="5">
-        <v>46083</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -6201,28 +6378,28 @@
         <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="C120" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D120" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E120">
-        <v>57781</v>
+        <v>57587</v>
       </c>
       <c r="F120" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="G120" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H120" t="s">
-        <v>65</v>
+        <v>45951</v>
+      </c>
+      <c r="H120" s="5">
+        <v>45976</v>
       </c>
       <c r="I120" s="5">
-        <v>46052</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -6230,28 +6407,28 @@
         <v>17</v>
       </c>
       <c r="B121" t="s">
-        <v>151</v>
+        <v>308</v>
       </c>
       <c r="C121" t="s">
-        <v>152</v>
+        <v>309</v>
       </c>
       <c r="D121" t="s">
-        <v>153</v>
+        <v>310</v>
       </c>
       <c r="E121">
-        <v>57618</v>
+        <v>57777</v>
       </c>
       <c r="F121" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G121" s="5">
-        <v>45954</v>
-      </c>
-      <c r="H121" s="5">
-        <v>45976</v>
+        <v>46049</v>
+      </c>
+      <c r="H121" t="s">
+        <v>65</v>
       </c>
       <c r="I121" s="5">
-        <v>46070</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -6259,28 +6436,28 @@
         <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>154</v>
+        <v>308</v>
       </c>
       <c r="C122" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D122" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="E122">
-        <v>55992</v>
+        <v>57778</v>
       </c>
       <c r="F122" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G122" s="5">
-        <v>46057</v>
-      </c>
-      <c r="H122" s="5">
-        <v>46062</v>
+        <v>46049</v>
+      </c>
+      <c r="H122" t="s">
+        <v>65</v>
       </c>
       <c r="I122" s="5">
-        <v>46057</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -6288,28 +6465,28 @@
         <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>154</v>
+        <v>308</v>
       </c>
       <c r="C123" t="s">
-        <v>155</v>
+        <v>313</v>
       </c>
       <c r="D123" t="s">
-        <v>156</v>
+        <v>314</v>
       </c>
       <c r="E123">
-        <v>57641</v>
+        <v>57775</v>
       </c>
       <c r="F123" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="G123" s="5">
-        <v>45963</v>
-      </c>
-      <c r="H123" s="5">
-        <v>45992</v>
+        <v>46049</v>
+      </c>
+      <c r="H123" t="s">
+        <v>65</v>
       </c>
       <c r="I123" s="5">
-        <v>46042</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -6317,28 +6494,28 @@
         <v>17</v>
       </c>
       <c r="B124" t="s">
-        <v>157</v>
+        <v>308</v>
       </c>
       <c r="C124" t="s">
-        <v>158</v>
+        <v>315</v>
       </c>
       <c r="D124" t="s">
-        <v>159</v>
+        <v>316</v>
       </c>
       <c r="E124">
-        <v>57645</v>
+        <v>57776</v>
       </c>
       <c r="F124" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G124" s="5">
-        <v>45964</v>
-      </c>
-      <c r="H124" s="5">
-        <v>45992</v>
+        <v>46049</v>
+      </c>
+      <c r="H124" t="s">
+        <v>65</v>
       </c>
       <c r="I124" s="5">
-        <v>46042</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -6346,28 +6523,28 @@
         <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>160</v>
+        <v>317</v>
       </c>
       <c r="C125" t="s">
-        <v>161</v>
+        <v>318</v>
       </c>
       <c r="D125" t="s">
-        <v>162</v>
+        <v>319</v>
       </c>
       <c r="E125">
-        <v>57646</v>
+        <v>57782</v>
       </c>
       <c r="F125" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G125" s="5">
-        <v>45964</v>
-      </c>
-      <c r="H125" s="5">
-        <v>45992</v>
+        <v>46049</v>
+      </c>
+      <c r="H125" t="s">
+        <v>65</v>
       </c>
       <c r="I125" s="5">
-        <v>46048</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -6375,28 +6552,28 @@
         <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C126" t="s">
-        <v>163</v>
+        <v>320</v>
       </c>
       <c r="D126" t="s">
-        <v>164</v>
+        <v>321</v>
       </c>
       <c r="E126">
-        <v>57647</v>
+        <v>57780</v>
       </c>
       <c r="F126" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G126" s="5">
-        <v>45964</v>
-      </c>
-      <c r="H126" s="5">
-        <v>45992</v>
+        <v>46049</v>
+      </c>
+      <c r="H126" t="s">
+        <v>65</v>
       </c>
       <c r="I126" s="5">
-        <v>46048</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -6404,28 +6581,28 @@
         <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C127" t="s">
-        <v>165</v>
+        <v>386</v>
       </c>
       <c r="D127" t="s">
-        <v>166</v>
+        <v>387</v>
       </c>
       <c r="E127">
-        <v>57648</v>
+        <v>57703</v>
       </c>
       <c r="F127" t="s">
         <v>10</v>
       </c>
       <c r="G127" s="5">
-        <v>45964</v>
+        <v>45993</v>
       </c>
       <c r="H127" s="5">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I127" s="5">
-        <v>46048</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -6433,28 +6610,28 @@
         <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C128" t="s">
-        <v>324</v>
+        <v>149</v>
       </c>
       <c r="D128" t="s">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="E128">
-        <v>56446</v>
+        <v>57781</v>
       </c>
       <c r="F128" t="s">
         <v>107</v>
       </c>
       <c r="G128" s="5">
-        <v>46038</v>
+        <v>46083</v>
       </c>
       <c r="H128" s="5">
-        <v>46055</v>
+        <v>46096</v>
       </c>
       <c r="I128" s="5">
-        <v>46038</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
@@ -6462,28 +6639,28 @@
         <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C129" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="D129" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E129">
-        <v>57652</v>
+        <v>57781</v>
       </c>
       <c r="F129" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G129" s="5">
-        <v>45964</v>
-      </c>
-      <c r="H129" s="5">
-        <v>45992</v>
+        <v>46049</v>
+      </c>
+      <c r="H129" t="s">
+        <v>65</v>
       </c>
       <c r="I129" s="5">
-        <v>46042</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -6491,28 +6668,28 @@
         <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="C130" t="s">
-        <v>534</v>
+        <v>152</v>
       </c>
       <c r="D130" t="s">
-        <v>535</v>
+        <v>153</v>
       </c>
       <c r="E130">
-        <v>57699</v>
+        <v>57618</v>
       </c>
       <c r="F130" t="s">
         <v>10</v>
       </c>
       <c r="G130" s="5">
-        <v>45992</v>
+        <v>45954</v>
       </c>
       <c r="H130" s="5">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c r="I130" s="5">
-        <v>46106</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -6520,28 +6697,28 @@
         <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>170</v>
+        <v>322</v>
       </c>
       <c r="D131" t="s">
-        <v>171</v>
+        <v>323</v>
       </c>
       <c r="E131">
-        <v>57653</v>
+        <v>55992</v>
       </c>
       <c r="F131" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G131" s="5">
-        <v>45964</v>
+        <v>46057</v>
       </c>
       <c r="H131" s="5">
-        <v>45992</v>
+        <v>46062</v>
       </c>
       <c r="I131" s="5">
-        <v>46042</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -6549,25 +6726,25 @@
         <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C132" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="D132" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="E132">
-        <v>57579</v>
+        <v>57641</v>
       </c>
       <c r="F132" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G132" s="5">
-        <v>45951</v>
+        <v>45963</v>
       </c>
       <c r="H132" s="5">
-        <v>45976</v>
+        <v>45992</v>
       </c>
       <c r="I132" s="5">
         <v>46042</v>
@@ -6578,28 +6755,28 @@
         <v>17</v>
       </c>
       <c r="B133" t="s">
-        <v>388</v>
+        <v>157</v>
       </c>
       <c r="C133" t="s">
-        <v>447</v>
+        <v>158</v>
       </c>
       <c r="D133" t="s">
-        <v>448</v>
+        <v>159</v>
       </c>
       <c r="E133">
-        <v>56879</v>
+        <v>57645</v>
       </c>
       <c r="F133" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G133" s="5">
-        <v>46083</v>
+        <v>45964</v>
       </c>
       <c r="H133" s="5">
-        <v>46096</v>
+        <v>45992</v>
       </c>
       <c r="I133" s="5">
-        <v>46083</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
@@ -6607,19 +6784,19 @@
         <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>388</v>
+        <v>160</v>
       </c>
       <c r="C134" t="s">
-        <v>389</v>
+        <v>161</v>
       </c>
       <c r="D134" t="s">
-        <v>390</v>
+        <v>162</v>
       </c>
       <c r="E134">
-        <v>57659</v>
+        <v>57646</v>
       </c>
       <c r="F134" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="G134" s="5">
         <v>45964</v>
@@ -6628,7 +6805,7 @@
         <v>45992</v>
       </c>
       <c r="I134" s="5">
-        <v>46078</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
@@ -6636,28 +6813,28 @@
         <v>17</v>
       </c>
       <c r="B135" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C135" t="s">
-        <v>449</v>
+        <v>163</v>
       </c>
       <c r="D135" t="s">
-        <v>450</v>
+        <v>164</v>
       </c>
       <c r="E135">
-        <v>55922</v>
+        <v>57647</v>
       </c>
       <c r="F135" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G135" s="5">
-        <v>46083</v>
+        <v>45964</v>
       </c>
       <c r="H135" s="5">
-        <v>46096</v>
+        <v>45992</v>
       </c>
       <c r="I135" s="5">
-        <v>46083</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
@@ -6665,25 +6842,25 @@
         <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C136" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D136" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E136">
-        <v>57238</v>
+        <v>57648</v>
       </c>
       <c r="F136" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="G136" s="5">
-        <v>45817</v>
+        <v>45964</v>
       </c>
       <c r="H136" s="5">
-        <v>45839</v>
+        <v>45992</v>
       </c>
       <c r="I136" s="5">
         <v>46048</v>
@@ -6694,28 +6871,28 @@
         <v>17</v>
       </c>
       <c r="B137" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C137" t="s">
-        <v>175</v>
+        <v>324</v>
       </c>
       <c r="D137" t="s">
-        <v>176</v>
+        <v>325</v>
       </c>
       <c r="E137">
-        <v>57238</v>
+        <v>56446</v>
       </c>
       <c r="F137" t="s">
-        <v>177</v>
+        <v>107</v>
       </c>
       <c r="G137" s="5">
-        <v>45951</v>
+        <v>46038</v>
       </c>
       <c r="H137" s="5">
-        <v>45976</v>
+        <v>46055</v>
       </c>
       <c r="I137" s="5">
-        <v>46048</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
@@ -6723,28 +6900,28 @@
         <v>17</v>
       </c>
       <c r="B138" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C138" t="s">
-        <v>391</v>
+        <v>168</v>
       </c>
       <c r="D138" t="s">
-        <v>392</v>
+        <v>169</v>
       </c>
       <c r="E138">
-        <v>57700</v>
+        <v>57652</v>
       </c>
       <c r="F138" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="G138" s="5">
+        <v>45964</v>
+      </c>
+      <c r="H138" s="5">
         <v>45992</v>
       </c>
-      <c r="H138" s="5">
-        <v>46006</v>
-      </c>
       <c r="I138" s="5">
-        <v>46070</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -6752,28 +6929,28 @@
         <v>17</v>
       </c>
       <c r="B139" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C139" t="s">
-        <v>179</v>
+        <v>534</v>
       </c>
       <c r="D139" t="s">
-        <v>180</v>
+        <v>535</v>
       </c>
       <c r="E139">
-        <v>57583</v>
+        <v>57699</v>
       </c>
       <c r="F139" t="s">
         <v>10</v>
       </c>
       <c r="G139" s="5">
-        <v>45951</v>
+        <v>45992</v>
       </c>
       <c r="H139" s="5">
-        <v>45976</v>
+        <v>46006</v>
       </c>
       <c r="I139" s="5">
-        <v>46042</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
@@ -6781,25 +6958,25 @@
         <v>17</v>
       </c>
       <c r="B140" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C140" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="D140" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E140">
-        <v>57581</v>
+        <v>57653</v>
       </c>
       <c r="F140" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G140" s="5">
-        <v>45951</v>
+        <v>45964</v>
       </c>
       <c r="H140" s="5">
-        <v>45976</v>
+        <v>45992</v>
       </c>
       <c r="I140" s="5">
         <v>46042</v>
@@ -6810,28 +6987,28 @@
         <v>17</v>
       </c>
       <c r="B141" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C141" t="s">
-        <v>389</v>
+        <v>172</v>
       </c>
       <c r="D141" t="s">
-        <v>393</v>
+        <v>173</v>
       </c>
       <c r="E141">
-        <v>57658</v>
+        <v>57579</v>
       </c>
       <c r="F141" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G141" s="5">
-        <v>45964</v>
+        <v>45951</v>
       </c>
       <c r="H141" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I141" s="5">
-        <v>46078</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
@@ -6839,28 +7016,28 @@
         <v>17</v>
       </c>
       <c r="B142" t="s">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="C142" t="s">
-        <v>84</v>
+        <v>447</v>
       </c>
       <c r="D142" t="s">
-        <v>85</v>
+        <v>448</v>
       </c>
       <c r="E142">
-        <v>57736</v>
+        <v>56879</v>
       </c>
       <c r="F142" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G142" s="5">
-        <v>46007</v>
-      </c>
-      <c r="H142" t="s">
-        <v>65</v>
+        <v>46083</v>
+      </c>
+      <c r="H142" s="5">
+        <v>46096</v>
       </c>
       <c r="I142" s="5">
-        <v>46027</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
@@ -6868,28 +7045,28 @@
         <v>17</v>
       </c>
       <c r="B143" t="s">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="C143" t="s">
-        <v>451</v>
+        <v>389</v>
       </c>
       <c r="D143" t="s">
-        <v>452</v>
+        <v>390</v>
       </c>
       <c r="E143">
-        <v>57440</v>
+        <v>57659</v>
       </c>
       <c r="F143" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="G143" s="5">
-        <v>46083</v>
+        <v>45964</v>
       </c>
       <c r="H143" s="5">
-        <v>46096</v>
+        <v>45992</v>
       </c>
       <c r="I143" s="5">
-        <v>46083</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
@@ -6897,28 +7074,28 @@
         <v>17</v>
       </c>
       <c r="B144" t="s">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="C144" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D144" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E144">
-        <v>57829</v>
+        <v>55922</v>
       </c>
       <c r="F144" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G144" s="5">
         <v>46083</v>
       </c>
-      <c r="H144" t="s">
-        <v>65</v>
+      <c r="H144" s="5">
+        <v>46096</v>
       </c>
       <c r="I144" s="5">
-        <v>46096</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -6926,28 +7103,28 @@
         <v>17</v>
       </c>
       <c r="B145" t="s">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="C145" t="s">
-        <v>455</v>
+        <v>175</v>
       </c>
       <c r="D145" t="s">
-        <v>456</v>
+        <v>176</v>
       </c>
       <c r="E145">
-        <v>57830</v>
+        <v>57238</v>
       </c>
       <c r="F145" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="G145" s="5">
-        <v>46083</v>
-      </c>
-      <c r="H145" t="s">
-        <v>65</v>
+        <v>45817</v>
+      </c>
+      <c r="H145" s="5">
+        <v>45839</v>
       </c>
       <c r="I145" s="5">
-        <v>46096</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
@@ -6955,28 +7132,28 @@
         <v>17</v>
       </c>
       <c r="B146" t="s">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="C146" t="s">
-        <v>457</v>
+        <v>175</v>
       </c>
       <c r="D146" t="s">
-        <v>458</v>
+        <v>176</v>
       </c>
       <c r="E146">
-        <v>55583</v>
+        <v>57238</v>
       </c>
       <c r="F146" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="G146" s="5">
-        <v>46083</v>
+        <v>45951</v>
       </c>
       <c r="H146" s="5">
-        <v>46096</v>
+        <v>45976</v>
       </c>
       <c r="I146" s="5">
-        <v>46083</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
@@ -6984,28 +7161,28 @@
         <v>17</v>
       </c>
       <c r="B147" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C147" t="s">
-        <v>184</v>
+        <v>391</v>
       </c>
       <c r="D147" t="s">
-        <v>185</v>
+        <v>392</v>
       </c>
       <c r="E147">
-        <v>57642</v>
+        <v>57700</v>
       </c>
       <c r="F147" t="s">
         <v>141</v>
       </c>
       <c r="G147" s="5">
-        <v>45963</v>
+        <v>45992</v>
       </c>
       <c r="H147" s="5">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="I147" s="5">
-        <v>46048</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
@@ -7013,28 +7190,28 @@
         <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C148" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D148" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E148">
-        <v>57655</v>
+        <v>57583</v>
       </c>
       <c r="F148" t="s">
         <v>10</v>
       </c>
       <c r="G148" s="5">
-        <v>45964</v>
+        <v>45951</v>
       </c>
       <c r="H148" s="5">
-        <v>45992</v>
+        <v>45976</v>
       </c>
       <c r="I148" s="5">
-        <v>46048</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
@@ -7042,28 +7219,28 @@
         <v>17</v>
       </c>
       <c r="B149" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C149" t="s">
-        <v>394</v>
+        <v>181</v>
       </c>
       <c r="D149" t="s">
-        <v>395</v>
+        <v>182</v>
       </c>
       <c r="E149">
-        <v>57698</v>
+        <v>57581</v>
       </c>
       <c r="F149" t="s">
         <v>10</v>
       </c>
       <c r="G149" s="5">
-        <v>45992</v>
+        <v>45951</v>
       </c>
       <c r="H149" s="5">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c r="I149" s="5">
-        <v>46070</v>
+        <v>46042</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
@@ -7071,28 +7248,28 @@
         <v>17</v>
       </c>
       <c r="B150" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C150" t="s">
-        <v>188</v>
+        <v>389</v>
       </c>
       <c r="D150" t="s">
-        <v>189</v>
+        <v>393</v>
       </c>
       <c r="E150">
-        <v>57582</v>
+        <v>57658</v>
       </c>
       <c r="F150" t="s">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="G150" s="5">
-        <v>45951</v>
+        <v>45964</v>
       </c>
       <c r="H150" s="5">
-        <v>45976</v>
+        <v>45992</v>
       </c>
       <c r="I150" s="5">
-        <v>46048</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
@@ -7100,28 +7277,28 @@
         <v>17</v>
       </c>
       <c r="B151" t="s">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="C151" t="s">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="D151" t="s">
-        <v>191</v>
+        <v>85</v>
       </c>
       <c r="E151">
-        <v>57654</v>
+        <v>57736</v>
       </c>
       <c r="F151" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G151" s="5">
-        <v>45964</v>
-      </c>
-      <c r="H151" s="5">
-        <v>45992</v>
+        <v>46007</v>
+      </c>
+      <c r="H151" t="s">
+        <v>65</v>
       </c>
       <c r="I151" s="5">
-        <v>46048</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
@@ -7129,28 +7306,28 @@
         <v>17</v>
       </c>
       <c r="B152" t="s">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="C152" t="s">
-        <v>326</v>
+        <v>451</v>
       </c>
       <c r="D152" t="s">
-        <v>327</v>
+        <v>452</v>
       </c>
       <c r="E152">
-        <v>57779</v>
+        <v>57440</v>
       </c>
       <c r="F152" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G152" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H152" t="s">
-        <v>65</v>
+        <v>46083</v>
+      </c>
+      <c r="H152" s="5">
+        <v>46096</v>
       </c>
       <c r="I152" s="5">
-        <v>46055</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -7158,51 +7335,51 @@
         <v>17</v>
       </c>
       <c r="B153" t="s">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="C153" t="s">
-        <v>397</v>
+        <v>453</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>454</v>
       </c>
       <c r="E153">
-        <v>56119</v>
+        <v>57829</v>
       </c>
       <c r="F153" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G153" s="5">
-        <v>46070</v>
-      </c>
-      <c r="H153" s="5">
-        <v>46072</v>
+        <v>46083</v>
+      </c>
+      <c r="H153" t="s">
+        <v>65</v>
       </c>
       <c r="I153" s="5">
-        <v>46070</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B154" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C154" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D154" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E154">
-        <v>57840</v>
+        <v>57830</v>
       </c>
       <c r="F154" t="s">
         <v>64</v>
       </c>
       <c r="G154" s="5">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="H154" t="s">
         <v>65</v>
@@ -7213,263 +7390,263 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B155" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C155" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D155" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E155">
-        <v>57841</v>
+        <v>55583</v>
       </c>
       <c r="F155" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G155" s="5">
-        <v>46086</v>
-      </c>
-      <c r="H155" t="s">
-        <v>65</v>
+        <v>46083</v>
+      </c>
+      <c r="H155" s="5">
+        <v>46096</v>
       </c>
       <c r="I155" s="5">
-        <v>46096</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B156" t="s">
-        <v>35</v>
+        <v>564</v>
       </c>
       <c r="C156" t="s">
-        <v>192</v>
+        <v>565</v>
       </c>
       <c r="D156" t="s">
-        <v>193</v>
+        <v>566</v>
       </c>
       <c r="E156">
-        <v>57407</v>
+        <v>57544</v>
       </c>
       <c r="F156" t="s">
         <v>107</v>
       </c>
       <c r="G156" s="5">
-        <v>46029</v>
+        <v>46106</v>
       </c>
       <c r="H156" s="5">
-        <v>46047</v>
+        <v>46119</v>
       </c>
       <c r="I156" s="5">
-        <v>46029</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B157" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="C157" t="s">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="D157" t="s">
-        <v>88</v>
+        <v>185</v>
       </c>
       <c r="E157">
-        <v>57682</v>
+        <v>57642</v>
       </c>
       <c r="F157" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="G157" s="5">
-        <v>45975</v>
+        <v>45963</v>
       </c>
       <c r="H157" s="5">
         <v>45992</v>
       </c>
       <c r="I157" s="5">
-        <v>46036</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B158" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="C158" t="s">
-        <v>463</v>
+        <v>186</v>
       </c>
       <c r="D158" t="s">
-        <v>464</v>
+        <v>187</v>
       </c>
       <c r="E158">
-        <v>57842</v>
+        <v>57655</v>
       </c>
       <c r="F158" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G158" s="5">
-        <v>46087</v>
-      </c>
-      <c r="H158" t="s">
-        <v>65</v>
+        <v>45964</v>
+      </c>
+      <c r="H158" s="5">
+        <v>45992</v>
       </c>
       <c r="I158" s="5">
-        <v>46096</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B159" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="C159" t="s">
-        <v>465</v>
+        <v>394</v>
       </c>
       <c r="D159" t="s">
-        <v>466</v>
+        <v>395</v>
       </c>
       <c r="E159">
-        <v>57845</v>
+        <v>57698</v>
       </c>
       <c r="F159" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G159" s="5">
-        <v>46087</v>
-      </c>
-      <c r="H159" t="s">
-        <v>65</v>
+        <v>45992</v>
+      </c>
+      <c r="H159" s="5">
+        <v>46006</v>
       </c>
       <c r="I159" s="5">
-        <v>46096</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B160" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>467</v>
+        <v>188</v>
       </c>
       <c r="D160" t="s">
-        <v>468</v>
+        <v>189</v>
       </c>
       <c r="E160">
-        <v>57524</v>
+        <v>57582</v>
       </c>
       <c r="F160" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="G160" s="5">
-        <v>46086</v>
+        <v>45951</v>
       </c>
       <c r="H160" s="5">
-        <v>46096</v>
+        <v>45976</v>
       </c>
       <c r="I160" s="5">
-        <v>46086</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B161" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="C161" t="s">
-        <v>467</v>
+        <v>190</v>
       </c>
       <c r="D161" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="E161">
-        <v>57847</v>
+        <v>57654</v>
       </c>
       <c r="F161" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G161" s="5">
-        <v>46087</v>
-      </c>
-      <c r="H161" t="s">
-        <v>65</v>
+        <v>45964</v>
+      </c>
+      <c r="H161" s="5">
+        <v>45992</v>
       </c>
       <c r="I161" s="5">
-        <v>46096</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B162" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="C162" t="s">
-        <v>469</v>
+        <v>326</v>
       </c>
       <c r="D162" t="s">
-        <v>470</v>
+        <v>327</v>
       </c>
       <c r="E162">
-        <v>57843</v>
+        <v>57779</v>
       </c>
       <c r="F162" t="s">
         <v>64</v>
       </c>
       <c r="G162" s="5">
-        <v>46087</v>
+        <v>46049</v>
       </c>
       <c r="H162" t="s">
         <v>65</v>
       </c>
       <c r="I162" s="5">
-        <v>46096</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="B163" t="s">
-        <v>35</v>
+        <v>396</v>
       </c>
       <c r="C163" t="s">
-        <v>194</v>
+        <v>397</v>
       </c>
       <c r="D163" t="s">
-        <v>195</v>
+        <v>398</v>
       </c>
       <c r="E163">
-        <v>57406</v>
+        <v>56119</v>
       </c>
       <c r="F163" t="s">
         <v>107</v>
       </c>
       <c r="G163" s="5">
-        <v>46029</v>
+        <v>46070</v>
       </c>
       <c r="H163" s="5">
-        <v>46047</v>
+        <v>46072</v>
       </c>
       <c r="I163" s="5">
-        <v>46029</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
@@ -7480,25 +7657,25 @@
         <v>35</v>
       </c>
       <c r="C164" t="s">
-        <v>194</v>
+        <v>567</v>
       </c>
       <c r="D164" t="s">
-        <v>195</v>
+        <v>568</v>
       </c>
       <c r="E164">
-        <v>57784</v>
+        <v>57865</v>
       </c>
       <c r="F164" t="s">
         <v>64</v>
       </c>
       <c r="G164" s="5">
-        <v>46050</v>
+        <v>46101</v>
       </c>
       <c r="H164" t="s">
         <v>65</v>
       </c>
       <c r="I164" s="5">
-        <v>46055</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
@@ -7509,25 +7686,25 @@
         <v>35</v>
       </c>
       <c r="C165" t="s">
-        <v>536</v>
+        <v>569</v>
       </c>
       <c r="D165" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="E165">
-        <v>57861</v>
+        <v>57866</v>
       </c>
       <c r="F165" t="s">
         <v>64</v>
       </c>
       <c r="G165" s="5">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="H165" t="s">
         <v>65</v>
       </c>
       <c r="I165" s="5">
-        <v>46104</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
@@ -7538,25 +7715,25 @@
         <v>35</v>
       </c>
       <c r="C166" t="s">
-        <v>538</v>
+        <v>459</v>
       </c>
       <c r="D166" t="s">
-        <v>539</v>
+        <v>460</v>
       </c>
       <c r="E166">
-        <v>57862</v>
+        <v>57840</v>
       </c>
       <c r="F166" t="s">
         <v>64</v>
       </c>
       <c r="G166" s="5">
-        <v>46097</v>
+        <v>46086</v>
       </c>
       <c r="H166" t="s">
         <v>65</v>
       </c>
       <c r="I166" s="5">
-        <v>46104</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
@@ -7567,19 +7744,19 @@
         <v>35</v>
       </c>
       <c r="C167" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="D167" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="E167">
-        <v>57844</v>
+        <v>57841</v>
       </c>
       <c r="F167" t="s">
         <v>64</v>
       </c>
       <c r="G167" s="5">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="H167" t="s">
         <v>65</v>
@@ -7596,25 +7773,25 @@
         <v>35</v>
       </c>
       <c r="C168" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="D168" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="E168">
-        <v>57683</v>
+        <v>57407</v>
       </c>
       <c r="F168" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G168" s="5">
-        <v>45975</v>
+        <v>46029</v>
       </c>
       <c r="H168" s="5">
-        <v>45992</v>
+        <v>46047</v>
       </c>
       <c r="I168" s="5">
-        <v>46036</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
@@ -7625,25 +7802,25 @@
         <v>35</v>
       </c>
       <c r="C169" t="s">
-        <v>473</v>
+        <v>87</v>
       </c>
       <c r="D169" t="s">
-        <v>474</v>
+        <v>88</v>
       </c>
       <c r="E169">
-        <v>57846</v>
+        <v>57682</v>
       </c>
       <c r="F169" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="G169" s="5">
-        <v>46087</v>
-      </c>
-      <c r="H169" t="s">
-        <v>65</v>
+        <v>45975</v>
+      </c>
+      <c r="H169" s="5">
+        <v>45992</v>
       </c>
       <c r="I169" s="5">
-        <v>46096</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -7654,25 +7831,25 @@
         <v>35</v>
       </c>
       <c r="C170" t="s">
-        <v>91</v>
+        <v>463</v>
       </c>
       <c r="D170" t="s">
-        <v>92</v>
+        <v>464</v>
       </c>
       <c r="E170">
-        <v>57681</v>
+        <v>57842</v>
       </c>
       <c r="F170" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G170" s="5">
-        <v>45975</v>
-      </c>
-      <c r="H170" s="5">
-        <v>45992</v>
+        <v>46087</v>
+      </c>
+      <c r="H170" t="s">
+        <v>65</v>
       </c>
       <c r="I170" s="5">
-        <v>46036</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -7680,28 +7857,28 @@
         <v>86</v>
       </c>
       <c r="B171" t="s">
-        <v>328</v>
+        <v>35</v>
       </c>
       <c r="C171" t="s">
-        <v>329</v>
+        <v>465</v>
       </c>
       <c r="D171" t="s">
-        <v>330</v>
+        <v>466</v>
       </c>
       <c r="E171">
-        <v>57772</v>
+        <v>57845</v>
       </c>
       <c r="F171" t="s">
         <v>64</v>
       </c>
       <c r="G171" s="5">
-        <v>46049</v>
+        <v>46087</v>
       </c>
       <c r="H171" t="s">
         <v>65</v>
       </c>
       <c r="I171" s="5">
-        <v>46055</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
@@ -7709,28 +7886,28 @@
         <v>86</v>
       </c>
       <c r="B172" t="s">
-        <v>328</v>
+        <v>35</v>
       </c>
       <c r="C172" t="s">
-        <v>331</v>
+        <v>467</v>
       </c>
       <c r="D172" t="s">
-        <v>332</v>
+        <v>468</v>
       </c>
       <c r="E172">
-        <v>57773</v>
+        <v>57524</v>
       </c>
       <c r="F172" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G172" s="5">
-        <v>46049</v>
-      </c>
-      <c r="H172" t="s">
-        <v>65</v>
+        <v>46086</v>
+      </c>
+      <c r="H172" s="5">
+        <v>46096</v>
       </c>
       <c r="I172" s="5">
-        <v>46055</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
@@ -7738,567 +7915,567 @@
         <v>86</v>
       </c>
       <c r="B173" t="s">
-        <v>328</v>
+        <v>35</v>
       </c>
       <c r="C173" t="s">
-        <v>333</v>
+        <v>467</v>
       </c>
       <c r="D173" t="s">
-        <v>334</v>
+        <v>468</v>
       </c>
       <c r="E173">
-        <v>57774</v>
+        <v>57847</v>
       </c>
       <c r="F173" t="s">
         <v>64</v>
       </c>
       <c r="G173" s="5">
-        <v>46049</v>
+        <v>46087</v>
       </c>
       <c r="H173" t="s">
         <v>65</v>
       </c>
       <c r="I173" s="5">
-        <v>46055</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B174" t="s">
         <v>35</v>
       </c>
       <c r="C174" t="s">
-        <v>335</v>
+        <v>469</v>
       </c>
       <c r="D174" t="s">
-        <v>336</v>
+        <v>470</v>
       </c>
       <c r="E174">
-        <v>53987</v>
+        <v>57843</v>
       </c>
       <c r="F174" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G174" s="5">
-        <v>46059</v>
-      </c>
-      <c r="H174" s="5">
-        <v>46062</v>
+        <v>46087</v>
+      </c>
+      <c r="H174" t="s">
+        <v>65</v>
       </c>
       <c r="I174" s="5">
-        <v>46059</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B175" t="s">
         <v>35</v>
       </c>
       <c r="C175" t="s">
-        <v>337</v>
+        <v>194</v>
       </c>
       <c r="D175" t="s">
-        <v>338</v>
+        <v>195</v>
       </c>
       <c r="E175">
-        <v>55109</v>
+        <v>57406</v>
       </c>
       <c r="F175" t="s">
         <v>107</v>
       </c>
       <c r="G175" s="5">
-        <v>46059</v>
+        <v>46029</v>
       </c>
       <c r="H175" s="5">
-        <v>46062</v>
+        <v>46047</v>
       </c>
       <c r="I175" s="5">
-        <v>46059</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B176" t="s">
         <v>35</v>
       </c>
       <c r="C176" t="s">
-        <v>339</v>
+        <v>194</v>
       </c>
       <c r="D176" t="s">
-        <v>340</v>
+        <v>195</v>
       </c>
       <c r="E176">
-        <v>56415</v>
+        <v>57784</v>
       </c>
       <c r="F176" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G176" s="5">
-        <v>46059</v>
-      </c>
-      <c r="H176" s="5">
-        <v>46062</v>
+        <v>46050</v>
+      </c>
+      <c r="H176" t="s">
+        <v>65</v>
       </c>
       <c r="I176" s="5">
-        <v>46059</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B177" t="s">
         <v>35</v>
       </c>
       <c r="C177" t="s">
-        <v>341</v>
+        <v>571</v>
       </c>
       <c r="D177" t="s">
-        <v>342</v>
+        <v>572</v>
       </c>
       <c r="E177">
-        <v>57704</v>
+        <v>54117</v>
       </c>
       <c r="F177" t="s">
-        <v>10</v>
+        <v>357</v>
       </c>
       <c r="G177" s="5">
-        <v>45995</v>
-      </c>
-      <c r="H177" s="5">
-        <v>46023</v>
+        <v>46126</v>
+      </c>
+      <c r="H177" t="s">
+        <v>358</v>
       </c>
       <c r="I177" s="5">
-        <v>46062</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B178" t="s">
         <v>35</v>
       </c>
       <c r="C178" t="s">
-        <v>196</v>
+        <v>536</v>
       </c>
       <c r="D178" t="s">
-        <v>197</v>
+        <v>537</v>
       </c>
       <c r="E178">
-        <v>55810</v>
+        <v>57861</v>
       </c>
       <c r="F178" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G178" s="5">
-        <v>46029</v>
-      </c>
-      <c r="H178" s="5">
-        <v>46047</v>
+        <v>46097</v>
+      </c>
+      <c r="H178" t="s">
+        <v>65</v>
       </c>
       <c r="I178" s="5">
-        <v>46029</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B179" t="s">
         <v>35</v>
       </c>
       <c r="C179" t="s">
-        <v>36</v>
+        <v>538</v>
       </c>
       <c r="D179" t="s">
-        <v>37</v>
+        <v>539</v>
       </c>
       <c r="E179">
-        <v>57626</v>
+        <v>57862</v>
       </c>
       <c r="F179" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G179" s="5">
-        <v>45958</v>
-      </c>
-      <c r="H179" s="5">
-        <v>45976</v>
+        <v>46097</v>
+      </c>
+      <c r="H179" t="s">
+        <v>65</v>
       </c>
       <c r="I179" s="5">
-        <v>46023</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B180" t="s">
         <v>35</v>
       </c>
       <c r="C180" t="s">
-        <v>343</v>
+        <v>471</v>
       </c>
       <c r="D180" t="s">
-        <v>344</v>
+        <v>472</v>
       </c>
       <c r="E180">
-        <v>56750</v>
+        <v>57844</v>
       </c>
       <c r="F180" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G180" s="5">
-        <v>46059</v>
-      </c>
-      <c r="H180" s="5">
-        <v>46062</v>
+        <v>46087</v>
+      </c>
+      <c r="H180" t="s">
+        <v>65</v>
       </c>
       <c r="I180" s="5">
-        <v>46059</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B181" t="s">
         <v>35</v>
       </c>
       <c r="C181" t="s">
-        <v>475</v>
+        <v>89</v>
       </c>
       <c r="D181" t="s">
-        <v>476</v>
+        <v>90</v>
       </c>
       <c r="E181">
-        <v>57006</v>
+        <v>57683</v>
       </c>
       <c r="F181" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G181" s="5">
-        <v>46090</v>
+        <v>45975</v>
       </c>
       <c r="H181" s="5">
-        <v>46096</v>
+        <v>45992</v>
       </c>
       <c r="I181" s="5">
-        <v>46090</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B182" t="s">
         <v>35</v>
       </c>
       <c r="C182" t="s">
-        <v>399</v>
+        <v>473</v>
       </c>
       <c r="D182" t="s">
-        <v>400</v>
+        <v>474</v>
       </c>
       <c r="E182">
-        <v>57607</v>
+        <v>57846</v>
       </c>
       <c r="F182" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="G182" s="5">
-        <v>45952</v>
-      </c>
-      <c r="H182" s="5">
-        <v>45976</v>
+        <v>46087</v>
+      </c>
+      <c r="H182" t="s">
+        <v>65</v>
       </c>
       <c r="I182" s="5">
-        <v>46071</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B183" t="s">
         <v>35</v>
       </c>
       <c r="C183" t="s">
-        <v>399</v>
+        <v>91</v>
       </c>
       <c r="D183" t="s">
-        <v>400</v>
+        <v>92</v>
       </c>
       <c r="E183">
-        <v>57607</v>
+        <v>57681</v>
       </c>
       <c r="F183" t="s">
-        <v>401</v>
+        <v>10</v>
       </c>
       <c r="G183" s="5">
-        <v>46009</v>
+        <v>45975</v>
       </c>
       <c r="H183" s="5">
-        <v>46037</v>
+        <v>45992</v>
       </c>
       <c r="I183" s="5">
-        <v>46071</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B184" t="s">
-        <v>93</v>
+        <v>328</v>
       </c>
       <c r="C184" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="D184" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="E184">
-        <v>54040</v>
+        <v>57772</v>
       </c>
       <c r="F184" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G184" s="5">
-        <v>46062</v>
-      </c>
-      <c r="H184" s="5">
-        <v>46066</v>
+        <v>46049</v>
+      </c>
+      <c r="H184" t="s">
+        <v>65</v>
       </c>
       <c r="I184" s="5">
-        <v>46062</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B185" t="s">
-        <v>93</v>
+        <v>328</v>
       </c>
       <c r="C185" t="s">
-        <v>94</v>
+        <v>331</v>
       </c>
       <c r="D185" t="s">
-        <v>95</v>
+        <v>332</v>
       </c>
       <c r="E185">
-        <v>57685</v>
+        <v>57773</v>
       </c>
       <c r="F185" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G185" s="5">
-        <v>45975</v>
-      </c>
-      <c r="H185" s="5">
-        <v>45992</v>
+        <v>46049</v>
+      </c>
+      <c r="H185" t="s">
+        <v>65</v>
       </c>
       <c r="I185" s="5">
-        <v>46029</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="B186" t="s">
-        <v>198</v>
+        <v>328</v>
       </c>
       <c r="C186" t="s">
-        <v>199</v>
+        <v>333</v>
       </c>
       <c r="D186" t="s">
-        <v>200</v>
+        <v>334</v>
       </c>
       <c r="E186">
-        <v>51497</v>
+        <v>57774</v>
       </c>
       <c r="F186" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G186" s="5">
-        <v>46030</v>
-      </c>
-      <c r="H186" s="5">
-        <v>46047</v>
+        <v>46049</v>
+      </c>
+      <c r="H186" t="s">
+        <v>65</v>
       </c>
       <c r="I186" s="5">
-        <v>46030</v>
+        <v>46055</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B187" t="s">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="C187" t="s">
-        <v>202</v>
+        <v>335</v>
       </c>
       <c r="D187" t="s">
-        <v>203</v>
+        <v>336</v>
       </c>
       <c r="E187">
-        <v>51493</v>
+        <v>53987</v>
       </c>
       <c r="F187" t="s">
         <v>107</v>
       </c>
       <c r="G187" s="5">
-        <v>46030</v>
+        <v>46059</v>
       </c>
       <c r="H187" s="5">
-        <v>46047</v>
+        <v>46062</v>
       </c>
       <c r="I187" s="5">
-        <v>46030</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B188" t="s">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="C188" t="s">
-        <v>204</v>
+        <v>337</v>
       </c>
       <c r="D188" t="s">
-        <v>205</v>
+        <v>338</v>
       </c>
       <c r="E188">
-        <v>51495</v>
+        <v>55109</v>
       </c>
       <c r="F188" t="s">
         <v>107</v>
       </c>
       <c r="G188" s="5">
-        <v>46030</v>
+        <v>46059</v>
       </c>
       <c r="H188" s="5">
-        <v>46047</v>
+        <v>46062</v>
       </c>
       <c r="I188" s="5">
-        <v>46030</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B189" t="s">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="C189" t="s">
-        <v>206</v>
+        <v>339</v>
       </c>
       <c r="D189" t="s">
-        <v>207</v>
+        <v>340</v>
       </c>
       <c r="E189">
-        <v>51496</v>
+        <v>56415</v>
       </c>
       <c r="F189" t="s">
         <v>107</v>
       </c>
       <c r="G189" s="5">
-        <v>46030</v>
+        <v>46059</v>
       </c>
       <c r="H189" s="5">
-        <v>46047</v>
+        <v>46062</v>
       </c>
       <c r="I189" s="5">
-        <v>46030</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B190" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C190" t="s">
-        <v>40</v>
+        <v>341</v>
       </c>
       <c r="D190" t="s">
-        <v>41</v>
+        <v>342</v>
       </c>
       <c r="E190">
-        <v>57619</v>
+        <v>57704</v>
       </c>
       <c r="F190" t="s">
         <v>10</v>
       </c>
       <c r="G190" s="5">
-        <v>45957</v>
+        <v>45995</v>
       </c>
       <c r="H190" s="5">
-        <v>45976</v>
+        <v>46023</v>
       </c>
       <c r="I190" s="5">
-        <v>46023</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B191" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C191" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
       <c r="D191" t="s">
-        <v>41</v>
+        <v>197</v>
       </c>
       <c r="E191">
-        <v>57620</v>
+        <v>55810</v>
       </c>
       <c r="F191" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G191" s="5">
-        <v>45957</v>
+        <v>46029</v>
       </c>
       <c r="H191" s="5">
-        <v>45976</v>
+        <v>46047</v>
       </c>
       <c r="I191" s="5">
-        <v>46023</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B192" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C192" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D192" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E192">
-        <v>57625</v>
+        <v>57626</v>
       </c>
       <c r="F192" t="s">
         <v>10</v>
@@ -8315,193 +8492,193 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B193" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C193" t="s">
-        <v>40</v>
+        <v>343</v>
       </c>
       <c r="D193" t="s">
-        <v>41</v>
+        <v>344</v>
       </c>
       <c r="E193">
-        <v>57637</v>
+        <v>56750</v>
       </c>
       <c r="F193" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G193" s="5">
-        <v>45961</v>
+        <v>46059</v>
       </c>
       <c r="H193" s="5">
-        <v>45976</v>
+        <v>46062</v>
       </c>
       <c r="I193" s="5">
-        <v>46023</v>
+        <v>46059</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B194" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C194" t="s">
-        <v>42</v>
+        <v>475</v>
       </c>
       <c r="D194" t="s">
-        <v>43</v>
+        <v>476</v>
       </c>
       <c r="E194">
-        <v>57621</v>
+        <v>57006</v>
       </c>
       <c r="F194" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G194" s="5">
-        <v>45957</v>
+        <v>46090</v>
       </c>
       <c r="H194" s="5">
-        <v>45976</v>
+        <v>46096</v>
       </c>
       <c r="I194" s="5">
-        <v>46023</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>208</v>
+        <v>34</v>
       </c>
       <c r="B195" t="s">
-        <v>209</v>
+        <v>35</v>
       </c>
       <c r="C195" t="s">
-        <v>210</v>
+        <v>399</v>
       </c>
       <c r="D195" t="s">
-        <v>211</v>
+        <v>400</v>
       </c>
       <c r="E195">
-        <v>57701</v>
+        <v>57607</v>
       </c>
       <c r="F195" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G195" s="5">
-        <v>45992</v>
+        <v>45952</v>
       </c>
       <c r="H195" s="5">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c r="I195" s="5">
-        <v>46043</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>347</v>
+        <v>34</v>
       </c>
       <c r="B196" t="s">
         <v>35</v>
       </c>
       <c r="C196" t="s">
-        <v>348</v>
+        <v>399</v>
       </c>
       <c r="D196" t="s">
-        <v>349</v>
+        <v>400</v>
       </c>
       <c r="E196">
-        <v>57490</v>
+        <v>57607</v>
       </c>
       <c r="F196" t="s">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="G196" s="5">
-        <v>46048</v>
+        <v>46009</v>
       </c>
       <c r="H196" s="5">
-        <v>46055</v>
+        <v>46037</v>
       </c>
       <c r="I196" s="5">
-        <v>46048</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>347</v>
+        <v>34</v>
       </c>
       <c r="B197" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="C197" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D197" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E197">
-        <v>51528</v>
+        <v>54040</v>
       </c>
       <c r="F197" t="s">
         <v>107</v>
       </c>
       <c r="G197" s="5">
-        <v>46048</v>
+        <v>46062</v>
       </c>
       <c r="H197" s="5">
-        <v>46055</v>
+        <v>46066</v>
       </c>
       <c r="I197" s="5">
-        <v>46048</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>347</v>
+        <v>34</v>
       </c>
       <c r="B198" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="C198" t="s">
-        <v>352</v>
+        <v>94</v>
       </c>
       <c r="D198" t="s">
-        <v>353</v>
+        <v>95</v>
       </c>
       <c r="E198">
-        <v>51522</v>
+        <v>57685</v>
       </c>
       <c r="F198" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G198" s="5">
-        <v>46048</v>
+        <v>45975</v>
       </c>
       <c r="H198" s="5">
-        <v>46055</v>
+        <v>45992</v>
       </c>
       <c r="I198" s="5">
-        <v>46048</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B199" t="s">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="C199" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="D199" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="E199">
-        <v>56438</v>
+        <v>51497</v>
       </c>
       <c r="F199" t="s">
         <v>107</v>
@@ -8518,350 +8695,350 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B200" t="s">
-        <v>96</v>
+        <v>201</v>
       </c>
       <c r="C200" t="s">
-        <v>402</v>
+        <v>202</v>
       </c>
       <c r="D200" t="s">
-        <v>403</v>
+        <v>203</v>
       </c>
       <c r="E200">
-        <v>57743</v>
+        <v>51493</v>
       </c>
       <c r="F200" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G200" s="5">
-        <v>46013</v>
+        <v>46030</v>
       </c>
       <c r="H200" s="5">
-        <v>46037</v>
+        <v>46047</v>
       </c>
       <c r="I200" s="5">
-        <v>46077</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B201" t="s">
-        <v>96</v>
+        <v>201</v>
       </c>
       <c r="C201" t="s">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="D201" t="s">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c r="E201">
-        <v>57671</v>
+        <v>51495</v>
       </c>
       <c r="F201" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G201" s="5">
-        <v>45974</v>
+        <v>46030</v>
       </c>
       <c r="H201" s="5">
-        <v>45992</v>
+        <v>46047</v>
       </c>
       <c r="I201" s="5">
-        <v>46029</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B202" t="s">
-        <v>96</v>
+        <v>201</v>
       </c>
       <c r="C202" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D202" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E202">
-        <v>51696</v>
+        <v>51496</v>
       </c>
       <c r="F202" t="s">
         <v>107</v>
       </c>
       <c r="G202" s="5">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H202" s="5">
         <v>46047</v>
       </c>
       <c r="I202" s="5">
-        <v>46029</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B203" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="C203" t="s">
-        <v>216</v>
+        <v>40</v>
       </c>
       <c r="D203" t="s">
-        <v>217</v>
+        <v>41</v>
       </c>
       <c r="E203">
-        <v>51693</v>
+        <v>57619</v>
       </c>
       <c r="F203" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G203" s="5">
-        <v>46029</v>
+        <v>45957</v>
       </c>
       <c r="H203" s="5">
-        <v>46047</v>
+        <v>45976</v>
       </c>
       <c r="I203" s="5">
-        <v>46029</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B204" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="C204" t="s">
-        <v>218</v>
+        <v>40</v>
       </c>
       <c r="D204" t="s">
-        <v>219</v>
+        <v>41</v>
       </c>
       <c r="E204">
-        <v>51697</v>
+        <v>57620</v>
       </c>
       <c r="F204" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G204" s="5">
-        <v>46029</v>
+        <v>45957</v>
       </c>
       <c r="H204" s="5">
-        <v>46047</v>
+        <v>45976</v>
       </c>
       <c r="I204" s="5">
-        <v>46029</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B205" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="C205" t="s">
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="D205" t="s">
-        <v>221</v>
+        <v>41</v>
       </c>
       <c r="E205">
-        <v>51687</v>
+        <v>57625</v>
       </c>
       <c r="F205" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G205" s="5">
-        <v>46030</v>
+        <v>45958</v>
       </c>
       <c r="H205" s="5">
-        <v>46047</v>
+        <v>45976</v>
       </c>
       <c r="I205" s="5">
-        <v>46030</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B206" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="C206" t="s">
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="D206" t="s">
-        <v>221</v>
+        <v>41</v>
       </c>
       <c r="E206">
-        <v>57756</v>
+        <v>57637</v>
       </c>
       <c r="F206" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G206" s="5">
-        <v>46029</v>
-      </c>
-      <c r="H206" t="s">
-        <v>65</v>
+        <v>45961</v>
+      </c>
+      <c r="H206" s="5">
+        <v>45976</v>
       </c>
       <c r="I206" s="5">
-        <v>46047</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B207" t="s">
-        <v>354</v>
+        <v>39</v>
       </c>
       <c r="C207" t="s">
-        <v>355</v>
+        <v>42</v>
       </c>
       <c r="D207" t="s">
-        <v>356</v>
+        <v>43</v>
       </c>
       <c r="E207">
-        <v>53634</v>
+        <v>57621</v>
       </c>
       <c r="F207" t="s">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="G207" s="5">
-        <v>46063</v>
-      </c>
-      <c r="H207" t="s">
-        <v>358</v>
+        <v>45957</v>
+      </c>
+      <c r="H207" s="5">
+        <v>45976</v>
       </c>
       <c r="I207" s="5">
-        <v>46063</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>20</v>
+        <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C208" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D208" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="E208">
-        <v>53224</v>
+        <v>57701</v>
       </c>
       <c r="F208" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G208" s="5">
-        <v>46031</v>
+        <v>45992</v>
       </c>
       <c r="H208" s="5">
-        <v>46047</v>
+        <v>46006</v>
       </c>
       <c r="I208" s="5">
-        <v>46031</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="B209" t="s">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c r="C209" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="D209" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="E209">
-        <v>57708</v>
+        <v>57490</v>
       </c>
       <c r="F209" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G209" s="5">
-        <v>46001</v>
+        <v>46048</v>
       </c>
       <c r="H209" s="5">
-        <v>46023</v>
+        <v>46055</v>
       </c>
       <c r="I209" s="5">
-        <v>46063</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="B210" t="s">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c r="C210" t="s">
-        <v>226</v>
+        <v>350</v>
       </c>
       <c r="D210" t="s">
-        <v>227</v>
+        <v>351</v>
       </c>
       <c r="E210">
-        <v>55787</v>
+        <v>51528</v>
       </c>
       <c r="F210" t="s">
         <v>107</v>
       </c>
       <c r="G210" s="5">
-        <v>46027</v>
+        <v>46048</v>
       </c>
       <c r="H210" s="5">
-        <v>46047</v>
+        <v>46055</v>
       </c>
       <c r="I210" s="5">
-        <v>46027</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="B211" t="s">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c r="C211" t="s">
-        <v>477</v>
+        <v>352</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>353</v>
       </c>
       <c r="E211">
-        <v>57766</v>
+        <v>51522</v>
       </c>
       <c r="F211" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G211" s="5">
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="H211" s="5">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="I211" s="5">
-        <v>46092</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -8869,1130 +9046,2000 @@
         <v>20</v>
       </c>
       <c r="B212" t="s">
-        <v>225</v>
+        <v>96</v>
       </c>
       <c r="C212" t="s">
-        <v>479</v>
+        <v>212</v>
       </c>
       <c r="D212" t="s">
-        <v>480</v>
+        <v>213</v>
       </c>
       <c r="E212">
-        <v>57767</v>
+        <v>56438</v>
       </c>
       <c r="F212" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="G212" s="5">
-        <v>46037</v>
+        <v>46030</v>
       </c>
       <c r="H212" s="5">
-        <v>46054</v>
+        <v>46047</v>
       </c>
       <c r="I212" s="5">
-        <v>46092</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B213" t="s">
-        <v>362</v>
+        <v>96</v>
       </c>
       <c r="C213" t="s">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="D213" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="E213">
-        <v>52702</v>
+        <v>57743</v>
       </c>
       <c r="F213" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G213" s="5">
-        <v>46057</v>
+        <v>46013</v>
       </c>
       <c r="H213" s="5">
-        <v>46062</v>
+        <v>46037</v>
       </c>
       <c r="I213" s="5">
-        <v>46057</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B214" t="s">
-        <v>362</v>
+        <v>96</v>
       </c>
       <c r="C214" t="s">
-        <v>365</v>
+        <v>97</v>
       </c>
       <c r="D214" t="s">
-        <v>366</v>
+        <v>98</v>
       </c>
       <c r="E214">
-        <v>51793</v>
+        <v>57671</v>
       </c>
       <c r="F214" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G214" s="5">
-        <v>46057</v>
+        <v>45974</v>
       </c>
       <c r="H214" s="5">
-        <v>46062</v>
+        <v>45992</v>
       </c>
       <c r="I214" s="5">
-        <v>46057</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B215" t="s">
-        <v>362</v>
+        <v>96</v>
       </c>
       <c r="C215" t="s">
-        <v>367</v>
+        <v>214</v>
       </c>
       <c r="D215" t="s">
-        <v>368</v>
+        <v>215</v>
       </c>
       <c r="E215">
-        <v>51802</v>
+        <v>51696</v>
       </c>
       <c r="F215" t="s">
         <v>107</v>
       </c>
       <c r="G215" s="5">
-        <v>46057</v>
+        <v>46029</v>
       </c>
       <c r="H215" s="5">
-        <v>46062</v>
+        <v>46047</v>
       </c>
       <c r="I215" s="5">
-        <v>46057</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B216" t="s">
-        <v>362</v>
+        <v>96</v>
       </c>
       <c r="C216" t="s">
-        <v>369</v>
+        <v>216</v>
       </c>
       <c r="D216" t="s">
-        <v>370</v>
+        <v>217</v>
       </c>
       <c r="E216">
-        <v>51798</v>
+        <v>51693</v>
       </c>
       <c r="F216" t="s">
         <v>107</v>
       </c>
       <c r="G216" s="5">
-        <v>46057</v>
+        <v>46029</v>
       </c>
       <c r="H216" s="5">
-        <v>46062</v>
+        <v>46047</v>
       </c>
       <c r="I216" s="5">
-        <v>46057</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B217" t="s">
-        <v>362</v>
+        <v>96</v>
       </c>
       <c r="C217" t="s">
-        <v>404</v>
+        <v>218</v>
       </c>
       <c r="D217" t="s">
-        <v>405</v>
+        <v>219</v>
       </c>
       <c r="E217">
-        <v>51799</v>
+        <v>51697</v>
       </c>
       <c r="F217" t="s">
         <v>107</v>
       </c>
       <c r="G217" s="5">
-        <v>46076</v>
+        <v>46029</v>
       </c>
       <c r="H217" s="5">
-        <v>46082</v>
+        <v>46047</v>
       </c>
       <c r="I217" s="5">
-        <v>46076</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B218" t="s">
-        <v>362</v>
+        <v>96</v>
       </c>
       <c r="C218" t="s">
-        <v>406</v>
+        <v>220</v>
       </c>
       <c r="D218" t="s">
-        <v>407</v>
+        <v>221</v>
       </c>
       <c r="E218">
-        <v>51800</v>
+        <v>51687</v>
       </c>
       <c r="F218" t="s">
         <v>107</v>
       </c>
       <c r="G218" s="5">
-        <v>46076</v>
+        <v>46030</v>
       </c>
       <c r="H218" s="5">
-        <v>46082</v>
+        <v>46047</v>
       </c>
       <c r="I218" s="5">
-        <v>46076</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B219" t="s">
-        <v>362</v>
+        <v>96</v>
       </c>
       <c r="C219" t="s">
-        <v>408</v>
+        <v>220</v>
       </c>
       <c r="D219" t="s">
-        <v>409</v>
+        <v>221</v>
       </c>
       <c r="E219">
-        <v>51803</v>
+        <v>57756</v>
       </c>
       <c r="F219" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="G219" s="5">
-        <v>46076</v>
-      </c>
-      <c r="H219" s="5">
-        <v>46082</v>
+        <v>46029</v>
+      </c>
+      <c r="H219" t="s">
+        <v>65</v>
       </c>
       <c r="I219" s="5">
-        <v>46076</v>
+        <v>46047</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B220" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C220" t="s">
-        <v>410</v>
+        <v>355</v>
       </c>
       <c r="D220" t="s">
-        <v>411</v>
+        <v>356</v>
       </c>
       <c r="E220">
-        <v>51807</v>
+        <v>53634</v>
       </c>
       <c r="F220" t="s">
-        <v>107</v>
+        <v>357</v>
       </c>
       <c r="G220" s="5">
-        <v>46076</v>
-      </c>
-      <c r="H220" s="5">
-        <v>46082</v>
+        <v>46063</v>
+      </c>
+      <c r="H220" t="s">
+        <v>358</v>
       </c>
       <c r="I220" s="5">
-        <v>46076</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B221" t="s">
-        <v>362</v>
+        <v>573</v>
       </c>
       <c r="C221" t="s">
-        <v>540</v>
+        <v>574</v>
       </c>
       <c r="D221" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
       <c r="E221">
-        <v>51810</v>
+        <v>51556</v>
       </c>
       <c r="F221" t="s">
         <v>107</v>
       </c>
       <c r="G221" s="5">
-        <v>46094</v>
+        <v>46108</v>
       </c>
       <c r="H221" s="5">
-        <v>46098</v>
+        <v>46119</v>
       </c>
       <c r="I221" s="5">
-        <v>46094</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B222" t="s">
-        <v>362</v>
+        <v>573</v>
       </c>
       <c r="C222" t="s">
-        <v>542</v>
+        <v>576</v>
       </c>
       <c r="D222" t="s">
-        <v>543</v>
+        <v>577</v>
       </c>
       <c r="E222">
-        <v>51814</v>
+        <v>51558</v>
       </c>
       <c r="F222" t="s">
         <v>107</v>
       </c>
       <c r="G222" s="5">
-        <v>46094</v>
+        <v>46108</v>
       </c>
       <c r="H222" s="5">
-        <v>46098</v>
+        <v>46119</v>
       </c>
       <c r="I222" s="5">
-        <v>46094</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B223" t="s">
-        <v>362</v>
+        <v>573</v>
       </c>
       <c r="C223" t="s">
-        <v>544</v>
+        <v>578</v>
       </c>
       <c r="D223" t="s">
-        <v>545</v>
+        <v>579</v>
       </c>
       <c r="E223">
-        <v>53472</v>
+        <v>51561</v>
       </c>
       <c r="F223" t="s">
         <v>107</v>
       </c>
       <c r="G223" s="5">
-        <v>46094</v>
+        <v>46108</v>
       </c>
       <c r="H223" s="5">
-        <v>46098</v>
+        <v>46119</v>
       </c>
       <c r="I223" s="5">
-        <v>46094</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B224" t="s">
-        <v>362</v>
+        <v>573</v>
       </c>
       <c r="C224" t="s">
-        <v>546</v>
+        <v>580</v>
       </c>
       <c r="D224" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
       <c r="E224">
-        <v>53473</v>
+        <v>51565</v>
       </c>
       <c r="F224" t="s">
         <v>107</v>
       </c>
       <c r="G224" s="5">
-        <v>46094</v>
+        <v>46108</v>
       </c>
       <c r="H224" s="5">
-        <v>46098</v>
+        <v>46119</v>
       </c>
       <c r="I224" s="5">
-        <v>46094</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="B225" t="s">
-        <v>362</v>
+        <v>573</v>
       </c>
       <c r="C225" t="s">
-        <v>371</v>
+        <v>214</v>
       </c>
       <c r="D225" t="s">
-        <v>372</v>
+        <v>582</v>
       </c>
       <c r="E225">
-        <v>52701</v>
+        <v>51559</v>
       </c>
       <c r="F225" t="s">
         <v>107</v>
       </c>
       <c r="G225" s="5">
-        <v>46057</v>
+        <v>46108</v>
       </c>
       <c r="H225" s="5">
-        <v>46062</v>
+        <v>46119</v>
       </c>
       <c r="I225" s="5">
-        <v>46057</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B226" t="s">
-        <v>35</v>
+        <v>573</v>
       </c>
       <c r="C226" t="s">
-        <v>123</v>
+        <v>583</v>
       </c>
       <c r="D226" t="s">
-        <v>481</v>
+        <v>584</v>
       </c>
       <c r="E226">
-        <v>57591</v>
+        <v>51568</v>
       </c>
       <c r="F226" t="s">
         <v>107</v>
       </c>
       <c r="G226" s="5">
-        <v>46087</v>
+        <v>46108</v>
       </c>
       <c r="H226" s="5">
-        <v>46096</v>
+        <v>46119</v>
       </c>
       <c r="I226" s="5">
-        <v>46087</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B227" t="s">
-        <v>35</v>
+        <v>573</v>
       </c>
       <c r="C227" t="s">
-        <v>482</v>
+        <v>585</v>
       </c>
       <c r="D227" t="s">
-        <v>483</v>
+        <v>586</v>
       </c>
       <c r="E227">
-        <v>57097</v>
+        <v>51564</v>
       </c>
       <c r="F227" t="s">
         <v>107</v>
       </c>
       <c r="G227" s="5">
-        <v>46087</v>
+        <v>46108</v>
       </c>
       <c r="H227" s="5">
-        <v>46096</v>
+        <v>46119</v>
       </c>
       <c r="I227" s="5">
-        <v>46087</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B228" t="s">
-        <v>35</v>
+        <v>573</v>
       </c>
       <c r="C228" t="s">
-        <v>484</v>
+        <v>587</v>
       </c>
       <c r="D228" t="s">
-        <v>485</v>
+        <v>588</v>
       </c>
       <c r="E228">
-        <v>57272</v>
+        <v>51566</v>
       </c>
       <c r="F228" t="s">
         <v>107</v>
       </c>
       <c r="G228" s="5">
-        <v>46087</v>
+        <v>46108</v>
       </c>
       <c r="H228" s="5">
-        <v>46096</v>
+        <v>46119</v>
       </c>
       <c r="I228" s="5">
-        <v>46087</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B229" t="s">
-        <v>35</v>
+        <v>573</v>
       </c>
       <c r="C229" t="s">
-        <v>100</v>
+        <v>589</v>
       </c>
       <c r="D229" t="s">
-        <v>101</v>
+        <v>590</v>
       </c>
       <c r="E229">
-        <v>57604</v>
+        <v>51567</v>
       </c>
       <c r="F229" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G229" s="5">
-        <v>45952</v>
+        <v>46108</v>
       </c>
       <c r="H229" s="5">
-        <v>45976</v>
+        <v>46119</v>
       </c>
       <c r="I229" s="5">
-        <v>46038</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B230" t="s">
-        <v>35</v>
+        <v>222</v>
       </c>
       <c r="C230" t="s">
-        <v>102</v>
+        <v>223</v>
       </c>
       <c r="D230" t="s">
-        <v>103</v>
+        <v>224</v>
       </c>
       <c r="E230">
-        <v>57606</v>
+        <v>53224</v>
       </c>
       <c r="F230" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G230" s="5">
-        <v>45952</v>
+        <v>46031</v>
       </c>
       <c r="H230" s="5">
-        <v>45976</v>
+        <v>46047</v>
       </c>
       <c r="I230" s="5">
-        <v>46038</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="B231" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="C231" t="s">
-        <v>229</v>
+        <v>359</v>
       </c>
       <c r="D231" t="s">
-        <v>230</v>
+        <v>360</v>
       </c>
       <c r="E231">
-        <v>57088</v>
+        <v>57708</v>
       </c>
       <c r="F231" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="G231" s="5">
-        <v>46029</v>
+        <v>46001</v>
       </c>
       <c r="H231" s="5">
-        <v>46047</v>
+        <v>46023</v>
       </c>
       <c r="I231" s="5">
-        <v>46029</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="B232" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C232" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D232" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E232">
-        <v>56876</v>
+        <v>55787</v>
       </c>
       <c r="F232" t="s">
         <v>107</v>
       </c>
       <c r="G232" s="5">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="H232" s="5">
         <v>46047</v>
       </c>
       <c r="I232" s="5">
-        <v>46029</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B233" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="C233" t="s">
-        <v>45</v>
+        <v>477</v>
       </c>
       <c r="D233" t="s">
-        <v>46</v>
+        <v>478</v>
       </c>
       <c r="E233">
-        <v>57639</v>
+        <v>57766</v>
       </c>
       <c r="F233" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G233" s="5">
-        <v>45961</v>
+        <v>46037</v>
       </c>
       <c r="H233" s="5">
-        <v>45976</v>
+        <v>46054</v>
       </c>
       <c r="I233" s="5">
-        <v>46023</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B234" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="C234" t="s">
-        <v>412</v>
+        <v>479</v>
       </c>
       <c r="D234" t="s">
-        <v>413</v>
+        <v>480</v>
       </c>
       <c r="E234">
-        <v>56505</v>
+        <v>57767</v>
       </c>
       <c r="F234" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="G234" s="5">
-        <v>46071</v>
+        <v>46037</v>
       </c>
       <c r="H234" s="5">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="I234" s="5">
-        <v>46071</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B235" t="s">
-        <v>27</v>
+        <v>362</v>
       </c>
       <c r="C235" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="D235" t="s">
-        <v>29</v>
+        <v>364</v>
       </c>
       <c r="E235">
-        <v>57419</v>
+        <v>52702</v>
       </c>
       <c r="F235" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G235" s="5">
-        <v>45895</v>
+        <v>46057</v>
       </c>
       <c r="H235" s="5">
-        <v>45915</v>
+        <v>46062</v>
       </c>
       <c r="I235" s="5">
-        <v>46023</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B236" t="s">
-        <v>27</v>
+        <v>362</v>
       </c>
       <c r="C236" t="s">
-        <v>28</v>
+        <v>365</v>
       </c>
       <c r="D236" t="s">
-        <v>29</v>
+        <v>366</v>
       </c>
       <c r="E236">
-        <v>57420</v>
+        <v>51793</v>
       </c>
       <c r="F236" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G236" s="5">
-        <v>45895</v>
+        <v>46057</v>
       </c>
       <c r="H236" s="5">
-        <v>45915</v>
+        <v>46062</v>
       </c>
       <c r="I236" s="5">
-        <v>46023</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B237" t="s">
-        <v>27</v>
+        <v>362</v>
       </c>
       <c r="C237" t="s">
-        <v>30</v>
+        <v>367</v>
       </c>
       <c r="D237" t="s">
-        <v>31</v>
+        <v>368</v>
       </c>
       <c r="E237">
-        <v>57418</v>
+        <v>51802</v>
       </c>
       <c r="F237" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G237" s="5">
-        <v>45895</v>
+        <v>46057</v>
       </c>
       <c r="H237" s="5">
-        <v>45915</v>
+        <v>46062</v>
       </c>
       <c r="I237" s="5">
-        <v>46023</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B238" t="s">
-        <v>27</v>
+        <v>362</v>
       </c>
       <c r="C238" t="s">
-        <v>32</v>
+        <v>369</v>
       </c>
       <c r="D238" t="s">
-        <v>33</v>
+        <v>370</v>
       </c>
       <c r="E238">
-        <v>57417</v>
+        <v>51798</v>
       </c>
       <c r="F238" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G238" s="5">
-        <v>45895</v>
+        <v>46057</v>
       </c>
       <c r="H238" s="5">
-        <v>45915</v>
+        <v>46062</v>
       </c>
       <c r="I238" s="5">
-        <v>46023</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B239" t="s">
-        <v>27</v>
+        <v>362</v>
       </c>
       <c r="C239" t="s">
-        <v>32</v>
+        <v>404</v>
       </c>
       <c r="D239" t="s">
-        <v>33</v>
+        <v>405</v>
       </c>
       <c r="E239">
-        <v>57421</v>
+        <v>51799</v>
       </c>
       <c r="F239" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G239" s="5">
-        <v>45895</v>
+        <v>46076</v>
       </c>
       <c r="H239" s="5">
-        <v>45915</v>
+        <v>46082</v>
       </c>
       <c r="I239" s="5">
-        <v>46023</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B240" t="s">
-        <v>234</v>
+        <v>362</v>
       </c>
       <c r="C240" t="s">
-        <v>234</v>
+        <v>406</v>
       </c>
       <c r="D240" t="s">
-        <v>235</v>
+        <v>407</v>
       </c>
       <c r="E240">
-        <v>57760</v>
+        <v>51800</v>
       </c>
       <c r="F240" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G240" s="5">
-        <v>46035</v>
-      </c>
-      <c r="H240" t="s">
-        <v>65</v>
+        <v>46076</v>
+      </c>
+      <c r="H240" s="5">
+        <v>46082</v>
       </c>
       <c r="I240" s="5">
-        <v>46047</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B241" t="s">
-        <v>14</v>
+        <v>362</v>
       </c>
       <c r="C241" t="s">
-        <v>14</v>
+        <v>408</v>
       </c>
       <c r="D241" t="s">
-        <v>15</v>
+        <v>409</v>
       </c>
       <c r="E241">
-        <v>57459</v>
+        <v>51803</v>
       </c>
       <c r="F241" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G241" s="5">
-        <v>45902</v>
+        <v>46076</v>
       </c>
       <c r="H241" s="5">
-        <v>45915</v>
+        <v>46082</v>
       </c>
       <c r="I241" s="5">
-        <v>46023</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B242" t="s">
-        <v>14</v>
+        <v>362</v>
       </c>
       <c r="C242" t="s">
-        <v>14</v>
+        <v>410</v>
       </c>
       <c r="D242" t="s">
-        <v>15</v>
+        <v>411</v>
       </c>
       <c r="E242">
-        <v>57485</v>
+        <v>51807</v>
       </c>
       <c r="F242" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G242" s="5">
-        <v>45911</v>
+        <v>46076</v>
       </c>
       <c r="H242" s="5">
-        <v>45931</v>
+        <v>46082</v>
       </c>
       <c r="I242" s="5">
-        <v>46023</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>12</v>
+        <v>361</v>
       </c>
       <c r="B243" t="s">
-        <v>14</v>
+        <v>362</v>
       </c>
       <c r="C243" t="s">
-        <v>14</v>
+        <v>540</v>
       </c>
       <c r="D243" t="s">
-        <v>15</v>
+        <v>541</v>
       </c>
       <c r="E243">
-        <v>57486</v>
+        <v>51810</v>
       </c>
       <c r="F243" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G243" s="5">
-        <v>45911</v>
+        <v>46094</v>
       </c>
       <c r="H243" s="5">
-        <v>45931</v>
+        <v>46098</v>
       </c>
       <c r="I243" s="5">
-        <v>46023</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="B244" t="s">
-        <v>486</v>
+        <v>362</v>
       </c>
       <c r="C244" t="s">
-        <v>487</v>
+        <v>542</v>
       </c>
       <c r="D244" t="s">
-        <v>488</v>
+        <v>543</v>
       </c>
       <c r="E244">
-        <v>57758</v>
+        <v>51814</v>
       </c>
       <c r="F244" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G244" s="5">
-        <v>46030</v>
+        <v>46094</v>
       </c>
       <c r="H244" s="5">
-        <v>46054</v>
+        <v>46098</v>
       </c>
       <c r="I244" s="5">
-        <v>46097</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="B245" t="s">
-        <v>489</v>
+        <v>362</v>
       </c>
       <c r="C245" t="s">
-        <v>490</v>
+        <v>544</v>
       </c>
       <c r="D245" t="s">
-        <v>491</v>
+        <v>545</v>
       </c>
       <c r="E245">
-        <v>57738</v>
+        <v>53472</v>
       </c>
       <c r="F245" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G245" s="5">
-        <v>46010</v>
+        <v>46094</v>
       </c>
       <c r="H245" s="5">
-        <v>46037</v>
+        <v>46098</v>
       </c>
       <c r="I245" s="5">
-        <v>46097</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="B246" t="s">
-        <v>489</v>
+        <v>362</v>
       </c>
       <c r="C246" t="s">
-        <v>492</v>
+        <v>546</v>
       </c>
       <c r="D246" t="s">
-        <v>493</v>
+        <v>547</v>
       </c>
       <c r="E246">
-        <v>57739</v>
+        <v>53473</v>
       </c>
       <c r="F246" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="G246" s="5">
-        <v>46010</v>
+        <v>46094</v>
       </c>
       <c r="H246" s="5">
-        <v>46037</v>
+        <v>46098</v>
       </c>
       <c r="I246" s="5">
-        <v>46097</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="B247" t="s">
-        <v>489</v>
+        <v>362</v>
       </c>
       <c r="C247" t="s">
-        <v>494</v>
+        <v>371</v>
       </c>
       <c r="D247" t="s">
-        <v>495</v>
+        <v>372</v>
       </c>
       <c r="E247">
-        <v>57744</v>
+        <v>52701</v>
       </c>
       <c r="F247" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G247" s="5">
-        <v>46014</v>
+        <v>46057</v>
       </c>
       <c r="H247" s="5">
-        <v>46037</v>
+        <v>46062</v>
       </c>
       <c r="I247" s="5">
-        <v>46097</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>236</v>
+        <v>99</v>
       </c>
       <c r="B248" t="s">
-        <v>489</v>
+        <v>35</v>
       </c>
       <c r="C248" t="s">
-        <v>496</v>
+        <v>123</v>
       </c>
       <c r="D248" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="E248">
-        <v>57742</v>
+        <v>57591</v>
       </c>
       <c r="F248" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="G248" s="5">
-        <v>46010</v>
+        <v>46087</v>
       </c>
       <c r="H248" s="5">
-        <v>46037</v>
+        <v>46096</v>
       </c>
       <c r="I248" s="5">
-        <v>46097</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>236</v>
+        <v>99</v>
       </c>
       <c r="B249" t="s">
-        <v>237</v>
+        <v>35</v>
       </c>
       <c r="C249" t="s">
-        <v>238</v>
+        <v>482</v>
       </c>
       <c r="D249" t="s">
-        <v>239</v>
+        <v>483</v>
       </c>
       <c r="E249">
-        <v>57324</v>
+        <v>57097</v>
       </c>
       <c r="F249" t="s">
         <v>107</v>
       </c>
       <c r="G249" s="5">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="H249" s="5">
-        <v>46047</v>
+        <v>46096</v>
       </c>
       <c r="I249" s="5">
-        <v>46030</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>498</v>
+        <v>99</v>
       </c>
       <c r="B250" t="s">
         <v>35</v>
       </c>
       <c r="C250" t="s">
+        <v>484</v>
+      </c>
+      <c r="D250" t="s">
+        <v>485</v>
+      </c>
+      <c r="E250">
+        <v>57272</v>
+      </c>
+      <c r="F250" t="s">
+        <v>107</v>
+      </c>
+      <c r="G250" s="5">
+        <v>46087</v>
+      </c>
+      <c r="H250" s="5">
+        <v>46096</v>
+      </c>
+      <c r="I250" s="5">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>99</v>
+      </c>
+      <c r="B251" t="s">
+        <v>35</v>
+      </c>
+      <c r="C251" t="s">
+        <v>100</v>
+      </c>
+      <c r="D251" t="s">
+        <v>101</v>
+      </c>
+      <c r="E251">
+        <v>57604</v>
+      </c>
+      <c r="F251" t="s">
+        <v>10</v>
+      </c>
+      <c r="G251" s="5">
+        <v>45952</v>
+      </c>
+      <c r="H251" s="5">
+        <v>45976</v>
+      </c>
+      <c r="I251" s="5">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>99</v>
+      </c>
+      <c r="B252" t="s">
+        <v>35</v>
+      </c>
+      <c r="C252" t="s">
+        <v>591</v>
+      </c>
+      <c r="D252" t="s">
+        <v>592</v>
+      </c>
+      <c r="E252">
+        <v>51828</v>
+      </c>
+      <c r="F252" t="s">
+        <v>107</v>
+      </c>
+      <c r="G252" s="5">
+        <v>46104</v>
+      </c>
+      <c r="H252" s="5">
+        <v>46119</v>
+      </c>
+      <c r="I252" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>99</v>
+      </c>
+      <c r="B253" t="s">
+        <v>35</v>
+      </c>
+      <c r="C253" t="s">
+        <v>102</v>
+      </c>
+      <c r="D253" t="s">
+        <v>103</v>
+      </c>
+      <c r="E253">
+        <v>57606</v>
+      </c>
+      <c r="F253" t="s">
+        <v>10</v>
+      </c>
+      <c r="G253" s="5">
+        <v>45952</v>
+      </c>
+      <c r="H253" s="5">
+        <v>45976</v>
+      </c>
+      <c r="I253" s="5">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>228</v>
+      </c>
+      <c r="B254" t="s">
+        <v>35</v>
+      </c>
+      <c r="C254" t="s">
+        <v>229</v>
+      </c>
+      <c r="D254" t="s">
+        <v>230</v>
+      </c>
+      <c r="E254">
+        <v>57088</v>
+      </c>
+      <c r="F254" t="s">
+        <v>107</v>
+      </c>
+      <c r="G254" s="5">
+        <v>46029</v>
+      </c>
+      <c r="H254" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I254" s="5">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>228</v>
+      </c>
+      <c r="B255" t="s">
+        <v>231</v>
+      </c>
+      <c r="C255" t="s">
+        <v>232</v>
+      </c>
+      <c r="D255" t="s">
+        <v>233</v>
+      </c>
+      <c r="E255">
+        <v>56876</v>
+      </c>
+      <c r="F255" t="s">
+        <v>107</v>
+      </c>
+      <c r="G255" s="5">
+        <v>46029</v>
+      </c>
+      <c r="H255" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I255" s="5">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>228</v>
+      </c>
+      <c r="B256" t="s">
+        <v>593</v>
+      </c>
+      <c r="C256" t="s">
+        <v>594</v>
+      </c>
+      <c r="D256" t="s">
+        <v>595</v>
+      </c>
+      <c r="E256">
+        <v>55804</v>
+      </c>
+      <c r="F256" t="s">
+        <v>107</v>
+      </c>
+      <c r="G256" s="5">
+        <v>46098</v>
+      </c>
+      <c r="H256" s="5">
+        <v>46119</v>
+      </c>
+      <c r="I256" s="5">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>44</v>
+      </c>
+      <c r="B257" t="s">
+        <v>35</v>
+      </c>
+      <c r="C257" t="s">
+        <v>45</v>
+      </c>
+      <c r="D257" t="s">
+        <v>46</v>
+      </c>
+      <c r="E257">
+        <v>57639</v>
+      </c>
+      <c r="F257" t="s">
+        <v>19</v>
+      </c>
+      <c r="G257" s="5">
+        <v>45961</v>
+      </c>
+      <c r="H257" s="5">
+        <v>45976</v>
+      </c>
+      <c r="I257" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>44</v>
+      </c>
+      <c r="B258" t="s">
+        <v>35</v>
+      </c>
+      <c r="C258" t="s">
+        <v>412</v>
+      </c>
+      <c r="D258" t="s">
+        <v>413</v>
+      </c>
+      <c r="E258">
+        <v>56505</v>
+      </c>
+      <c r="F258" t="s">
+        <v>107</v>
+      </c>
+      <c r="G258" s="5">
+        <v>46071</v>
+      </c>
+      <c r="H258" s="5">
+        <v>46082</v>
+      </c>
+      <c r="I258" s="5">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>596</v>
+      </c>
+      <c r="B259" t="s">
+        <v>35</v>
+      </c>
+      <c r="C259" t="s">
+        <v>597</v>
+      </c>
+      <c r="D259" t="s">
+        <v>598</v>
+      </c>
+      <c r="E259">
+        <v>53308</v>
+      </c>
+      <c r="F259" t="s">
+        <v>107</v>
+      </c>
+      <c r="G259" s="5">
+        <v>46105</v>
+      </c>
+      <c r="H259" s="5">
+        <v>46119</v>
+      </c>
+      <c r="I259" s="5">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>12</v>
+      </c>
+      <c r="B260" t="s">
+        <v>27</v>
+      </c>
+      <c r="C260" t="s">
+        <v>28</v>
+      </c>
+      <c r="D260" t="s">
+        <v>29</v>
+      </c>
+      <c r="E260">
+        <v>57419</v>
+      </c>
+      <c r="F260" t="s">
+        <v>10</v>
+      </c>
+      <c r="G260" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H260" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I260" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>12</v>
+      </c>
+      <c r="B261" t="s">
+        <v>27</v>
+      </c>
+      <c r="C261" t="s">
+        <v>28</v>
+      </c>
+      <c r="D261" t="s">
+        <v>29</v>
+      </c>
+      <c r="E261">
+        <v>57420</v>
+      </c>
+      <c r="F261" t="s">
+        <v>10</v>
+      </c>
+      <c r="G261" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H261" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I261" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>12</v>
+      </c>
+      <c r="B262" t="s">
+        <v>27</v>
+      </c>
+      <c r="C262" t="s">
+        <v>30</v>
+      </c>
+      <c r="D262" t="s">
+        <v>31</v>
+      </c>
+      <c r="E262">
+        <v>57418</v>
+      </c>
+      <c r="F262" t="s">
+        <v>10</v>
+      </c>
+      <c r="G262" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H262" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I262" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>12</v>
+      </c>
+      <c r="B263" t="s">
+        <v>27</v>
+      </c>
+      <c r="C263" t="s">
+        <v>32</v>
+      </c>
+      <c r="D263" t="s">
+        <v>33</v>
+      </c>
+      <c r="E263">
+        <v>57417</v>
+      </c>
+      <c r="F263" t="s">
+        <v>10</v>
+      </c>
+      <c r="G263" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H263" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I263" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>12</v>
+      </c>
+      <c r="B264" t="s">
+        <v>27</v>
+      </c>
+      <c r="C264" t="s">
+        <v>32</v>
+      </c>
+      <c r="D264" t="s">
+        <v>33</v>
+      </c>
+      <c r="E264">
+        <v>57421</v>
+      </c>
+      <c r="F264" t="s">
+        <v>10</v>
+      </c>
+      <c r="G264" s="5">
+        <v>45895</v>
+      </c>
+      <c r="H264" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I264" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>12</v>
+      </c>
+      <c r="B265" t="s">
+        <v>234</v>
+      </c>
+      <c r="C265" t="s">
+        <v>234</v>
+      </c>
+      <c r="D265" t="s">
+        <v>235</v>
+      </c>
+      <c r="E265">
+        <v>57760</v>
+      </c>
+      <c r="F265" t="s">
+        <v>64</v>
+      </c>
+      <c r="G265" s="5">
+        <v>46035</v>
+      </c>
+      <c r="H265" t="s">
+        <v>65</v>
+      </c>
+      <c r="I265" s="5">
+        <v>46047</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>12</v>
+      </c>
+      <c r="B266" t="s">
+        <v>14</v>
+      </c>
+      <c r="C266" t="s">
+        <v>14</v>
+      </c>
+      <c r="D266" t="s">
+        <v>15</v>
+      </c>
+      <c r="E266">
+        <v>57459</v>
+      </c>
+      <c r="F266" t="s">
+        <v>10</v>
+      </c>
+      <c r="G266" s="5">
+        <v>45902</v>
+      </c>
+      <c r="H266" s="5">
+        <v>45915</v>
+      </c>
+      <c r="I266" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>12</v>
+      </c>
+      <c r="B267" t="s">
+        <v>14</v>
+      </c>
+      <c r="C267" t="s">
+        <v>14</v>
+      </c>
+      <c r="D267" t="s">
+        <v>15</v>
+      </c>
+      <c r="E267">
+        <v>57485</v>
+      </c>
+      <c r="F267" t="s">
+        <v>10</v>
+      </c>
+      <c r="G267" s="5">
+        <v>45911</v>
+      </c>
+      <c r="H267" s="5">
+        <v>45931</v>
+      </c>
+      <c r="I267" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>12</v>
+      </c>
+      <c r="B268" t="s">
+        <v>14</v>
+      </c>
+      <c r="C268" t="s">
+        <v>14</v>
+      </c>
+      <c r="D268" t="s">
+        <v>15</v>
+      </c>
+      <c r="E268">
+        <v>57486</v>
+      </c>
+      <c r="F268" t="s">
+        <v>10</v>
+      </c>
+      <c r="G268" s="5">
+        <v>45911</v>
+      </c>
+      <c r="H268" s="5">
+        <v>45931</v>
+      </c>
+      <c r="I268" s="5">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>236</v>
+      </c>
+      <c r="B269" t="s">
+        <v>486</v>
+      </c>
+      <c r="C269" t="s">
+        <v>487</v>
+      </c>
+      <c r="D269" t="s">
+        <v>488</v>
+      </c>
+      <c r="E269">
+        <v>57758</v>
+      </c>
+      <c r="F269" t="s">
+        <v>10</v>
+      </c>
+      <c r="G269" s="5">
+        <v>46030</v>
+      </c>
+      <c r="H269" s="5">
+        <v>46054</v>
+      </c>
+      <c r="I269" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>236</v>
+      </c>
+      <c r="B270" t="s">
+        <v>489</v>
+      </c>
+      <c r="C270" t="s">
+        <v>490</v>
+      </c>
+      <c r="D270" t="s">
+        <v>491</v>
+      </c>
+      <c r="E270">
+        <v>57738</v>
+      </c>
+      <c r="F270" t="s">
+        <v>107</v>
+      </c>
+      <c r="G270" s="5">
+        <v>46119</v>
+      </c>
+      <c r="H270" s="5">
+        <v>46121</v>
+      </c>
+      <c r="I270" s="5">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>236</v>
+      </c>
+      <c r="B271" t="s">
+        <v>489</v>
+      </c>
+      <c r="C271" t="s">
+        <v>490</v>
+      </c>
+      <c r="D271" t="s">
+        <v>491</v>
+      </c>
+      <c r="E271">
+        <v>57738</v>
+      </c>
+      <c r="F271" t="s">
+        <v>141</v>
+      </c>
+      <c r="G271" s="5">
+        <v>46010</v>
+      </c>
+      <c r="H271" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I271" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>236</v>
+      </c>
+      <c r="B272" t="s">
+        <v>489</v>
+      </c>
+      <c r="C272" t="s">
+        <v>492</v>
+      </c>
+      <c r="D272" t="s">
+        <v>493</v>
+      </c>
+      <c r="E272">
+        <v>57739</v>
+      </c>
+      <c r="F272" t="s">
+        <v>107</v>
+      </c>
+      <c r="G272" s="5">
+        <v>46120</v>
+      </c>
+      <c r="H272" s="5">
+        <v>46121</v>
+      </c>
+      <c r="I272" s="5">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>236</v>
+      </c>
+      <c r="B273" t="s">
+        <v>489</v>
+      </c>
+      <c r="C273" t="s">
+        <v>492</v>
+      </c>
+      <c r="D273" t="s">
+        <v>493</v>
+      </c>
+      <c r="E273">
+        <v>57739</v>
+      </c>
+      <c r="F273" t="s">
+        <v>141</v>
+      </c>
+      <c r="G273" s="5">
+        <v>46010</v>
+      </c>
+      <c r="H273" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I273" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>236</v>
+      </c>
+      <c r="B274" t="s">
+        <v>489</v>
+      </c>
+      <c r="C274" t="s">
+        <v>494</v>
+      </c>
+      <c r="D274" t="s">
+        <v>495</v>
+      </c>
+      <c r="E274">
+        <v>57744</v>
+      </c>
+      <c r="F274" t="s">
+        <v>82</v>
+      </c>
+      <c r="G274" s="5">
+        <v>46014</v>
+      </c>
+      <c r="H274" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I274" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>236</v>
+      </c>
+      <c r="B275" t="s">
+        <v>489</v>
+      </c>
+      <c r="C275" t="s">
+        <v>496</v>
+      </c>
+      <c r="D275" t="s">
+        <v>497</v>
+      </c>
+      <c r="E275">
+        <v>57742</v>
+      </c>
+      <c r="F275" t="s">
+        <v>82</v>
+      </c>
+      <c r="G275" s="5">
+        <v>46010</v>
+      </c>
+      <c r="H275" s="5">
+        <v>46037</v>
+      </c>
+      <c r="I275" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>236</v>
+      </c>
+      <c r="B276" t="s">
+        <v>237</v>
+      </c>
+      <c r="C276" t="s">
+        <v>238</v>
+      </c>
+      <c r="D276" t="s">
+        <v>239</v>
+      </c>
+      <c r="E276">
+        <v>57324</v>
+      </c>
+      <c r="F276" t="s">
+        <v>107</v>
+      </c>
+      <c r="G276" s="5">
+        <v>46030</v>
+      </c>
+      <c r="H276" s="5">
+        <v>46047</v>
+      </c>
+      <c r="I276" s="5">
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>236</v>
+      </c>
+      <c r="B277" t="s">
+        <v>599</v>
+      </c>
+      <c r="C277" t="s">
+        <v>600</v>
+      </c>
+      <c r="D277" t="s">
+        <v>601</v>
+      </c>
+      <c r="E277">
+        <v>52142</v>
+      </c>
+      <c r="F277" t="s">
+        <v>107</v>
+      </c>
+      <c r="G277" s="5">
+        <v>46102</v>
+      </c>
+      <c r="H277" s="5">
+        <v>46119</v>
+      </c>
+      <c r="I277" s="5">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>498</v>
+      </c>
+      <c r="B278" t="s">
+        <v>35</v>
+      </c>
+      <c r="C278" t="s">
         <v>499</v>
       </c>
-      <c r="D250" t="s">
+      <c r="D278" t="s">
         <v>500</v>
       </c>
-      <c r="E250">
+      <c r="E278">
         <v>57686</v>
       </c>
-      <c r="F250" t="s">
+      <c r="F278" t="s">
         <v>10</v>
       </c>
-      <c r="G250" s="5">
+      <c r="G278" s="5">
         <v>45976</v>
       </c>
-      <c r="H250" s="5">
+      <c r="H278" s="5">
         <v>46006</v>
       </c>
-      <c r="I250" s="5">
+      <c r="I278" s="5">
         <v>46097</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>498</v>
+      </c>
+      <c r="B279" t="s">
+        <v>35</v>
+      </c>
+      <c r="C279" t="s">
+        <v>499</v>
+      </c>
+      <c r="D279" t="s">
+        <v>500</v>
+      </c>
+      <c r="E279">
+        <v>57686</v>
+      </c>
+      <c r="F279" t="s">
+        <v>107</v>
+      </c>
+      <c r="G279" s="5">
+        <v>46120</v>
+      </c>
+      <c r="H279" s="5">
+        <v>46121</v>
+      </c>
+      <c r="I279" s="5">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>498</v>
+      </c>
+      <c r="B280" t="s">
+        <v>35</v>
+      </c>
+      <c r="C280" t="s">
+        <v>602</v>
+      </c>
+      <c r="D280" t="s">
+        <v>603</v>
+      </c>
+      <c r="E280">
+        <v>52163</v>
+      </c>
+      <c r="F280" t="s">
+        <v>107</v>
+      </c>
+      <c r="G280" s="5">
+        <v>46102</v>
+      </c>
+      <c r="H280" s="5">
+        <v>46119</v>
+      </c>
+      <c r="I280" s="5">
+        <v>46102</v>
       </c>
     </row>
   </sheetData>
@@ -10043,7 +11090,15 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E2" s="3"/>
+      <c r="C2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>606</v>
+      </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>

--- a/Utah_Index_of_Changes.xlsx
+++ b/Utah_Index_of_Changes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Shared drives\DAS_Rules_DAR\Index of Changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22AC235-E0B9-4FB7-AD42-EDFD589E7254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A5A40C-1F50-4867-8059-C7FFD8B78037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="820">
   <si>
     <t>Agency Name</t>
   </si>
@@ -2481,17 +2481,30 @@
   </si>
   <si>
     <t>R933-2</t>
+  </si>
+  <si>
+    <t>R636. Energy Development (Office of)</t>
+  </si>
+  <si>
+    <t>After creating Title R636 in 2024 (see 2025 Index of Changes), OAR determined moving the existing Title R362 to the Department of Natural Resources would minimize confusion for the regulated public. No rules were created or enforced under Title R636 since its creation, and it has been removed from the Administrative Code.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2550,22 +2563,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3187,7 +3204,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A1:E3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A1:E4">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Old Agency"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Old R-Number and Title"/>
@@ -15815,14 +15832,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.140625" customWidth="1"/>
-    <col min="2" max="2" width="42.7109375" customWidth="1"/>
-    <col min="3" max="3" width="43" customWidth="1"/>
-    <col min="4" max="4" width="51.85546875" customWidth="1"/>
-    <col min="5" max="5" width="180" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="133" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="32.7109375" customWidth="1"/>
@@ -15846,7 +15863,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
@@ -15862,997 +15879,33 @@
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>818</v>
+      </c>
       <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="10" t="s">
+        <v>819</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
         <v>679</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
